--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Notes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Sales Track'!$A$1:$W$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Sales Track'!$A$1:$X$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22,9 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="d-mmm-yyyy"/>
+    <numFmt numFmtId="166" formatCode="&quot;£&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="&quot;€&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="169" formatCode="&quot;CA$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -97,23 +101,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -479,32 +489,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
     <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="18" customWidth="1" min="22" max="22"/>
-    <col width="16" customWidth="1" min="23" max="23"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -520,105 +531,110 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Today's Sales (£)</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Yesterday Sales (£)</t>
+          <t>Today's Sales</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Sales Diff (£)</t>
+          <t>Yesterday Sales</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Sales Diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Sales Growth %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Same Day LY Sales (£)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Same Day LY Sales</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Today's Orders</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Yesterday Orders</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Order Growth %</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Same Day LY Orders</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Units Sold</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Avg Order Value (£)</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Avg Order Value</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Active Listing</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>AH Listing</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>AH Listing Sales</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>AH Sales Trend</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>PH Listing</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>PH Listing Sales</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>PH Sales Trend</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Account Sales Trend</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>AH Holder</t>
         </is>
@@ -635,74 +651,79 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="E2" s="4" t="n">
         <v>837.9299999999999</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="F2" s="4" t="n">
         <v>863.36</v>
       </c>
-      <c r="F2" s="4">
-        <f>D2-E2</f>
-        <v/>
-      </c>
-      <c r="G2" s="5">
-        <f>IF(E2=0,"",(D2-E2)/E2)</f>
-        <v/>
-      </c>
-      <c r="H2" s="4" t="n">
+      <c r="G2" s="4">
+        <f>E2-F2</f>
+        <v/>
+      </c>
+      <c r="H2" s="5">
+        <f>IF(F2=0,"",(E2-F2)/F2)</f>
+        <v/>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>1233.51</v>
       </c>
-      <c r="I2" s="6" t="n">
+      <c r="J2" s="6" t="n">
         <v>42</v>
       </c>
-      <c r="J2" s="6" t="n">
+      <c r="K2" s="6" t="n">
         <v>49</v>
       </c>
-      <c r="K2" s="5">
-        <f>IF(J2=0,"",(I2-J2)/J2)</f>
-        <v/>
-      </c>
-      <c r="L2" s="6" t="n">
+      <c r="L2" s="5">
+        <f>IF(K2=0,"",(J2-K2)/K2)</f>
+        <v/>
+      </c>
+      <c r="M2" s="6" t="n">
         <v>78</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="N2" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="N2" s="4">
-        <f>IF(I2=0,"",D2/I2)</f>
-        <v/>
-      </c>
-      <c r="O2" s="6" t="n">
+      <c r="O2" s="4">
+        <f>IF(J2=0,"",E2/J2)</f>
+        <v/>
+      </c>
+      <c r="P2" s="6" t="n">
         <v>2843</v>
       </c>
-      <c r="P2" s="6" t="n">
+      <c r="Q2" s="6" t="n">
         <v>1598</v>
       </c>
-      <c r="Q2" s="4" t="n">
+      <c r="R2" s="4" t="n">
         <v>436.24</v>
       </c>
-      <c r="R2" s="2">
-        <f>IF(AND('Engine Inputs'!D2=0,Q2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((Q2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((Q2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S2" s="6" t="n">
+      <c r="S2" s="2">
+        <f>IF(AND('Engine Inputs'!E2=0,R2=0),"",IF('Engine Inputs'!E2=0,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&gt;Config!$B$2,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T2" s="6" t="n">
         <v>1245</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>394.11</v>
       </c>
-      <c r="U2" s="2">
-        <f>IF(AND('Engine Inputs'!C2=0,T2=0),"",IF('Engine Inputs'!C2=0,"📈 Up",IF((T2-'Engine Inputs'!C2)/'Engine Inputs'!C2&gt;Config!$B$2,"📈 Up",IF((T2-'Engine Inputs'!C2)/'Engine Inputs'!C2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
       <c r="V2" s="2">
-        <f>IF(AND(E2=0,D2=0),"",IF(E2=0,"📈 Up",IF((D2-E2)/E2&gt;Config!$B$2,"📈 Up",IF((D2-E2)/E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D2=0,U2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W2" s="2">
+        <f>IF(AND(F2=0,E2=0),"",IF(F2=0,"📈 Up",IF((E2-F2)/F2&gt;Config!$B$2,"📈 Up",IF((E2-F2)/F2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Sharmilan</t>
         </is>
@@ -719,74 +740,79 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="E3" s="4" t="n">
         <v>397.95</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="F3" s="4" t="n">
         <v>444.6</v>
       </c>
-      <c r="F3" s="4">
-        <f>D3-E3</f>
-        <v/>
-      </c>
-      <c r="G3" s="5">
-        <f>IF(E3=0,"",(D3-E3)/E3)</f>
-        <v/>
-      </c>
-      <c r="H3" s="4" t="n">
+      <c r="G3" s="4">
+        <f>E3-F3</f>
+        <v/>
+      </c>
+      <c r="H3" s="5">
+        <f>IF(F3=0,"",(E3-F3)/F3)</f>
+        <v/>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>497.19</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="J3" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="K3" s="5">
-        <f>IF(J3=0,"",(I3-J3)/J3)</f>
-        <v/>
-      </c>
-      <c r="L3" s="6" t="n">
+      <c r="L3" s="5">
+        <f>IF(K3=0,"",(J3-K3)/K3)</f>
+        <v/>
+      </c>
+      <c r="M3" s="6" t="n">
         <v>34</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="N3" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="N3" s="4">
-        <f>IF(I3=0,"",D3/I3)</f>
-        <v/>
-      </c>
-      <c r="O3" s="6" t="n">
+      <c r="O3" s="4">
+        <f>IF(J3=0,"",E3/J3)</f>
+        <v/>
+      </c>
+      <c r="P3" s="6" t="n">
         <v>1513</v>
       </c>
-      <c r="P3" s="6" t="n">
+      <c r="Q3" s="6" t="n">
         <v>965</v>
       </c>
-      <c r="Q3" s="4" t="n">
+      <c r="R3" s="4" t="n">
         <v>197.77</v>
       </c>
-      <c r="R3" s="2">
-        <f>IF(AND('Engine Inputs'!D3=0,Q3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((Q3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((Q3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S3" s="6" t="n">
+      <c r="S3" s="2">
+        <f>IF(AND('Engine Inputs'!E3=0,R3=0),"",IF('Engine Inputs'!E3=0,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&gt;Config!$B$2,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T3" s="6" t="n">
         <v>548</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="U3" s="4" t="n">
         <v>223.86</v>
       </c>
-      <c r="U3" s="2">
-        <f>IF(AND('Engine Inputs'!C3=0,T3=0),"",IF('Engine Inputs'!C3=0,"📈 Up",IF((T3-'Engine Inputs'!C3)/'Engine Inputs'!C3&gt;Config!$B$2,"📈 Up",IF((T3-'Engine Inputs'!C3)/'Engine Inputs'!C3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
       <c r="V3" s="2">
-        <f>IF(AND(E3=0,D3=0),"",IF(E3=0,"📈 Up",IF((D3-E3)/E3&gt;Config!$B$2,"📈 Up",IF((D3-E3)/E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D3=0,U3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W3" s="2">
+        <f>IF(AND(F3=0,E3=0),"",IF(F3=0,"📈 Up",IF((E3-F3)/F3&gt;Config!$B$2,"📈 Up",IF((E3-F3)/F3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>Kobiga</t>
         </is>
@@ -803,74 +829,79 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="E4" s="7" t="n">
         <v>306.58</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="F4" s="7" t="n">
         <v>61.33</v>
       </c>
-      <c r="F4" s="4">
-        <f>D4-E4</f>
-        <v/>
-      </c>
-      <c r="G4" s="5">
-        <f>IF(E4=0,"",(D4-E4)/E4)</f>
-        <v/>
-      </c>
-      <c r="H4" s="4" t="n">
+      <c r="G4" s="7">
+        <f>E4-F4</f>
+        <v/>
+      </c>
+      <c r="H4" s="5">
+        <f>IF(F4=0,"",(E4-F4)/F4)</f>
+        <v/>
+      </c>
+      <c r="I4" s="7" t="n">
         <v>534.5599999999999</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="K4" s="5">
-        <f>IF(J4=0,"",(I4-J4)/J4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="6" t="n">
+      <c r="L4" s="5">
+        <f>IF(K4=0,"",(J4-K4)/K4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="N4" s="4">
-        <f>IF(I4=0,"",D4/I4)</f>
-        <v/>
-      </c>
-      <c r="O4" s="6" t="n">
+      <c r="O4" s="7">
+        <f>IF(J4=0,"",E4/J4)</f>
+        <v/>
+      </c>
+      <c r="P4" s="6" t="n">
         <v>1353</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="Q4" s="6" t="n">
         <v>1139</v>
       </c>
-      <c r="Q4" s="4" t="n">
+      <c r="R4" s="7" t="n">
         <v>298.23</v>
       </c>
-      <c r="R4" s="2">
-        <f>IF(AND('Engine Inputs'!D4=0,Q4=0),"",IF('Engine Inputs'!D4=0,"📈 Up",IF((Q4-'Engine Inputs'!D4)/'Engine Inputs'!D4&gt;Config!$B$2,"📈 Up",IF((Q4-'Engine Inputs'!D4)/'Engine Inputs'!D4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S4" s="6" t="n">
+      <c r="S4" s="2">
+        <f>IF(AND('Engine Inputs'!E4=0,R4=0),"",IF('Engine Inputs'!E4=0,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&gt;Config!$B$2,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T4" s="6" t="n">
         <v>214</v>
       </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2">
-        <f>IF(AND('Engine Inputs'!C4=0,T4=0),"",IF('Engine Inputs'!C4=0,"📈 Up",IF((T4-'Engine Inputs'!C4)/'Engine Inputs'!C4&gt;Config!$B$2,"📈 Up",IF((T4-'Engine Inputs'!C4)/'Engine Inputs'!C4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="U4" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V4" s="2">
-        <f>IF(AND(E4=0,D4=0),"",IF(E4=0,"📈 Up",IF((D4-E4)/E4&gt;Config!$B$2,"📈 Up",IF((D4-E4)/E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D4=0,U4=0),"",IF('Engine Inputs'!D4=0,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&gt;Config!$B$2,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W4" s="2">
+        <f>IF(AND(F4=0,E4=0),"",IF(F4=0,"📈 Up",IF((E4-F4)/F4&gt;Config!$B$2,"📈 Up",IF((E4-F4)/F4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>Sharmilan</t>
         </is>
@@ -887,74 +918,79 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="E5" s="4" t="n">
         <v>261.26</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>198</v>
       </c>
-      <c r="F5" s="4">
-        <f>D5-E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="5">
-        <f>IF(E5=0,"",(D5-E5)/E5)</f>
-        <v/>
-      </c>
-      <c r="H5" s="4" t="n">
+      <c r="G5" s="4">
+        <f>E5-F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="5">
+        <f>IF(F5=0,"",(E5-F5)/F5)</f>
+        <v/>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>259.76</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="K5" s="5">
-        <f>IF(J5=0,"",(I5-J5)/J5)</f>
-        <v/>
-      </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="5">
+        <f>IF(K5=0,"",(J5-K5)/K5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="M5" s="6" t="n">
+      <c r="N5" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="N5" s="4">
-        <f>IF(I5=0,"",D5/I5)</f>
-        <v/>
-      </c>
-      <c r="O5" s="6" t="n">
+      <c r="O5" s="4">
+        <f>IF(J5=0,"",E5/J5)</f>
+        <v/>
+      </c>
+      <c r="P5" s="6" t="n">
         <v>1150</v>
       </c>
-      <c r="P5" s="6" t="n">
+      <c r="Q5" s="6" t="n">
         <v>693</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="R5" s="4" t="n">
         <v>201.28</v>
       </c>
-      <c r="R5" s="2">
-        <f>IF(AND('Engine Inputs'!D5=0,Q5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((Q5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((Q5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S5" s="6" t="n">
+      <c r="S5" s="2">
+        <f>IF(AND('Engine Inputs'!E5=0,R5=0),"",IF('Engine Inputs'!E5=0,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&gt;Config!$B$2,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T5" s="6" t="n">
         <v>457</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="U5" s="4" t="n">
         <v>70.20999999999999</v>
       </c>
-      <c r="U5" s="2">
-        <f>IF(AND('Engine Inputs'!C5=0,T5=0),"",IF('Engine Inputs'!C5=0,"📈 Up",IF((T5-'Engine Inputs'!C5)/'Engine Inputs'!C5&gt;Config!$B$2,"📈 Up",IF((T5-'Engine Inputs'!C5)/'Engine Inputs'!C5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
       <c r="V5" s="2">
-        <f>IF(AND(E5=0,D5=0),"",IF(E5=0,"📈 Up",IF((D5-E5)/E5&gt;Config!$B$2,"📈 Up",IF((D5-E5)/E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D5=0,U5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W5" s="2">
+        <f>IF(AND(F5=0,E5=0),"",IF(F5=0,"📈 Up",IF((E5-F5)/F5&gt;Config!$B$2,"📈 Up",IF((E5-F5)/F5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>Powsteena</t>
         </is>
@@ -971,74 +1007,79 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="E6" s="7" t="n">
         <v>149.5</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F6" s="7" t="n">
         <v>241.79</v>
       </c>
-      <c r="F6" s="4">
-        <f>D6-E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="5">
-        <f>IF(E6=0,"",(D6-E6)/E6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="4" t="n">
+      <c r="G6" s="7">
+        <f>E6-F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="5">
+        <f>IF(F6=0,"",(E6-F6)/F6)</f>
+        <v/>
+      </c>
+      <c r="I6" s="7" t="n">
         <v>212.66</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="K6" s="5">
-        <f>IF(J6=0,"",(I6-J6)/J6)</f>
-        <v/>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>11</v>
+      <c r="L6" s="5">
+        <f>IF(K6=0,"",(J6-K6)/K6)</f>
+        <v/>
       </c>
       <c r="M6" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="4">
-        <f>IF(I6=0,"",D6/I6)</f>
-        <v/>
-      </c>
-      <c r="O6" s="6" t="n">
+      <c r="N6" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="O6" s="7">
+        <f>IF(J6=0,"",E6/J6)</f>
+        <v/>
+      </c>
+      <c r="P6" s="6" t="n">
         <v>634</v>
       </c>
-      <c r="P6" s="6" t="n">
+      <c r="Q6" s="6" t="n">
         <v>552</v>
       </c>
-      <c r="Q6" s="4" t="n">
+      <c r="R6" s="7" t="n">
         <v>133.07</v>
       </c>
-      <c r="R6" s="2">
-        <f>IF(AND('Engine Inputs'!D6=0,Q6=0),"",IF('Engine Inputs'!D6=0,"📈 Up",IF((Q6-'Engine Inputs'!D6)/'Engine Inputs'!D6&gt;Config!$B$2,"📈 Up",IF((Q6-'Engine Inputs'!D6)/'Engine Inputs'!D6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S6" s="6" t="n">
+      <c r="S6" s="2">
+        <f>IF(AND('Engine Inputs'!E6=0,R6=0),"",IF('Engine Inputs'!E6=0,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&gt;Config!$B$2,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T6" s="6" t="n">
         <v>82</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="U6" s="7" t="n">
         <v>7.19</v>
       </c>
-      <c r="U6" s="2">
-        <f>IF(AND('Engine Inputs'!C6=0,T6=0),"",IF('Engine Inputs'!C6=0,"📈 Up",IF((T6-'Engine Inputs'!C6)/'Engine Inputs'!C6&gt;Config!$B$2,"📈 Up",IF((T6-'Engine Inputs'!C6)/'Engine Inputs'!C6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
       <c r="V6" s="2">
-        <f>IF(AND(E6=0,D6=0),"",IF(E6=0,"📈 Up",IF((D6-E6)/E6&gt;Config!$B$2,"📈 Up",IF((D6-E6)/E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D6=0,U6=0),"",IF('Engine Inputs'!D6=0,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&gt;Config!$B$2,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W6" s="2">
+        <f>IF(AND(F6=0,E6=0),"",IF(F6=0,"📈 Up",IF((E6-F6)/F6&gt;Config!$B$2,"📈 Up",IF((E6-F6)/F6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>Jarsini</t>
         </is>
@@ -1055,74 +1096,79 @@
           <t>Ireland</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="7" t="n">
         <v>5.81</v>
       </c>
-      <c r="F7" s="4">
-        <f>D7-E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
-        <f>IF(E7=0,"",(D7-E7)/E7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6" t="n">
+      <c r="G7" s="7">
+        <f>E7-F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="5">
+        <f>IF(F7=0,"",(E7-F7)/F7)</f>
+        <v/>
+      </c>
+      <c r="I7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K7" s="5">
-        <f>IF(J7=0,"",(I7-J7)/J7)</f>
-        <v/>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0</v>
+      <c r="L7" s="5">
+        <f>IF(K7=0,"",(J7-K7)/K7)</f>
+        <v/>
       </c>
       <c r="M7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="4">
-        <f>IF(I7=0,"",D7/I7)</f>
-        <v/>
-      </c>
-      <c r="O7" s="6" t="n">
-        <v>622</v>
+      <c r="N7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="7">
+        <f>IF(J7=0,"",E7/J7)</f>
+        <v/>
       </c>
       <c r="P7" s="6" t="n">
         <v>622</v>
       </c>
-      <c r="Q7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2">
-        <f>IF(AND('Engine Inputs'!D7=0,Q7=0),"",IF('Engine Inputs'!D7=0,"📈 Up",IF((Q7-'Engine Inputs'!D7)/'Engine Inputs'!D7&gt;Config!$B$2,"📈 Up",IF((Q7-'Engine Inputs'!D7)/'Engine Inputs'!D7&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="2">
-        <f>IF(AND('Engine Inputs'!C7=0,T7=0),"",IF('Engine Inputs'!C7=0,"📈 Up",IF((T7-'Engine Inputs'!C7)/'Engine Inputs'!C7&gt;Config!$B$2,"📈 Up",IF((T7-'Engine Inputs'!C7)/'Engine Inputs'!C7&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q7" s="6" t="n">
+        <v>622</v>
+      </c>
+      <c r="R7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
+        <f>IF(AND('Engine Inputs'!E7=0,R7=0),"",IF('Engine Inputs'!E7=0,"📈 Up",IF((R7-'Engine Inputs'!E7)/'Engine Inputs'!E7&gt;Config!$B$2,"📈 Up",IF((R7-'Engine Inputs'!E7)/'Engine Inputs'!E7&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V7" s="2">
-        <f>IF(AND(E7=0,D7=0),"",IF(E7=0,"📈 Up",IF((D7-E7)/E7&gt;Config!$B$2,"📈 Up",IF((D7-E7)/E7&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D7=0,U7=0),"",IF('Engine Inputs'!D7=0,"📈 Up",IF((U7-'Engine Inputs'!D7)/'Engine Inputs'!D7&gt;Config!$B$2,"📈 Up",IF((U7-'Engine Inputs'!D7)/'Engine Inputs'!D7&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W7" s="2">
+        <f>IF(AND(F7=0,E7=0),"",IF(F7=0,"📈 Up",IF((E7-F7)/F7&gt;Config!$B$2,"📈 Up",IF((E7-F7)/F7&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>Sharmilan</t>
         </is>
@@ -1139,74 +1185,79 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="4">
-        <f>D8-E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="5">
-        <f>IF(E8=0,"",(D8-E8)/E8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="n">
+      <c r="E8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7">
+        <f>E8-F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="5">
+        <f>IF(F8=0,"",(E8-F8)/F8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="5">
-        <f>IF(J8=0,"",(I8-J8)/J8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>0</v>
+      <c r="K8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <f>IF(K8=0,"",(J8-K8)/K8)</f>
+        <v/>
       </c>
       <c r="M8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="4">
-        <f>IF(I8=0,"",D8/I8)</f>
-        <v/>
-      </c>
-      <c r="O8" s="6" t="n">
-        <v>592</v>
+      <c r="N8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <f>IF(J8=0,"",E8/J8)</f>
+        <v/>
       </c>
       <c r="P8" s="6" t="n">
         <v>592</v>
       </c>
-      <c r="Q8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2">
-        <f>IF(AND('Engine Inputs'!D8=0,Q8=0),"",IF('Engine Inputs'!D8=0,"📈 Up",IF((Q8-'Engine Inputs'!D8)/'Engine Inputs'!D8&gt;Config!$B$2,"📈 Up",IF((Q8-'Engine Inputs'!D8)/'Engine Inputs'!D8&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="2">
-        <f>IF(AND('Engine Inputs'!C8=0,T8=0),"",IF('Engine Inputs'!C8=0,"📈 Up",IF((T8-'Engine Inputs'!C8)/'Engine Inputs'!C8&gt;Config!$B$2,"📈 Up",IF((T8-'Engine Inputs'!C8)/'Engine Inputs'!C8&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q8" s="6" t="n">
+        <v>592</v>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
+        <f>IF(AND('Engine Inputs'!E8=0,R8=0),"",IF('Engine Inputs'!E8=0,"📈 Up",IF((R8-'Engine Inputs'!E8)/'Engine Inputs'!E8&gt;Config!$B$2,"📈 Up",IF((R8-'Engine Inputs'!E8)/'Engine Inputs'!E8&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T8" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V8" s="2">
-        <f>IF(AND(E8=0,D8=0),"",IF(E8=0,"📈 Up",IF((D8-E8)/E8&gt;Config!$B$2,"📈 Up",IF((D8-E8)/E8&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D8=0,U8=0),"",IF('Engine Inputs'!D8=0,"📈 Up",IF((U8-'Engine Inputs'!D8)/'Engine Inputs'!D8&gt;Config!$B$2,"📈 Up",IF((U8-'Engine Inputs'!D8)/'Engine Inputs'!D8&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W8" s="2">
+        <f>IF(AND(F8=0,E8=0),"",IF(F8=0,"📈 Up",IF((E8-F8)/F8&gt;Config!$B$2,"📈 Up",IF((E8-F8)/F8&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>Sharmilan</t>
         </is>
@@ -1223,74 +1274,79 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="E9" s="7" t="n">
         <v>397.19</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="F9" s="7" t="n">
         <v>256.76</v>
       </c>
-      <c r="F9" s="4">
-        <f>D9-E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="5">
-        <f>IF(E9=0,"",(D9-E9)/E9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="4" t="n">
+      <c r="G9" s="7">
+        <f>E9-F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="5">
+        <f>IF(F9=0,"",(E9-F9)/F9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="7" t="n">
         <v>394.9</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="J9" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="K9" s="5">
-        <f>IF(J9=0,"",(I9-J9)/J9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="6" t="n">
+      <c r="L9" s="5">
+        <f>IF(K9=0,"",(J9-K9)/K9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="M9" s="6" t="n">
+      <c r="N9" s="6" t="n">
         <v>22</v>
       </c>
-      <c r="N9" s="4">
-        <f>IF(I9=0,"",D9/I9)</f>
-        <v/>
-      </c>
-      <c r="O9" s="6" t="n">
+      <c r="O9" s="7">
+        <f>IF(J9=0,"",E9/J9)</f>
+        <v/>
+      </c>
+      <c r="P9" s="6" t="n">
         <v>541</v>
       </c>
-      <c r="P9" s="6" t="n">
+      <c r="Q9" s="6" t="n">
         <v>449</v>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="R9" s="7" t="n">
         <v>379.38</v>
       </c>
-      <c r="R9" s="2">
-        <f>IF(AND('Engine Inputs'!D9=0,Q9=0),"",IF('Engine Inputs'!D9=0,"📈 Up",IF((Q9-'Engine Inputs'!D9)/'Engine Inputs'!D9&gt;Config!$B$2,"📈 Up",IF((Q9-'Engine Inputs'!D9)/'Engine Inputs'!D9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S9" s="6" t="n">
+      <c r="S9" s="2">
+        <f>IF(AND('Engine Inputs'!E9=0,R9=0),"",IF('Engine Inputs'!E9=0,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&gt;Config!$B$2,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T9" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="U9" s="7" t="n">
         <v>33.38</v>
       </c>
-      <c r="U9" s="2">
-        <f>IF(AND('Engine Inputs'!C9=0,T9=0),"",IF('Engine Inputs'!C9=0,"📈 Up",IF((T9-'Engine Inputs'!C9)/'Engine Inputs'!C9&gt;Config!$B$2,"📈 Up",IF((T9-'Engine Inputs'!C9)/'Engine Inputs'!C9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
       <c r="V9" s="2">
-        <f>IF(AND(E9=0,D9=0),"",IF(E9=0,"📈 Up",IF((D9-E9)/E9&gt;Config!$B$2,"📈 Up",IF((D9-E9)/E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D9=0,U9=0),"",IF('Engine Inputs'!D9=0,"📈 Up",IF((U9-'Engine Inputs'!D9)/'Engine Inputs'!D9&gt;Config!$B$2,"📈 Up",IF((U9-'Engine Inputs'!D9)/'Engine Inputs'!D9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W9" s="2">
+        <f>IF(AND(F9=0,E9=0),"",IF(F9=0,"📈 Up",IF((E9-F9)/F9&gt;Config!$B$2,"📈 Up",IF((E9-F9)/F9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>Jarsini</t>
         </is>
@@ -1307,74 +1363,79 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>202.68</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="F10" s="4" t="n">
         <v>280.92</v>
       </c>
-      <c r="F10" s="4">
-        <f>D10-E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
-        <f>IF(E10=0,"",(D10-E10)/E10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="4" t="n">
+      <c r="G10" s="4">
+        <f>E10-F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="5">
+        <f>IF(F10=0,"",(E10-F10)/F10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>113.61</v>
       </c>
-      <c r="I10" s="6" t="n">
+      <c r="J10" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="K10" s="5">
-        <f>IF(J10=0,"",(I10-J10)/J10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="6" t="n">
+      <c r="L10" s="5">
+        <f>IF(K10=0,"",(J10-K10)/K10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="M10" s="6" t="n">
+      <c r="N10" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="N10" s="4">
-        <f>IF(I10=0,"",D10/I10)</f>
-        <v/>
-      </c>
-      <c r="O10" s="6" t="n">
-        <v>537</v>
+      <c r="O10" s="4">
+        <f>IF(J10=0,"",E10/J10)</f>
+        <v/>
       </c>
       <c r="P10" s="6" t="n">
         <v>537</v>
       </c>
-      <c r="Q10" s="4" t="n">
+      <c r="Q10" s="6" t="n">
+        <v>537</v>
+      </c>
+      <c r="R10" s="4" t="n">
         <v>202.68</v>
       </c>
-      <c r="R10" s="2">
-        <f>IF(AND('Engine Inputs'!D10=0,Q10=0),"",IF('Engine Inputs'!D10=0,"📈 Up",IF((Q10-'Engine Inputs'!D10)/'Engine Inputs'!D10&gt;Config!$B$2,"📈 Up",IF((Q10-'Engine Inputs'!D10)/'Engine Inputs'!D10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="2">
-        <f>IF(AND('Engine Inputs'!C10=0,T10=0),"",IF('Engine Inputs'!C10=0,"📈 Up",IF((T10-'Engine Inputs'!C10)/'Engine Inputs'!C10&gt;Config!$B$2,"📈 Up",IF((T10-'Engine Inputs'!C10)/'Engine Inputs'!C10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="S10" s="2">
+        <f>IF(AND('Engine Inputs'!E10=0,R10=0),"",IF('Engine Inputs'!E10=0,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&gt;Config!$B$2,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T10" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V10" s="2">
-        <f>IF(AND(E10=0,D10=0),"",IF(E10=0,"📈 Up",IF((D10-E10)/E10&gt;Config!$B$2,"📈 Up",IF((D10-E10)/E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D10=0,U10=0),"",IF('Engine Inputs'!D10=0,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&gt;Config!$B$2,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W10" s="2">
+        <f>IF(AND(F10=0,E10=0),"",IF(F10=0,"📈 Up",IF((E10-F10)/F10&gt;Config!$B$2,"📈 Up",IF((E10-F10)/F10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>Genga</t>
         </is>
@@ -1391,74 +1452,79 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="E11" s="7" t="n">
         <v>45.48</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="F11" s="7" t="n">
         <v>159.54</v>
       </c>
-      <c r="F11" s="4">
-        <f>D11-E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="5">
-        <f>IF(E11=0,"",(D11-E11)/E11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="4" t="n">
+      <c r="G11" s="7">
+        <f>E11-F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="5">
+        <f>IF(F11=0,"",(E11-F11)/F11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="7" t="n">
         <v>105.46</v>
       </c>
-      <c r="I11" s="6" t="n">
+      <c r="J11" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="K11" s="5">
-        <f>IF(J11=0,"",(I11-J11)/J11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="6" t="n">
+      <c r="L11" s="5">
+        <f>IF(K11=0,"",(J11-K11)/K11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="N11" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="N11" s="4">
-        <f>IF(I11=0,"",D11/I11)</f>
-        <v/>
-      </c>
-      <c r="O11" s="6" t="n">
+      <c r="O11" s="7">
+        <f>IF(J11=0,"",E11/J11)</f>
+        <v/>
+      </c>
+      <c r="P11" s="6" t="n">
         <v>486</v>
       </c>
-      <c r="P11" s="6" t="n">
+      <c r="Q11" s="6" t="n">
         <v>450</v>
       </c>
-      <c r="Q11" s="4" t="n">
+      <c r="R11" s="7" t="n">
         <v>26.57</v>
       </c>
-      <c r="R11" s="2">
-        <f>IF(AND('Engine Inputs'!D11=0,Q11=0),"",IF('Engine Inputs'!D11=0,"📈 Up",IF((Q11-'Engine Inputs'!D11)/'Engine Inputs'!D11&gt;Config!$B$2,"📈 Up",IF((Q11-'Engine Inputs'!D11)/'Engine Inputs'!D11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S11" s="6" t="n">
+      <c r="S11" s="2">
+        <f>IF(AND('Engine Inputs'!E11=0,R11=0),"",IF('Engine Inputs'!E11=0,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&gt;Config!$B$2,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T11" s="6" t="n">
         <v>36</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="U11" s="7" t="n">
         <v>6.7</v>
       </c>
-      <c r="U11" s="2">
-        <f>IF(AND('Engine Inputs'!C11=0,T11=0),"",IF('Engine Inputs'!C11=0,"📈 Up",IF((T11-'Engine Inputs'!C11)/'Engine Inputs'!C11&gt;Config!$B$2,"📈 Up",IF((T11-'Engine Inputs'!C11)/'Engine Inputs'!C11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
       <c r="V11" s="2">
-        <f>IF(AND(E11=0,D11=0),"",IF(E11=0,"📈 Up",IF((D11-E11)/E11&gt;Config!$B$2,"📈 Up",IF((D11-E11)/E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D11=0,U11=0),"",IF('Engine Inputs'!D11=0,"📈 Up",IF((U11-'Engine Inputs'!D11)/'Engine Inputs'!D11&gt;Config!$B$2,"📈 Up",IF((U11-'Engine Inputs'!D11)/'Engine Inputs'!D11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W11" s="2">
+        <f>IF(AND(F11=0,E11=0),"",IF(F11=0,"📈 Up",IF((E11-F11)/F11&gt;Config!$B$2,"📈 Up",IF((E11-F11)/F11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>Kobiga</t>
         </is>
@@ -1475,74 +1541,79 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="E12" s="4" t="n">
         <v>157.59</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="F12" s="4" t="n">
         <v>75.78</v>
       </c>
-      <c r="F12" s="4">
-        <f>D12-E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="5">
-        <f>IF(E12=0,"",(D12-E12)/E12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="4" t="n">
+      <c r="G12" s="4">
+        <f>E12-F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="5">
+        <f>IF(F12=0,"",(E12-F12)/F12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>82.87</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>8</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="K12" s="5">
-        <f>IF(J12=0,"",(I12-J12)/J12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="6" t="n">
+      <c r="K12" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L12" s="5">
+        <f>IF(K12=0,"",(J12-K12)/K12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="N12" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="N12" s="4">
-        <f>IF(I12=0,"",D12/I12)</f>
-        <v/>
-      </c>
-      <c r="O12" s="6" t="n">
-        <v>474</v>
+      <c r="O12" s="4">
+        <f>IF(J12=0,"",E12/J12)</f>
+        <v/>
       </c>
       <c r="P12" s="6" t="n">
         <v>474</v>
       </c>
-      <c r="Q12" s="4" t="n">
+      <c r="Q12" s="6" t="n">
+        <v>474</v>
+      </c>
+      <c r="R12" s="4" t="n">
         <v>166.07</v>
       </c>
-      <c r="R12" s="2">
-        <f>IF(AND('Engine Inputs'!D12=0,Q12=0),"",IF('Engine Inputs'!D12=0,"📈 Up",IF((Q12-'Engine Inputs'!D12)/'Engine Inputs'!D12&gt;Config!$B$2,"📈 Up",IF((Q12-'Engine Inputs'!D12)/'Engine Inputs'!D12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="2">
-        <f>IF(AND('Engine Inputs'!C12=0,T12=0),"",IF('Engine Inputs'!C12=0,"📈 Up",IF((T12-'Engine Inputs'!C12)/'Engine Inputs'!C12&gt;Config!$B$2,"📈 Up",IF((T12-'Engine Inputs'!C12)/'Engine Inputs'!C12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="S12" s="2">
+        <f>IF(AND('Engine Inputs'!E12=0,R12=0),"",IF('Engine Inputs'!E12=0,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&gt;Config!$B$2,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V12" s="2">
-        <f>IF(AND(E12=0,D12=0),"",IF(E12=0,"📈 Up",IF((D12-E12)/E12&gt;Config!$B$2,"📈 Up",IF((D12-E12)/E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W12" s="7" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D12=0,U12=0),"",IF('Engine Inputs'!D12=0,"📈 Up",IF((U12-'Engine Inputs'!D12)/'Engine Inputs'!D12&gt;Config!$B$2,"📈 Up",IF((U12-'Engine Inputs'!D12)/'Engine Inputs'!D12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W12" s="2">
+        <f>IF(AND(F12=0,E12=0),"",IF(F12=0,"📈 Up",IF((E12-F12)/F12&gt;Config!$B$2,"📈 Up",IF((E12-F12)/F12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X12" s="8" t="inlineStr">
         <is>
           <t>— not assigned</t>
         </is>
@@ -1559,74 +1630,79 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>41.99</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>57.7</v>
       </c>
-      <c r="F13" s="4">
-        <f>D13-E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="5">
-        <f>IF(E13=0,"",(D13-E13)/E13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="4" t="n">
+      <c r="G13" s="4">
+        <f>E13-F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="5">
+        <f>IF(F13=0,"",(E13-F13)/F13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>27.34</v>
       </c>
-      <c r="I13" s="6" t="n">
+      <c r="J13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="K13" s="5">
-        <f>IF(J13=0,"",(I13-J13)/J13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="6" t="n">
+      <c r="L13" s="5">
+        <f>IF(K13=0,"",(J13-K13)/K13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="M13" s="6" t="n">
+      <c r="N13" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="N13" s="4">
-        <f>IF(I13=0,"",D13/I13)</f>
-        <v/>
-      </c>
-      <c r="O13" s="6" t="n">
-        <v>468</v>
+      <c r="O13" s="4">
+        <f>IF(J13=0,"",E13/J13)</f>
+        <v/>
       </c>
       <c r="P13" s="6" t="n">
         <v>468</v>
       </c>
-      <c r="Q13" s="4" t="n">
+      <c r="Q13" s="6" t="n">
+        <v>468</v>
+      </c>
+      <c r="R13" s="4" t="n">
         <v>45.43</v>
       </c>
-      <c r="R13" s="2">
-        <f>IF(AND('Engine Inputs'!D13=0,Q13=0),"",IF('Engine Inputs'!D13=0,"📈 Up",IF((Q13-'Engine Inputs'!D13)/'Engine Inputs'!D13&gt;Config!$B$2,"📈 Up",IF((Q13-'Engine Inputs'!D13)/'Engine Inputs'!D13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2">
-        <f>IF(AND('Engine Inputs'!C13=0,T13=0),"",IF('Engine Inputs'!C13=0,"📈 Up",IF((T13-'Engine Inputs'!C13)/'Engine Inputs'!C13&gt;Config!$B$2,"📈 Up",IF((T13-'Engine Inputs'!C13)/'Engine Inputs'!C13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="S13" s="2">
+        <f>IF(AND('Engine Inputs'!E13=0,R13=0),"",IF('Engine Inputs'!E13=0,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&gt;Config!$B$2,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V13" s="2">
-        <f>IF(AND(E13=0,D13=0),"",IF(E13=0,"📈 Up",IF((D13-E13)/E13&gt;Config!$B$2,"📈 Up",IF((D13-E13)/E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W13" s="7" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D13=0,U13=0),"",IF('Engine Inputs'!D13=0,"📈 Up",IF((U13-'Engine Inputs'!D13)/'Engine Inputs'!D13&gt;Config!$B$2,"📈 Up",IF((U13-'Engine Inputs'!D13)/'Engine Inputs'!D13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W13" s="2">
+        <f>IF(AND(F13=0,E13=0),"",IF(F13=0,"📈 Up",IF((E13-F13)/F13&gt;Config!$B$2,"📈 Up",IF((E13-F13)/F13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
         <is>
           <t>— not assigned</t>
         </is>
@@ -1643,74 +1719,79 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>65.78</v>
       </c>
-      <c r="F14" s="4">
-        <f>D14-E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="5">
-        <f>IF(E14=0,"",(D14-E14)/E14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="n">
+      <c r="G14" s="4">
+        <f>E14-F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="5">
+        <f>IF(F14=0,"",(E14-F14)/F14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>314.72</v>
       </c>
-      <c r="I14" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="K14" s="5">
-        <f>IF(J14=0,"",(I14-J14)/J14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="6" t="n">
+      <c r="L14" s="5">
+        <f>IF(K14=0,"",(J14-K14)/K14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="M14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="4">
-        <f>IF(I14=0,"",D14/I14)</f>
-        <v/>
-      </c>
-      <c r="O14" s="6" t="n">
-        <v>403</v>
+      <c r="N14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4">
+        <f>IF(J14=0,"",E14/J14)</f>
+        <v/>
       </c>
       <c r="P14" s="6" t="n">
         <v>403</v>
       </c>
-      <c r="Q14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="2">
-        <f>IF(AND('Engine Inputs'!D14=0,Q14=0),"",IF('Engine Inputs'!D14=0,"📈 Up",IF((Q14-'Engine Inputs'!D14)/'Engine Inputs'!D14&gt;Config!$B$2,"📈 Up",IF((Q14-'Engine Inputs'!D14)/'Engine Inputs'!D14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2">
-        <f>IF(AND('Engine Inputs'!C14=0,T14=0),"",IF('Engine Inputs'!C14=0,"📈 Up",IF((T14-'Engine Inputs'!C14)/'Engine Inputs'!C14&gt;Config!$B$2,"📈 Up",IF((T14-'Engine Inputs'!C14)/'Engine Inputs'!C14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q14" s="6" t="n">
+        <v>403</v>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="2">
+        <f>IF(AND('Engine Inputs'!E14=0,R14=0),"",IF('Engine Inputs'!E14=0,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&gt;Config!$B$2,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V14" s="2">
-        <f>IF(AND(E14=0,D14=0),"",IF(E14=0,"📈 Up",IF((D14-E14)/E14&gt;Config!$B$2,"📈 Up",IF((D14-E14)/E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W14" s="7" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D14=0,U14=0),"",IF('Engine Inputs'!D14=0,"📈 Up",IF((U14-'Engine Inputs'!D14)/'Engine Inputs'!D14&gt;Config!$B$2,"📈 Up",IF((U14-'Engine Inputs'!D14)/'Engine Inputs'!D14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W14" s="2">
+        <f>IF(AND(F14=0,E14=0),"",IF(F14=0,"📈 Up",IF((E14-F14)/F14&gt;Config!$B$2,"📈 Up",IF((E14-F14)/F14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
         <is>
           <t>— not assigned</t>
         </is>
@@ -1727,74 +1808,79 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
-        <f>D15-E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="5">
-        <f>IF(E15=0,"",(D15-E15)/E15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6" t="n">
+      <c r="E15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <f>E15-F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="5">
+        <f>IF(F15=0,"",(E15-F15)/F15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="5">
-        <f>IF(J15=0,"",(I15-J15)/J15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="6" t="n">
-        <v>0</v>
+      <c r="K15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5">
+        <f>IF(K15=0,"",(J15-K15)/K15)</f>
+        <v/>
       </c>
       <c r="M15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N15" s="4">
-        <f>IF(I15=0,"",D15/I15)</f>
-        <v/>
-      </c>
-      <c r="O15" s="6" t="n">
+      <c r="N15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="9">
+        <f>IF(J15=0,"",E15/J15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="6" t="n">
         <v>391</v>
       </c>
-      <c r="P15" s="6" t="n">
+      <c r="Q15" s="6" t="n">
         <v>353</v>
       </c>
-      <c r="Q15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="2">
-        <f>IF(AND('Engine Inputs'!D15=0,Q15=0),"",IF('Engine Inputs'!D15=0,"📈 Up",IF((Q15-'Engine Inputs'!D15)/'Engine Inputs'!D15&gt;Config!$B$2,"📈 Up",IF((Q15-'Engine Inputs'!D15)/'Engine Inputs'!D15&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S15" s="6" t="n">
+      <c r="R15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="2">
+        <f>IF(AND('Engine Inputs'!E15=0,R15=0),"",IF('Engine Inputs'!E15=0,"📈 Up",IF((R15-'Engine Inputs'!E15)/'Engine Inputs'!E15&gt;Config!$B$2,"📈 Up",IF((R15-'Engine Inputs'!E15)/'Engine Inputs'!E15&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T15" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="T15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="2">
-        <f>IF(AND('Engine Inputs'!C15=0,T15=0),"",IF('Engine Inputs'!C15=0,"📈 Up",IF((T15-'Engine Inputs'!C15)/'Engine Inputs'!C15&gt;Config!$B$2,"📈 Up",IF((T15-'Engine Inputs'!C15)/'Engine Inputs'!C15&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="U15" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V15" s="2">
-        <f>IF(AND(E15=0,D15=0),"",IF(E15=0,"📈 Up",IF((D15-E15)/E15&gt;Config!$B$2,"📈 Up",IF((D15-E15)/E15&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D15=0,U15=0),"",IF('Engine Inputs'!D15=0,"📈 Up",IF((U15-'Engine Inputs'!D15)/'Engine Inputs'!D15&gt;Config!$B$2,"📈 Up",IF((U15-'Engine Inputs'!D15)/'Engine Inputs'!D15&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W15" s="2">
+        <f>IF(AND(F15=0,E15=0),"",IF(F15=0,"📈 Up",IF((E15-F15)/F15&gt;Config!$B$2,"📈 Up",IF((E15-F15)/F15&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>Sharmilan</t>
         </is>
@@ -1811,74 +1897,79 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="4">
-        <f>D16-E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="5">
-        <f>IF(E16=0,"",(D16-E16)/E16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="6" t="n">
+      <c r="E16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <f>E16-F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="5">
+        <f>IF(F16=0,"",(E16-F16)/F16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="5">
-        <f>IF(J16=0,"",(I16-J16)/J16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="6" t="n">
-        <v>0</v>
+      <c r="K16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5">
+        <f>IF(K16=0,"",(J16-K16)/K16)</f>
+        <v/>
       </c>
       <c r="M16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N16" s="4">
-        <f>IF(I16=0,"",D16/I16)</f>
-        <v/>
-      </c>
-      <c r="O16" s="6" t="n">
+      <c r="N16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="9">
+        <f>IF(J16=0,"",E16/J16)</f>
+        <v/>
+      </c>
+      <c r="P16" s="6" t="n">
         <v>380</v>
       </c>
-      <c r="P16" s="6" t="n">
+      <c r="Q16" s="6" t="n">
         <v>377</v>
       </c>
-      <c r="Q16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="2">
-        <f>IF(AND('Engine Inputs'!D16=0,Q16=0),"",IF('Engine Inputs'!D16=0,"📈 Up",IF((Q16-'Engine Inputs'!D16)/'Engine Inputs'!D16&gt;Config!$B$2,"📈 Up",IF((Q16-'Engine Inputs'!D16)/'Engine Inputs'!D16&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S16" s="6" t="n">
+      <c r="R16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="2">
+        <f>IF(AND('Engine Inputs'!E16=0,R16=0),"",IF('Engine Inputs'!E16=0,"📈 Up",IF((R16-'Engine Inputs'!E16)/'Engine Inputs'!E16&gt;Config!$B$2,"📈 Up",IF((R16-'Engine Inputs'!E16)/'Engine Inputs'!E16&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T16" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="T16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="2">
-        <f>IF(AND('Engine Inputs'!C16=0,T16=0),"",IF('Engine Inputs'!C16=0,"📈 Up",IF((T16-'Engine Inputs'!C16)/'Engine Inputs'!C16&gt;Config!$B$2,"📈 Up",IF((T16-'Engine Inputs'!C16)/'Engine Inputs'!C16&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="U16" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V16" s="2">
-        <f>IF(AND(E16=0,D16=0),"",IF(E16=0,"📈 Up",IF((D16-E16)/E16&gt;Config!$B$2,"📈 Up",IF((D16-E16)/E16&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D16=0,U16=0),"",IF('Engine Inputs'!D16=0,"📈 Up",IF((U16-'Engine Inputs'!D16)/'Engine Inputs'!D16&gt;Config!$B$2,"📈 Up",IF((U16-'Engine Inputs'!D16)/'Engine Inputs'!D16&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W16" s="2">
+        <f>IF(AND(F16=0,E16=0),"",IF(F16=0,"📈 Up",IF((E16-F16)/F16&gt;Config!$B$2,"📈 Up",IF((E16-F16)/F16&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>Kobiga</t>
         </is>
@@ -1895,74 +1986,79 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7" t="n">
         <v>26.33</v>
       </c>
-      <c r="F17" s="4">
-        <f>D17-E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="5">
-        <f>IF(E17=0,"",(D17-E17)/E17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6" t="n">
+      <c r="G17" s="7">
+        <f>E17-F17</f>
+        <v/>
+      </c>
+      <c r="H17" s="5">
+        <f>IF(F17=0,"",(E17-F17)/F17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="5">
-        <f>IF(J17=0,"",(I17-J17)/J17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="6" t="n">
-        <v>0</v>
+      <c r="L17" s="5">
+        <f>IF(K17=0,"",(J17-K17)/K17)</f>
+        <v/>
       </c>
       <c r="M17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N17" s="4">
-        <f>IF(I17=0,"",D17/I17)</f>
-        <v/>
-      </c>
-      <c r="O17" s="6" t="n">
-        <v>368</v>
+      <c r="N17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="7">
+        <f>IF(J17=0,"",E17/J17)</f>
+        <v/>
       </c>
       <c r="P17" s="6" t="n">
         <v>368</v>
       </c>
-      <c r="Q17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" s="2">
-        <f>IF(AND('Engine Inputs'!D17=0,Q17=0),"",IF('Engine Inputs'!D17=0,"📈 Up",IF((Q17-'Engine Inputs'!D17)/'Engine Inputs'!D17&gt;Config!$B$2,"📈 Up",IF((Q17-'Engine Inputs'!D17)/'Engine Inputs'!D17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="2">
-        <f>IF(AND('Engine Inputs'!C17=0,T17=0),"",IF('Engine Inputs'!C17=0,"📈 Up",IF((T17-'Engine Inputs'!C17)/'Engine Inputs'!C17&gt;Config!$B$2,"📈 Up",IF((T17-'Engine Inputs'!C17)/'Engine Inputs'!C17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q17" s="6" t="n">
+        <v>368</v>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
+        <f>IF(AND('Engine Inputs'!E17=0,R17=0),"",IF('Engine Inputs'!E17=0,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&gt;Config!$B$2,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V17" s="2">
-        <f>IF(AND(E17=0,D17=0),"",IF(E17=0,"📈 Up",IF((D17-E17)/E17&gt;Config!$B$2,"📈 Up",IF((D17-E17)/E17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D17=0,U17=0),"",IF('Engine Inputs'!D17=0,"📈 Up",IF((U17-'Engine Inputs'!D17)/'Engine Inputs'!D17&gt;Config!$B$2,"📈 Up",IF((U17-'Engine Inputs'!D17)/'Engine Inputs'!D17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W17" s="2">
+        <f>IF(AND(F17=0,E17=0),"",IF(F17=0,"📈 Up",IF((E17-F17)/F17&gt;Config!$B$2,"📈 Up",IF((E17-F17)/F17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>Sharmilan</t>
         </is>
@@ -1979,74 +2075,79 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9" t="n">
         <v>29.62</v>
       </c>
-      <c r="F18" s="4">
-        <f>D18-E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="5">
-        <f>IF(E18=0,"",(D18-E18)/E18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="6" t="n">
+      <c r="G18" s="9">
+        <f>E18-F18</f>
+        <v/>
+      </c>
+      <c r="H18" s="5">
+        <f>IF(F18=0,"",(E18-F18)/F18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K18" s="5">
-        <f>IF(J18=0,"",(I18-J18)/J18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="6" t="n">
-        <v>0</v>
+      <c r="L18" s="5">
+        <f>IF(K18=0,"",(J18-K18)/K18)</f>
+        <v/>
       </c>
       <c r="M18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N18" s="4">
-        <f>IF(I18=0,"",D18/I18)</f>
-        <v/>
-      </c>
-      <c r="O18" s="6" t="n">
+      <c r="N18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="9">
+        <f>IF(J18=0,"",E18/J18)</f>
+        <v/>
+      </c>
+      <c r="P18" s="6" t="n">
         <v>344</v>
       </c>
-      <c r="P18" s="6" t="n">
+      <c r="Q18" s="6" t="n">
         <v>328</v>
       </c>
-      <c r="Q18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" s="2">
-        <f>IF(AND('Engine Inputs'!D18=0,Q18=0),"",IF('Engine Inputs'!D18=0,"📈 Up",IF((Q18-'Engine Inputs'!D18)/'Engine Inputs'!D18&gt;Config!$B$2,"📈 Up",IF((Q18-'Engine Inputs'!D18)/'Engine Inputs'!D18&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S18" s="6" t="n">
+      <c r="R18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="2">
+        <f>IF(AND('Engine Inputs'!E18=0,R18=0),"",IF('Engine Inputs'!E18=0,"📈 Up",IF((R18-'Engine Inputs'!E18)/'Engine Inputs'!E18&gt;Config!$B$2,"📈 Up",IF((R18-'Engine Inputs'!E18)/'Engine Inputs'!E18&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T18" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="T18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" s="2">
-        <f>IF(AND('Engine Inputs'!C18=0,T18=0),"",IF('Engine Inputs'!C18=0,"📈 Up",IF((T18-'Engine Inputs'!C18)/'Engine Inputs'!C18&gt;Config!$B$2,"📈 Up",IF((T18-'Engine Inputs'!C18)/'Engine Inputs'!C18&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="U18" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V18" s="2">
-        <f>IF(AND(E18=0,D18=0),"",IF(E18=0,"📈 Up",IF((D18-E18)/E18&gt;Config!$B$2,"📈 Up",IF((D18-E18)/E18&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W18" s="7" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D18=0,U18=0),"",IF('Engine Inputs'!D18=0,"📈 Up",IF((U18-'Engine Inputs'!D18)/'Engine Inputs'!D18&gt;Config!$B$2,"📈 Up",IF((U18-'Engine Inputs'!D18)/'Engine Inputs'!D18&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W18" s="2">
+        <f>IF(AND(F18=0,E18=0),"",IF(F18=0,"📈 Up",IF((E18-F18)/F18&gt;Config!$B$2,"📈 Up",IF((E18-F18)/F18&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
         <is>
           <t>— not assigned</t>
         </is>
@@ -2063,74 +2164,79 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="E19" s="7" t="n">
         <v>32.29</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="F19" s="7" t="n">
         <v>78.15000000000001</v>
       </c>
-      <c r="F19" s="4">
-        <f>D19-E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="5">
-        <f>IF(E19=0,"",(D19-E19)/E19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="4" t="n">
+      <c r="G19" s="7">
+        <f>E19-F19</f>
+        <v/>
+      </c>
+      <c r="H19" s="5">
+        <f>IF(F19=0,"",(E19-F19)/F19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="7" t="n">
         <v>152.48</v>
       </c>
-      <c r="I19" s="6" t="n">
+      <c r="J19" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="K19" s="5">
-        <f>IF(J19=0,"",(I19-J19)/J19)</f>
-        <v/>
-      </c>
-      <c r="L19" s="6" t="n">
+      <c r="L19" s="5">
+        <f>IF(K19=0,"",(J19-K19)/K19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="M19" s="6" t="n">
+      <c r="N19" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="N19" s="4">
-        <f>IF(I19=0,"",D19/I19)</f>
-        <v/>
-      </c>
-      <c r="O19" s="6" t="n">
-        <v>295</v>
+      <c r="O19" s="7">
+        <f>IF(J19=0,"",E19/J19)</f>
+        <v/>
       </c>
       <c r="P19" s="6" t="n">
         <v>295</v>
       </c>
-      <c r="Q19" s="4" t="n">
+      <c r="Q19" s="6" t="n">
+        <v>295</v>
+      </c>
+      <c r="R19" s="7" t="n">
         <v>28.84</v>
       </c>
-      <c r="R19" s="2">
-        <f>IF(AND('Engine Inputs'!D19=0,Q19=0),"",IF('Engine Inputs'!D19=0,"📈 Up",IF((Q19-'Engine Inputs'!D19)/'Engine Inputs'!D19&gt;Config!$B$2,"📈 Up",IF((Q19-'Engine Inputs'!D19)/'Engine Inputs'!D19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="2">
-        <f>IF(AND('Engine Inputs'!C19=0,T19=0),"",IF('Engine Inputs'!C19=0,"📈 Up",IF((T19-'Engine Inputs'!C19)/'Engine Inputs'!C19&gt;Config!$B$2,"📈 Up",IF((T19-'Engine Inputs'!C19)/'Engine Inputs'!C19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="S19" s="2">
+        <f>IF(AND('Engine Inputs'!E19=0,R19=0),"",IF('Engine Inputs'!E19=0,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&gt;Config!$B$2,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V19" s="2">
-        <f>IF(AND(E19=0,D19=0),"",IF(E19=0,"📈 Up",IF((D19-E19)/E19&gt;Config!$B$2,"📈 Up",IF((D19-E19)/E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D19=0,U19=0),"",IF('Engine Inputs'!D19=0,"📈 Up",IF((U19-'Engine Inputs'!D19)/'Engine Inputs'!D19&gt;Config!$B$2,"📈 Up",IF((U19-'Engine Inputs'!D19)/'Engine Inputs'!D19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W19" s="2">
+        <f>IF(AND(F19=0,E19=0),"",IF(F19=0,"📈 Up",IF((E19-F19)/F19&gt;Config!$B$2,"📈 Up",IF((E19-F19)/F19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>Sivajitha</t>
         </is>
@@ -2147,74 +2253,79 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D20" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
         <v>16.58</v>
       </c>
-      <c r="F20" s="4">
-        <f>D20-E20</f>
-        <v/>
-      </c>
-      <c r="G20" s="5">
-        <f>IF(E20=0,"",(D20-E20)/E20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="6" t="n">
+      <c r="G20" s="4">
+        <f>E20-F20</f>
+        <v/>
+      </c>
+      <c r="H20" s="5">
+        <f>IF(F20=0,"",(E20-F20)/F20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="K20" s="5">
-        <f>IF(J20=0,"",(I20-J20)/J20)</f>
-        <v/>
-      </c>
-      <c r="L20" s="6" t="n">
-        <v>0</v>
+      <c r="L20" s="5">
+        <f>IF(K20=0,"",(J20-K20)/K20)</f>
+        <v/>
       </c>
       <c r="M20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="4">
-        <f>IF(I20=0,"",D20/I20)</f>
-        <v/>
-      </c>
-      <c r="O20" s="6" t="n">
-        <v>247</v>
+      <c r="N20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="4">
+        <f>IF(J20=0,"",E20/J20)</f>
+        <v/>
       </c>
       <c r="P20" s="6" t="n">
         <v>247</v>
       </c>
-      <c r="Q20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="2">
-        <f>IF(AND('Engine Inputs'!D20=0,Q20=0),"",IF('Engine Inputs'!D20=0,"📈 Up",IF((Q20-'Engine Inputs'!D20)/'Engine Inputs'!D20&gt;Config!$B$2,"📈 Up",IF((Q20-'Engine Inputs'!D20)/'Engine Inputs'!D20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="2">
-        <f>IF(AND('Engine Inputs'!C20=0,T20=0),"",IF('Engine Inputs'!C20=0,"📈 Up",IF((T20-'Engine Inputs'!C20)/'Engine Inputs'!C20&gt;Config!$B$2,"📈 Up",IF((T20-'Engine Inputs'!C20)/'Engine Inputs'!C20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q20" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <f>IF(AND('Engine Inputs'!E20=0,R20=0),"",IF('Engine Inputs'!E20=0,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&gt;Config!$B$2,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V20" s="2">
-        <f>IF(AND(E20=0,D20=0),"",IF(E20=0,"📈 Up",IF((D20-E20)/E20&gt;Config!$B$2,"📈 Up",IF((D20-E20)/E20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W20" s="7" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D20=0,U20=0),"",IF('Engine Inputs'!D20=0,"📈 Up",IF((U20-'Engine Inputs'!D20)/'Engine Inputs'!D20&gt;Config!$B$2,"📈 Up",IF((U20-'Engine Inputs'!D20)/'Engine Inputs'!D20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W20" s="2">
+        <f>IF(AND(F20=0,E20=0),"",IF(F20=0,"📈 Up",IF((E20-F20)/F20&gt;Config!$B$2,"📈 Up",IF((E20-F20)/F20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
         <is>
           <t>— not assigned</t>
         </is>
@@ -2231,74 +2342,79 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="4">
-        <f>D21-E21</f>
-        <v/>
-      </c>
-      <c r="G21" s="5">
-        <f>IF(E21=0,"",(D21-E21)/E21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="n">
+      <c r="E21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="10">
+        <f>E21-F21</f>
+        <v/>
+      </c>
+      <c r="H21" s="5">
+        <f>IF(F21=0,"",(E21-F21)/F21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="5">
-        <f>IF(J21=0,"",(I21-J21)/J21)</f>
-        <v/>
-      </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
+      <c r="K21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5">
+        <f>IF(K21=0,"",(J21-K21)/K21)</f>
+        <v/>
       </c>
       <c r="M21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="4">
-        <f>IF(I21=0,"",D21/I21)</f>
-        <v/>
-      </c>
-      <c r="O21" s="6" t="n">
-        <v>184</v>
+      <c r="N21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10">
+        <f>IF(J21=0,"",E21/J21)</f>
+        <v/>
       </c>
       <c r="P21" s="6" t="n">
         <v>184</v>
       </c>
-      <c r="Q21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="2">
-        <f>IF(AND('Engine Inputs'!D21=0,Q21=0),"",IF('Engine Inputs'!D21=0,"📈 Up",IF((Q21-'Engine Inputs'!D21)/'Engine Inputs'!D21&gt;Config!$B$2,"📈 Up",IF((Q21-'Engine Inputs'!D21)/'Engine Inputs'!D21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="2">
-        <f>IF(AND('Engine Inputs'!C21=0,T21=0),"",IF('Engine Inputs'!C21=0,"📈 Up",IF((T21-'Engine Inputs'!C21)/'Engine Inputs'!C21&gt;Config!$B$2,"📈 Up",IF((T21-'Engine Inputs'!C21)/'Engine Inputs'!C21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q21" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="R21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="2">
+        <f>IF(AND('Engine Inputs'!E21=0,R21=0),"",IF('Engine Inputs'!E21=0,"📈 Up",IF((R21-'Engine Inputs'!E21)/'Engine Inputs'!E21&gt;Config!$B$2,"📈 Up",IF((R21-'Engine Inputs'!E21)/'Engine Inputs'!E21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="V21" s="2">
-        <f>IF(AND(E21=0,D21=0),"",IF(E21=0,"📈 Up",IF((D21-E21)/E21&gt;Config!$B$2,"📈 Up",IF((D21-E21)/E21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D21=0,U21=0),"",IF('Engine Inputs'!D21=0,"📈 Up",IF((U21-'Engine Inputs'!D21)/'Engine Inputs'!D21&gt;Config!$B$2,"📈 Up",IF((U21-'Engine Inputs'!D21)/'Engine Inputs'!D21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W21" s="2">
+        <f>IF(AND(F21=0,E21=0),"",IF(F21=0,"📈 Up",IF((E21-F21)/F21&gt;Config!$B$2,"📈 Up",IF((E21-F21)/F21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>Sharmilan</t>
         </is>
@@ -2315,74 +2431,79 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="4">
-        <f>D22-E22</f>
-        <v/>
-      </c>
-      <c r="G22" s="5">
-        <f>IF(E22=0,"",(D22-E22)/E22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="6" t="n">
+      <c r="E22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7">
+        <f>E22-F22</f>
+        <v/>
+      </c>
+      <c r="H22" s="5">
+        <f>IF(F22=0,"",(E22-F22)/F22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K22" s="5">
-        <f>IF(J22=0,"",(I22-J22)/J22)</f>
-        <v/>
-      </c>
-      <c r="L22" s="6" t="n">
-        <v>0</v>
+      <c r="K22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5">
+        <f>IF(K22=0,"",(J22-K22)/K22)</f>
+        <v/>
       </c>
       <c r="M22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N22" s="4">
-        <f>IF(I22=0,"",D22/I22)</f>
-        <v/>
-      </c>
-      <c r="O22" s="6" t="n">
+      <c r="N22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="7">
+        <f>IF(J22=0,"",E22/J22)</f>
+        <v/>
+      </c>
+      <c r="P22" s="6" t="n">
         <v>167</v>
       </c>
-      <c r="P22" s="6" t="n">
+      <c r="Q22" s="6" t="n">
         <v>148</v>
       </c>
-      <c r="Q22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" s="2">
-        <f>IF(AND('Engine Inputs'!D22=0,Q22=0),"",IF('Engine Inputs'!D22=0,"📈 Up",IF((Q22-'Engine Inputs'!D22)/'Engine Inputs'!D22&gt;Config!$B$2,"📈 Up",IF((Q22-'Engine Inputs'!D22)/'Engine Inputs'!D22&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S22" s="6" t="n">
+      <c r="R22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <f>IF(AND('Engine Inputs'!E22=0,R22=0),"",IF('Engine Inputs'!E22=0,"📈 Up",IF((R22-'Engine Inputs'!E22)/'Engine Inputs'!E22&gt;Config!$B$2,"📈 Up",IF((R22-'Engine Inputs'!E22)/'Engine Inputs'!E22&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T22" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="T22" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="2">
-        <f>IF(AND('Engine Inputs'!C22=0,T22=0),"",IF('Engine Inputs'!C22=0,"📈 Up",IF((T22-'Engine Inputs'!C22)/'Engine Inputs'!C22&gt;Config!$B$2,"📈 Up",IF((T22-'Engine Inputs'!C22)/'Engine Inputs'!C22&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="U22" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V22" s="2">
-        <f>IF(AND(E22=0,D22=0),"",IF(E22=0,"📈 Up",IF((D22-E22)/E22&gt;Config!$B$2,"📈 Up",IF((D22-E22)/E22&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D22=0,U22=0),"",IF('Engine Inputs'!D22=0,"📈 Up",IF((U22-'Engine Inputs'!D22)/'Engine Inputs'!D22&gt;Config!$B$2,"📈 Up",IF((U22-'Engine Inputs'!D22)/'Engine Inputs'!D22&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W22" s="2">
+        <f>IF(AND(F22=0,E22=0),"",IF(F22=0,"📈 Up",IF((E22-F22)/F22&gt;Config!$B$2,"📈 Up",IF((E22-F22)/F22&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>Kobiga</t>
         </is>
@@ -2399,74 +2520,79 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="E23" s="7" t="n">
         <v>152.91</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="F23" s="7" t="n">
         <v>28.98</v>
       </c>
-      <c r="F23" s="4">
-        <f>D23-E23</f>
-        <v/>
-      </c>
-      <c r="G23" s="5">
-        <f>IF(E23=0,"",(D23-E23)/E23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="6" t="n">
+      <c r="G23" s="7">
+        <f>E23-F23</f>
+        <v/>
+      </c>
+      <c r="H23" s="5">
+        <f>IF(F23=0,"",(E23-F23)/F23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="J23" s="6" t="n">
+      <c r="K23" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="K23" s="5">
-        <f>IF(J23=0,"",(I23-J23)/J23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
+      <c r="L23" s="5">
+        <f>IF(K23=0,"",(J23-K23)/K23)</f>
+        <v/>
       </c>
       <c r="M23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="N23" s="4">
-        <f>IF(I23=0,"",D23/I23)</f>
-        <v/>
-      </c>
-      <c r="O23" s="6" t="n">
-        <v>164</v>
+      <c r="O23" s="7">
+        <f>IF(J23=0,"",E23/J23)</f>
+        <v/>
       </c>
       <c r="P23" s="6" t="n">
         <v>164</v>
       </c>
-      <c r="Q23" s="4" t="n">
+      <c r="Q23" s="6" t="n">
+        <v>164</v>
+      </c>
+      <c r="R23" s="7" t="n">
         <v>157.69</v>
       </c>
-      <c r="R23" s="2">
-        <f>IF(AND('Engine Inputs'!D23=0,Q23=0),"",IF('Engine Inputs'!D23=0,"📈 Up",IF((Q23-'Engine Inputs'!D23)/'Engine Inputs'!D23&gt;Config!$B$2,"📈 Up",IF((Q23-'Engine Inputs'!D23)/'Engine Inputs'!D23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="2">
-        <f>IF(AND('Engine Inputs'!C23=0,T23=0),"",IF('Engine Inputs'!C23=0,"📈 Up",IF((T23-'Engine Inputs'!C23)/'Engine Inputs'!C23&gt;Config!$B$2,"📈 Up",IF((T23-'Engine Inputs'!C23)/'Engine Inputs'!C23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="S23" s="2">
+        <f>IF(AND('Engine Inputs'!E23=0,R23=0),"",IF('Engine Inputs'!E23=0,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&gt;Config!$B$2,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V23" s="2">
-        <f>IF(AND(E23=0,D23=0),"",IF(E23=0,"📈 Up",IF((D23-E23)/E23&gt;Config!$B$2,"📈 Up",IF((D23-E23)/E23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W23" s="7" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D23=0,U23=0),"",IF('Engine Inputs'!D23=0,"📈 Up",IF((U23-'Engine Inputs'!D23)/'Engine Inputs'!D23&gt;Config!$B$2,"📈 Up",IF((U23-'Engine Inputs'!D23)/'Engine Inputs'!D23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W23" s="2">
+        <f>IF(AND(F23=0,E23=0),"",IF(F23=0,"📈 Up",IF((E23-F23)/F23&gt;Config!$B$2,"📈 Up",IF((E23-F23)/F23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X23" s="8" t="inlineStr">
         <is>
           <t>— not assigned</t>
         </is>
@@ -2483,74 +2609,79 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="4">
-        <f>D24-E24</f>
-        <v/>
-      </c>
-      <c r="G24" s="5">
-        <f>IF(E24=0,"",(D24-E24)/E24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="6" t="n">
+      <c r="E24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="10">
+        <f>E24-F24</f>
+        <v/>
+      </c>
+      <c r="H24" s="5">
+        <f>IF(F24=0,"",(E24-F24)/F24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="5">
-        <f>IF(J24=0,"",(I24-J24)/J24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="6" t="n">
-        <v>0</v>
+      <c r="K24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5">
+        <f>IF(K24=0,"",(J24-K24)/K24)</f>
+        <v/>
       </c>
       <c r="M24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="4">
-        <f>IF(I24=0,"",D24/I24)</f>
-        <v/>
-      </c>
-      <c r="O24" s="6" t="n">
-        <v>154</v>
+      <c r="N24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="10">
+        <f>IF(J24=0,"",E24/J24)</f>
+        <v/>
       </c>
       <c r="P24" s="6" t="n">
         <v>154</v>
       </c>
-      <c r="Q24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="2">
-        <f>IF(AND('Engine Inputs'!D24=0,Q24=0),"",IF('Engine Inputs'!D24=0,"📈 Up",IF((Q24-'Engine Inputs'!D24)/'Engine Inputs'!D24&gt;Config!$B$2,"📈 Up",IF((Q24-'Engine Inputs'!D24)/'Engine Inputs'!D24&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="2">
-        <f>IF(AND('Engine Inputs'!C24=0,T24=0),"",IF('Engine Inputs'!C24=0,"📈 Up",IF((T24-'Engine Inputs'!C24)/'Engine Inputs'!C24&gt;Config!$B$2,"📈 Up",IF((T24-'Engine Inputs'!C24)/'Engine Inputs'!C24&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q24" s="6" t="n">
+        <v>154</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="2">
+        <f>IF(AND('Engine Inputs'!E24=0,R24=0),"",IF('Engine Inputs'!E24=0,"📈 Up",IF((R24-'Engine Inputs'!E24)/'Engine Inputs'!E24&gt;Config!$B$2,"📈 Up",IF((R24-'Engine Inputs'!E24)/'Engine Inputs'!E24&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="V24" s="2">
-        <f>IF(AND(E24=0,D24=0),"",IF(E24=0,"📈 Up",IF((D24-E24)/E24&gt;Config!$B$2,"📈 Up",IF((D24-E24)/E24&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D24=0,U24=0),"",IF('Engine Inputs'!D24=0,"📈 Up",IF((U24-'Engine Inputs'!D24)/'Engine Inputs'!D24&gt;Config!$B$2,"📈 Up",IF((U24-'Engine Inputs'!D24)/'Engine Inputs'!D24&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W24" s="2">
+        <f>IF(AND(F24=0,E24=0),"",IF(F24=0,"📈 Up",IF((E24-F24)/F24&gt;Config!$B$2,"📈 Up",IF((E24-F24)/F24&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>Kobiga</t>
         </is>
@@ -2567,74 +2698,79 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="4">
-        <f>D25-E25</f>
-        <v/>
-      </c>
-      <c r="G25" s="5">
-        <f>IF(E25=0,"",(D25-E25)/E25)</f>
-        <v/>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="6" t="n">
+      <c r="E25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7">
+        <f>E25-F25</f>
+        <v/>
+      </c>
+      <c r="H25" s="5">
+        <f>IF(F25=0,"",(E25-F25)/F25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K25" s="5">
-        <f>IF(J25=0,"",(I25-J25)/J25)</f>
-        <v/>
-      </c>
-      <c r="L25" s="6" t="n">
-        <v>0</v>
+      <c r="K25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <f>IF(K25=0,"",(J25-K25)/K25)</f>
+        <v/>
       </c>
       <c r="M25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N25" s="4">
-        <f>IF(I25=0,"",D25/I25)</f>
-        <v/>
-      </c>
-      <c r="O25" s="6" t="n">
-        <v>137</v>
+      <c r="N25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="7">
+        <f>IF(J25=0,"",E25/J25)</f>
+        <v/>
       </c>
       <c r="P25" s="6" t="n">
         <v>137</v>
       </c>
-      <c r="Q25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="2">
-        <f>IF(AND('Engine Inputs'!D25=0,Q25=0),"",IF('Engine Inputs'!D25=0,"📈 Up",IF((Q25-'Engine Inputs'!D25)/'Engine Inputs'!D25&gt;Config!$B$2,"📈 Up",IF((Q25-'Engine Inputs'!D25)/'Engine Inputs'!D25&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="2">
-        <f>IF(AND('Engine Inputs'!C25=0,T25=0),"",IF('Engine Inputs'!C25=0,"📈 Up",IF((T25-'Engine Inputs'!C25)/'Engine Inputs'!C25&gt;Config!$B$2,"📈 Up",IF((T25-'Engine Inputs'!C25)/'Engine Inputs'!C25&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q25" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="R25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2">
+        <f>IF(AND('Engine Inputs'!E25=0,R25=0),"",IF('Engine Inputs'!E25=0,"📈 Up",IF((R25-'Engine Inputs'!E25)/'Engine Inputs'!E25&gt;Config!$B$2,"📈 Up",IF((R25-'Engine Inputs'!E25)/'Engine Inputs'!E25&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T25" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V25" s="2">
-        <f>IF(AND(E25=0,D25=0),"",IF(E25=0,"📈 Up",IF((D25-E25)/E25&gt;Config!$B$2,"📈 Up",IF((D25-E25)/E25&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D25=0,U25=0),"",IF('Engine Inputs'!D25=0,"📈 Up",IF((U25-'Engine Inputs'!D25)/'Engine Inputs'!D25&gt;Config!$B$2,"📈 Up",IF((U25-'Engine Inputs'!D25)/'Engine Inputs'!D25&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W25" s="2">
+        <f>IF(AND(F25=0,E25=0),"",IF(F25=0,"📈 Up",IF((E25-F25)/F25&gt;Config!$B$2,"📈 Up",IF((E25-F25)/F25&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>Sharmilan</t>
         </is>
@@ -2651,74 +2787,79 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="4">
-        <f>D26-E26</f>
-        <v/>
-      </c>
-      <c r="G26" s="5">
-        <f>IF(E26=0,"",(D26-E26)/E26)</f>
-        <v/>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="6" t="n">
+      <c r="E26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="7">
+        <f>E26-F26</f>
+        <v/>
+      </c>
+      <c r="H26" s="5">
+        <f>IF(F26=0,"",(E26-F26)/F26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K26" s="5">
-        <f>IF(J26=0,"",(I26-J26)/J26)</f>
-        <v/>
-      </c>
-      <c r="L26" s="6" t="n">
-        <v>0</v>
+      <c r="K26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5">
+        <f>IF(K26=0,"",(J26-K26)/K26)</f>
+        <v/>
       </c>
       <c r="M26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="4">
-        <f>IF(I26=0,"",D26/I26)</f>
-        <v/>
-      </c>
-      <c r="O26" s="6" t="n">
-        <v>70</v>
+      <c r="N26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="7">
+        <f>IF(J26=0,"",E26/J26)</f>
+        <v/>
       </c>
       <c r="P26" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="Q26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="2">
-        <f>IF(AND('Engine Inputs'!D26=0,Q26=0),"",IF('Engine Inputs'!D26=0,"📈 Up",IF((Q26-'Engine Inputs'!D26)/'Engine Inputs'!D26&gt;Config!$B$2,"📈 Up",IF((Q26-'Engine Inputs'!D26)/'Engine Inputs'!D26&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="2">
-        <f>IF(AND('Engine Inputs'!C26=0,T26=0),"",IF('Engine Inputs'!C26=0,"📈 Up",IF((T26-'Engine Inputs'!C26)/'Engine Inputs'!C26&gt;Config!$B$2,"📈 Up",IF((T26-'Engine Inputs'!C26)/'Engine Inputs'!C26&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q26" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="R26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2">
+        <f>IF(AND('Engine Inputs'!E26=0,R26=0),"",IF('Engine Inputs'!E26=0,"📈 Up",IF((R26-'Engine Inputs'!E26)/'Engine Inputs'!E26&gt;Config!$B$2,"📈 Up",IF((R26-'Engine Inputs'!E26)/'Engine Inputs'!E26&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V26" s="2">
-        <f>IF(AND(E26=0,D26=0),"",IF(E26=0,"📈 Up",IF((D26-E26)/E26&gt;Config!$B$2,"📈 Up",IF((D26-E26)/E26&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W26" s="7" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D26=0,U26=0),"",IF('Engine Inputs'!D26=0,"📈 Up",IF((U26-'Engine Inputs'!D26)/'Engine Inputs'!D26&gt;Config!$B$2,"📈 Up",IF((U26-'Engine Inputs'!D26)/'Engine Inputs'!D26&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W26" s="2">
+        <f>IF(AND(F26=0,E26=0),"",IF(F26=0,"📈 Up",IF((E26-F26)/F26&gt;Config!$B$2,"📈 Up",IF((E26-F26)/F26&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X26" s="8" t="inlineStr">
         <is>
           <t>— not assigned</t>
         </is>
@@ -2735,74 +2876,79 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D27" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="4">
-        <f>D27-E27</f>
-        <v/>
-      </c>
-      <c r="G27" s="5">
-        <f>IF(E27=0,"",(D27-E27)/E27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="6" t="n">
+      <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4">
+        <f>E27-F27</f>
+        <v/>
+      </c>
+      <c r="H27" s="5">
+        <f>IF(F27=0,"",(E27-F27)/F27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K27" s="5">
-        <f>IF(J27=0,"",(I27-J27)/J27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="6" t="n">
-        <v>0</v>
+      <c r="K27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5">
+        <f>IF(K27=0,"",(J27-K27)/K27)</f>
+        <v/>
       </c>
       <c r="M27" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N27" s="4">
-        <f>IF(I27=0,"",D27/I27)</f>
-        <v/>
-      </c>
-      <c r="O27" s="6" t="n">
-        <v>65</v>
+      <c r="N27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="4">
+        <f>IF(J27=0,"",E27/J27)</f>
+        <v/>
       </c>
       <c r="P27" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="Q27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="2">
-        <f>IF(AND('Engine Inputs'!D27=0,Q27=0),"",IF('Engine Inputs'!D27=0,"📈 Up",IF((Q27-'Engine Inputs'!D27)/'Engine Inputs'!D27&gt;Config!$B$2,"📈 Up",IF((Q27-'Engine Inputs'!D27)/'Engine Inputs'!D27&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="2">
-        <f>IF(AND('Engine Inputs'!C27=0,T27=0),"",IF('Engine Inputs'!C27=0,"📈 Up",IF((T27-'Engine Inputs'!C27)/'Engine Inputs'!C27&gt;Config!$B$2,"📈 Up",IF((T27-'Engine Inputs'!C27)/'Engine Inputs'!C27&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q27" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2">
+        <f>IF(AND('Engine Inputs'!E27=0,R27=0),"",IF('Engine Inputs'!E27=0,"📈 Up",IF((R27-'Engine Inputs'!E27)/'Engine Inputs'!E27&gt;Config!$B$2,"📈 Up",IF((R27-'Engine Inputs'!E27)/'Engine Inputs'!E27&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V27" s="2">
-        <f>IF(AND(E27=0,D27=0),"",IF(E27=0,"📈 Up",IF((D27-E27)/E27&gt;Config!$B$2,"📈 Up",IF((D27-E27)/E27&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W27" s="7" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D27=0,U27=0),"",IF('Engine Inputs'!D27=0,"📈 Up",IF((U27-'Engine Inputs'!D27)/'Engine Inputs'!D27&gt;Config!$B$2,"📈 Up",IF((U27-'Engine Inputs'!D27)/'Engine Inputs'!D27&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W27" s="2">
+        <f>IF(AND(F27=0,E27=0),"",IF(F27=0,"📈 Up",IF((E27-F27)/F27&gt;Config!$B$2,"📈 Up",IF((E27-F27)/F27&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
         <is>
           <t>— not assigned</t>
         </is>
@@ -2819,74 +2965,79 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="4">
-        <f>D28-E28</f>
-        <v/>
-      </c>
-      <c r="G28" s="5">
-        <f>IF(E28=0,"",(D28-E28)/E28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="6" t="n">
+      <c r="E28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7">
+        <f>E28-F28</f>
+        <v/>
+      </c>
+      <c r="H28" s="5">
+        <f>IF(F28=0,"",(E28-F28)/F28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K28" s="5">
-        <f>IF(J28=0,"",(I28-J28)/J28)</f>
-        <v/>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>0</v>
+      <c r="K28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5">
+        <f>IF(K28=0,"",(J28-K28)/K28)</f>
+        <v/>
       </c>
       <c r="M28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N28" s="4">
-        <f>IF(I28=0,"",D28/I28)</f>
-        <v/>
-      </c>
-      <c r="O28" s="6" t="n">
-        <v>14</v>
+      <c r="N28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="7">
+        <f>IF(J28=0,"",E28/J28)</f>
+        <v/>
       </c>
       <c r="P28" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="Q28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" s="2">
-        <f>IF(AND('Engine Inputs'!D28=0,Q28=0),"",IF('Engine Inputs'!D28=0,"📈 Up",IF((Q28-'Engine Inputs'!D28)/'Engine Inputs'!D28&gt;Config!$B$2,"📈 Up",IF((Q28-'Engine Inputs'!D28)/'Engine Inputs'!D28&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" s="2">
-        <f>IF(AND('Engine Inputs'!C28=0,T28=0),"",IF('Engine Inputs'!C28=0,"📈 Up",IF((T28-'Engine Inputs'!C28)/'Engine Inputs'!C28&gt;Config!$B$2,"📈 Up",IF((T28-'Engine Inputs'!C28)/'Engine Inputs'!C28&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q28" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="R28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2">
+        <f>IF(AND('Engine Inputs'!E28=0,R28=0),"",IF('Engine Inputs'!E28=0,"📈 Up",IF((R28-'Engine Inputs'!E28)/'Engine Inputs'!E28&gt;Config!$B$2,"📈 Up",IF((R28-'Engine Inputs'!E28)/'Engine Inputs'!E28&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V28" s="2">
-        <f>IF(AND(E28=0,D28=0),"",IF(E28=0,"📈 Up",IF((D28-E28)/E28&gt;Config!$B$2,"📈 Up",IF((D28-E28)/E28&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D28=0,U28=0),"",IF('Engine Inputs'!D28=0,"📈 Up",IF((U28-'Engine Inputs'!D28)/'Engine Inputs'!D28&gt;Config!$B$2,"📈 Up",IF((U28-'Engine Inputs'!D28)/'Engine Inputs'!D28&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W28" s="2">
+        <f>IF(AND(F28=0,E28=0),"",IF(F28=0,"📈 Up",IF((E28-F28)/F28&gt;Config!$B$2,"📈 Up",IF((E28-F28)/F28&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>Sharmilan</t>
         </is>
@@ -2903,74 +3054,79 @@
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="4">
-        <f>D29-E29</f>
-        <v/>
-      </c>
-      <c r="G29" s="5">
-        <f>IF(E29=0,"",(D29-E29)/E29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6" t="n">
+      <c r="E29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="7">
+        <f>E29-F29</f>
+        <v/>
+      </c>
+      <c r="H29" s="5">
+        <f>IF(F29=0,"",(E29-F29)/F29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="5">
-        <f>IF(J29=0,"",(I29-J29)/J29)</f>
-        <v/>
-      </c>
-      <c r="L29" s="6" t="n">
-        <v>0</v>
+      <c r="K29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5">
+        <f>IF(K29=0,"",(J29-K29)/K29)</f>
+        <v/>
       </c>
       <c r="M29" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N29" s="4">
-        <f>IF(I29=0,"",D29/I29)</f>
-        <v/>
-      </c>
-      <c r="O29" s="6" t="n">
-        <v>6</v>
+      <c r="N29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="7">
+        <f>IF(J29=0,"",E29/J29)</f>
+        <v/>
       </c>
       <c r="P29" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="Q29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="2">
-        <f>IF(AND('Engine Inputs'!D29=0,Q29=0),"",IF('Engine Inputs'!D29=0,"📈 Up",IF((Q29-'Engine Inputs'!D29)/'Engine Inputs'!D29&gt;Config!$B$2,"📈 Up",IF((Q29-'Engine Inputs'!D29)/'Engine Inputs'!D29&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="2">
-        <f>IF(AND('Engine Inputs'!C29=0,T29=0),"",IF('Engine Inputs'!C29=0,"📈 Up",IF((T29-'Engine Inputs'!C29)/'Engine Inputs'!C29&gt;Config!$B$2,"📈 Up",IF((T29-'Engine Inputs'!C29)/'Engine Inputs'!C29&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q29" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="R29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2">
+        <f>IF(AND('Engine Inputs'!E29=0,R29=0),"",IF('Engine Inputs'!E29=0,"📈 Up",IF((R29-'Engine Inputs'!E29)/'Engine Inputs'!E29&gt;Config!$B$2,"📈 Up",IF((R29-'Engine Inputs'!E29)/'Engine Inputs'!E29&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V29" s="2">
-        <f>IF(AND(E29=0,D29=0),"",IF(E29=0,"📈 Up",IF((D29-E29)/E29&gt;Config!$B$2,"📈 Up",IF((D29-E29)/E29&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D29=0,U29=0),"",IF('Engine Inputs'!D29=0,"📈 Up",IF((U29-'Engine Inputs'!D29)/'Engine Inputs'!D29&gt;Config!$B$2,"📈 Up",IF((U29-'Engine Inputs'!D29)/'Engine Inputs'!D29&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W29" s="2">
+        <f>IF(AND(F29=0,E29=0),"",IF(F29=0,"📈 Up",IF((E29-F29)/F29&gt;Config!$B$2,"📈 Up",IF((E29-F29)/F29&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>Sharmilan</t>
         </is>
@@ -2987,74 +3143,79 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="4">
-        <f>D30-E30</f>
-        <v/>
-      </c>
-      <c r="G30" s="5">
-        <f>IF(E30=0,"",(D30-E30)/E30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="6" t="n">
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7">
+        <f>E30-F30</f>
+        <v/>
+      </c>
+      <c r="H30" s="5">
+        <f>IF(F30=0,"",(E30-F30)/F30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="5">
-        <f>IF(J30=0,"",(I30-J30)/J30)</f>
-        <v/>
-      </c>
-      <c r="L30" s="6" t="n">
-        <v>0</v>
+      <c r="K30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="5">
+        <f>IF(K30=0,"",(J30-K30)/K30)</f>
+        <v/>
       </c>
       <c r="M30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N30" s="4">
-        <f>IF(I30=0,"",D30/I30)</f>
-        <v/>
-      </c>
-      <c r="O30" s="6" t="n">
-        <v>2</v>
+      <c r="N30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="7">
+        <f>IF(J30=0,"",E30/J30)</f>
+        <v/>
       </c>
       <c r="P30" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="Q30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="2">
-        <f>IF(AND('Engine Inputs'!D30=0,Q30=0),"",IF('Engine Inputs'!D30=0,"📈 Up",IF((Q30-'Engine Inputs'!D30)/'Engine Inputs'!D30&gt;Config!$B$2,"📈 Up",IF((Q30-'Engine Inputs'!D30)/'Engine Inputs'!D30&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="2">
-        <f>IF(AND('Engine Inputs'!C30=0,T30=0),"",IF('Engine Inputs'!C30=0,"📈 Up",IF((T30-'Engine Inputs'!C30)/'Engine Inputs'!C30&gt;Config!$B$2,"📈 Up",IF((T30-'Engine Inputs'!C30)/'Engine Inputs'!C30&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q30" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2">
+        <f>IF(AND('Engine Inputs'!E30=0,R30=0),"",IF('Engine Inputs'!E30=0,"📈 Up",IF((R30-'Engine Inputs'!E30)/'Engine Inputs'!E30&gt;Config!$B$2,"📈 Up",IF((R30-'Engine Inputs'!E30)/'Engine Inputs'!E30&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T30" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="V30" s="2">
-        <f>IF(AND(E30=0,D30=0),"",IF(E30=0,"📈 Up",IF((D30-E30)/E30&gt;Config!$B$2,"📈 Up",IF((D30-E30)/E30&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D30=0,U30=0),"",IF('Engine Inputs'!D30=0,"📈 Up",IF((U30-'Engine Inputs'!D30)/'Engine Inputs'!D30&gt;Config!$B$2,"📈 Up",IF((U30-'Engine Inputs'!D30)/'Engine Inputs'!D30&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W30" s="2">
+        <f>IF(AND(F30=0,E30=0),"",IF(F30=0,"📈 Up",IF((E30-F30)/F30&gt;Config!$B$2,"📈 Up",IF((E30-F30)/F30&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>Jarsini</t>
         </is>
@@ -3071,81 +3232,86 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
         <v>46225</v>
       </c>
-      <c r="D31" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="E31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="4">
-        <f>D31-E31</f>
-        <v/>
-      </c>
-      <c r="G31" s="5">
-        <f>IF(E31=0,"",(D31-E31)/E31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="6" t="n">
+      <c r="F31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="4">
+        <f>E31-F31</f>
+        <v/>
+      </c>
+      <c r="H31" s="5">
+        <f>IF(F31=0,"",(E31-F31)/F31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="5">
-        <f>IF(J31=0,"",(I31-J31)/J31)</f>
-        <v/>
-      </c>
-      <c r="L31" s="6" t="n">
-        <v>0</v>
+      <c r="K31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="5">
+        <f>IF(K31=0,"",(J31-K31)/K31)</f>
+        <v/>
       </c>
       <c r="M31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="N31" s="4">
-        <f>IF(I31=0,"",D31/I31)</f>
-        <v/>
-      </c>
-      <c r="O31" s="6" t="n">
-        <v>2</v>
+      <c r="N31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="4">
+        <f>IF(J31=0,"",E31/J31)</f>
+        <v/>
       </c>
       <c r="P31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="Q31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="2">
-        <f>IF(AND('Engine Inputs'!D31=0,Q31=0),"",IF('Engine Inputs'!D31=0,"📈 Up",IF((Q31-'Engine Inputs'!D31)/'Engine Inputs'!D31&gt;Config!$B$2,"📈 Up",IF((Q31-'Engine Inputs'!D31)/'Engine Inputs'!D31&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="S31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="2">
-        <f>IF(AND('Engine Inputs'!C31=0,T31=0),"",IF('Engine Inputs'!C31=0,"📈 Up",IF((T31-'Engine Inputs'!C31)/'Engine Inputs'!C31&gt;Config!$B$2,"📈 Up",IF((T31-'Engine Inputs'!C31)/'Engine Inputs'!C31&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
+      <c r="Q31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2">
+        <f>IF(AND('Engine Inputs'!E31=0,R31=0),"",IF('Engine Inputs'!E31=0,"📈 Up",IF((R31-'Engine Inputs'!E31)/'Engine Inputs'!E31&gt;Config!$B$2,"📈 Up",IF((R31-'Engine Inputs'!E31)/'Engine Inputs'!E31&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V31" s="2">
-        <f>IF(AND(E31=0,D31=0),"",IF(E31=0,"📈 Up",IF((D31-E31)/E31&gt;Config!$B$2,"📈 Up",IF((D31-E31)/E31&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
-        <v/>
-      </c>
-      <c r="W31" s="2" t="inlineStr">
+        <f>IF(AND('Engine Inputs'!D31=0,U31=0),"",IF('Engine Inputs'!D31=0,"📈 Up",IF((U31-'Engine Inputs'!D31)/'Engine Inputs'!D31&gt;Config!$B$2,"📈 Up",IF((U31-'Engine Inputs'!D31)/'Engine Inputs'!D31&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W31" s="2">
+        <f>IF(AND(F31=0,E31=0),"",IF(F31=0,"📈 Up",IF((E31-F31)/F31&gt;Config!$B$2,"📈 Up",IF((E31-F31)/F31&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
         <is>
           <t>Jarsini</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W31"/>
+  <autoFilter ref="A1:X31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3156,15 +3322,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Daily Sales Track — KPI Summary</t>
         </is>
@@ -3176,7 +3342,7 @@
           <t>Reporting day</t>
         </is>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="12" t="n">
         <v>46225</v>
       </c>
     </row>
@@ -3186,17 +3352,17 @@
           <t>Generated</t>
         </is>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="12" t="n">
         <v>46226</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -3216,89 +3382,261 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Total Sales Today</t>
+          <t>Total Sales Today — GBP</t>
         </is>
       </c>
       <c r="B7" s="4">
-        <f>SUM('Daily Sales Track'!D2:D31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$E$2:$E$31)</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Total Sales Yesterday</t>
-        </is>
-      </c>
-      <c r="B8" s="4">
-        <f>SUM('Daily Sales Track'!E2:E31)</f>
+          <t>Total Sales Today — EUR</t>
+        </is>
+      </c>
+      <c r="B8" s="7">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$E$2:$E$31)</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Overall Growth</t>
-        </is>
-      </c>
-      <c r="B9" s="5">
-        <f>IF(B8=0,"",(B7-B8)/B8)</f>
+          <t>Total Sales Today — USD</t>
+        </is>
+      </c>
+      <c r="B9" s="9">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$E$2:$E$31)</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Total Orders</t>
-        </is>
-      </c>
-      <c r="B10" s="6">
-        <f>SUM('Daily Sales Track'!I2:I31)</f>
+          <t>Total Sales Today — CAD</t>
+        </is>
+      </c>
+      <c r="B10" s="10">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$E$2:$E$31)</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Yesterday Orders</t>
-        </is>
-      </c>
-      <c r="B11" s="6">
-        <f>SUM('Daily Sales Track'!J2:J31)</f>
+          <t>Total Sales Yesterday — GBP</t>
+        </is>
+      </c>
+      <c r="B11" s="4">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$F$2:$F$31)</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Order Growth</t>
-        </is>
-      </c>
-      <c r="B12" s="5">
-        <f>IF(B11=0,"",(B10-B11)/B11)</f>
+          <t>Total Sales Yesterday — EUR</t>
+        </is>
+      </c>
+      <c r="B12" s="7">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$F$2:$F$31)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Total Units Sold</t>
-        </is>
-      </c>
-      <c r="B13" s="6">
-        <f>SUM('Daily Sales Track'!M2:M31)</f>
+          <t>Total Sales Yesterday — USD</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$F$2:$F$31)</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Average Order Value</t>
-        </is>
-      </c>
-      <c r="B14" s="4">
-        <f>IF(B10=0,"",B7/B10)</f>
-        <v/>
+          <t>Total Sales Yesterday — CAD</t>
+        </is>
+      </c>
+      <c r="B14" s="10">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$F$2:$F$31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Same Day LY Sales — GBP</t>
+        </is>
+      </c>
+      <c r="B15" s="4">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$I$2:$I$31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Same Day LY Sales — EUR</t>
+        </is>
+      </c>
+      <c r="B16" s="7">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$I$2:$I$31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Same Day LY Sales — USD</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$I$2:$I$31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Same Day LY Sales — CAD</t>
+        </is>
+      </c>
+      <c r="B18" s="10">
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$I$2:$I$31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Sales Growth — GBP</t>
+        </is>
+      </c>
+      <c r="B19" s="5">
+        <f>IF(B11=0,"",(B7-B11)/B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Sales Growth — EUR</t>
+        </is>
+      </c>
+      <c r="B20" s="5">
+        <f>IF(B12=0,"",(B8-B12)/B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Sales Growth — USD</t>
+        </is>
+      </c>
+      <c r="B21" s="5">
+        <f>IF(B13=0,"",(B9-B13)/B13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Sales Growth — CAD</t>
+        </is>
+      </c>
+      <c r="B22" s="5">
+        <f>IF(B14=0,"",(B10-B14)/B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Total Orders</t>
+        </is>
+      </c>
+      <c r="B23" s="6">
+        <f>SUM('Daily Sales Track'!J2:J31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Yesterday Orders</t>
+        </is>
+      </c>
+      <c r="B24" s="6">
+        <f>SUM('Daily Sales Track'!K2:K31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Total Units Sold</t>
+        </is>
+      </c>
+      <c r="B25" s="6">
+        <f>SUM('Daily Sales Track'!N2:N31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Avg Order Value — GBP</t>
+        </is>
+      </c>
+      <c r="B26" s="4">
+        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$J$2:$J$31)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$E$2:$E$31)/SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$J$2:$J$31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Avg Order Value — EUR</t>
+        </is>
+      </c>
+      <c r="B27" s="7">
+        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$J$2:$J$31)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$E$2:$E$31)/SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$J$2:$J$31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Avg Order Value — USD</t>
+        </is>
+      </c>
+      <c r="B28" s="9">
+        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$J$2:$J$31)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$E$2:$E$31)/SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$J$2:$J$31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Avg Order Value — CAD</t>
+        </is>
+      </c>
+      <c r="B29" s="10">
+        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$J$2:$J$31)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$E$2:$E$31)/SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$J$2:$J$31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NOTE: money is never summed across currencies. orders.total is in each marketplace's own currency and ledsone holds no exchange rates.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3319,7 +3657,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Editable engine configuration</t>
         </is>
@@ -3331,7 +3669,7 @@
           <t>Trend band (+/-)</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" s="14" t="n">
         <v>0.05</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -3404,32 +3742,38 @@
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Account</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>PH Sales 2026-07-21</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>AH Sales 2026-07-21</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Prior-day (R-2) AH / PH sales - these drive the AH Sales Trend and PH Sales Trend columns. Rows 2..31 align 1:1 with 'Daily Sales Track' rows 2..31; do not sort or insert rows on either sheet independently.</t>
         </is>
@@ -3446,10 +3790,15 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="n">
         <v>534.77</v>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="E2" s="16" t="n">
         <v>336.33</v>
       </c>
     </row>
@@ -3464,10 +3813,15 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C3" s="13" t="n">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="n">
         <v>292.81</v>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="E3" s="16" t="n">
         <v>166.19</v>
       </c>
     </row>
@@ -3482,10 +3836,15 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C4" s="13" t="n">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="n">
         <v>7.41</v>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="E4" s="17" t="n">
         <v>33.65</v>
       </c>
     </row>
@@ -3500,10 +3859,15 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n">
         <v>53.83</v>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="E5" s="16" t="n">
         <v>146.1</v>
       </c>
     </row>
@@ -3518,10 +3882,15 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="n">
         <v>30.07</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="E6" s="17" t="n">
         <v>208.41</v>
       </c>
     </row>
@@ -3536,10 +3905,15 @@
           <t>Ireland</t>
         </is>
       </c>
-      <c r="C7" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13" t="n">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="17" t="n">
         <v>5.81</v>
       </c>
     </row>
@@ -3554,10 +3928,15 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="C8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13" t="n">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3572,10 +3951,15 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
         <v>60.27</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="E9" s="17" t="n">
         <v>201.27</v>
       </c>
     </row>
@@ -3590,10 +3974,15 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C10" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13" t="n">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="16" t="n">
         <v>271.95</v>
       </c>
     </row>
@@ -3608,10 +3997,15 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13" t="n">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="17" t="n">
         <v>138.84</v>
       </c>
     </row>
@@ -3626,10 +4020,15 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="13" t="n">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="16" t="n">
         <v>77.09999999999999</v>
       </c>
     </row>
@@ -3644,10 +4043,15 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C13" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="13" t="n">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="n">
         <v>60.76</v>
       </c>
     </row>
@@ -3662,10 +4066,15 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C14" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="13" t="n">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="16" t="n">
         <v>68.78</v>
       </c>
     </row>
@@ -3680,10 +4089,15 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C15" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="13" t="n">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3698,10 +4112,15 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="13" t="n">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3716,10 +4135,15 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="13" t="n">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="17" t="n">
         <v>9.08</v>
       </c>
     </row>
@@ -3734,10 +4158,15 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="13" t="n">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="18" t="n">
         <v>26.99</v>
       </c>
     </row>
@@ -3752,10 +4181,15 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C19" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13" t="n">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="17" t="n">
         <v>68.09</v>
       </c>
     </row>
@@ -3770,10 +4204,15 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="13" t="n">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="16" t="n">
         <v>16.58</v>
       </c>
     </row>
@@ -3788,10 +4227,15 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C21" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="13" t="n">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3806,10 +4250,15 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C22" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="13" t="n">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3824,10 +4273,15 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C23" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="13" t="n">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17" t="n">
         <v>28.98</v>
       </c>
     </row>
@@ -3842,10 +4296,15 @@
           <t>Canada</t>
         </is>
       </c>
-      <c r="C24" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="13" t="n">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3860,10 +4319,15 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C25" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="13" t="n">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3878,10 +4342,15 @@
           <t>France</t>
         </is>
       </c>
-      <c r="C26" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="13" t="n">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3896,10 +4365,15 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C27" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="13" t="n">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3914,10 +4388,15 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C28" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="13" t="n">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3932,10 +4411,15 @@
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="C29" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="13" t="n">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3950,10 +4434,15 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C30" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="13" t="n">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3968,10 +4457,15 @@
           <t>UK</t>
         </is>
       </c>
-      <c r="C31" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="13" t="n">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3993,7 +4487,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>REQ-17-D01 Daily Sales Track — sources, definitions, assumptions and gaps</t>
         </is>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E2" s="4" t="n">
+        <v>723.67</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>837.9299999999999</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>863.36</v>
       </c>
       <c r="G2" s="4">
         <f>E2-F2</f>
@@ -674,46 +674,46 @@
         <v/>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1233.51</v>
+        <v>928.04</v>
       </c>
       <c r="J2" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="K2" s="6" t="n">
         <v>42</v>
-      </c>
-      <c r="K2" s="6" t="n">
-        <v>49</v>
       </c>
       <c r="L2" s="5">
         <f>IF(K2=0,"",(J2-K2)/K2)</f>
         <v/>
       </c>
       <c r="M2" s="6" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="O2" s="4">
         <f>IF(J2=0,"",E2/J2)</f>
         <v/>
       </c>
       <c r="P2" s="6" t="n">
-        <v>2843</v>
+        <v>2851</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>1598</v>
+        <v>1603</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>436.24</v>
+        <v>261.57</v>
       </c>
       <c r="S2" s="2">
         <f>IF(AND('Engine Inputs'!E2=0,R2=0),"",IF('Engine Inputs'!E2=0,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&gt;Config!$B$2,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T2" s="6" t="n">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>394.11</v>
+        <v>473.2</v>
       </c>
       <c r="V2" s="2">
         <f>IF(AND('Engine Inputs'!D2=0,U2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E3" s="4" t="n">
+        <v>375.11</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>397.95</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>444.6</v>
       </c>
       <c r="G3" s="4">
         <f>E3-F3</f>
@@ -763,46 +763,46 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>497.19</v>
+        <v>682.62</v>
       </c>
       <c r="J3" s="6" t="n">
         <v>21</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="L3" s="5">
         <f>IF(K3=0,"",(J3-K3)/K3)</f>
         <v/>
       </c>
       <c r="M3" s="6" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="O3" s="4">
         <f>IF(J3=0,"",E3/J3)</f>
         <v/>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>965</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>197.77</v>
+        <v>81.13</v>
       </c>
       <c r="S3" s="2">
         <f>IF(AND('Engine Inputs'!E3=0,R3=0),"",IF('Engine Inputs'!E3=0,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&gt;Config!$B$2,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T3" s="6" t="n">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>223.86</v>
+        <v>307.45</v>
       </c>
       <c r="V3" s="2">
         <f>IF(AND('Engine Inputs'!D3=0,U3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E4" s="7" t="n">
+        <v>62.89</v>
+      </c>
+      <c r="F4" s="7" t="n">
         <v>306.58</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>61.33</v>
       </c>
       <c r="G4" s="7">
         <f>E4-F4</f>
@@ -852,36 +852,36 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>534.5599999999999</v>
+        <v>428.11</v>
       </c>
       <c r="J4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="L4" s="5">
         <f>IF(K4=0,"",(J4-K4)/K4)</f>
         <v/>
       </c>
       <c r="M4" s="6" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O4" s="7">
         <f>IF(J4=0,"",E4/J4)</f>
         <v/>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>298.23</v>
+        <v>37.94</v>
       </c>
       <c r="S4" s="2">
         <f>IF(AND('Engine Inputs'!E4=0,R4=0),"",IF('Engine Inputs'!E4=0,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&gt;Config!$B$2,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -891,7 +891,7 @@
         <v>214</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>0</v>
+        <v>7.83</v>
       </c>
       <c r="V4" s="2">
         <f>IF(AND('Engine Inputs'!D4=0,U4=0),"",IF('Engine Inputs'!D4=0,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&gt;Config!$B$2,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E5" s="4" t="n">
+        <v>104.03</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>261.26</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>198</v>
       </c>
       <c r="G5" s="4">
         <f>E5-F5</f>
@@ -941,36 +941,36 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>259.76</v>
+        <v>243.68</v>
       </c>
       <c r="J5" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>14</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>10</v>
       </c>
       <c r="L5" s="5">
         <f>IF(K5=0,"",(J5-K5)/K5)</f>
         <v/>
       </c>
       <c r="M5" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="O5" s="4">
         <f>IF(J5=0,"",E5/J5)</f>
         <v/>
       </c>
       <c r="P5" s="6" t="n">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>201.28</v>
+        <v>39.67</v>
       </c>
       <c r="S5" s="2">
         <f>IF(AND('Engine Inputs'!E5=0,R5=0),"",IF('Engine Inputs'!E5=0,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&gt;Config!$B$2,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -980,7 +980,7 @@
         <v>457</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>70.20999999999999</v>
+        <v>56.12</v>
       </c>
       <c r="V5" s="2">
         <f>IF(AND('Engine Inputs'!D5=0,U5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E6" s="7" t="n">
+        <v>159.67</v>
+      </c>
+      <c r="F6" s="7" t="n">
         <v>149.5</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>241.79</v>
       </c>
       <c r="G6" s="7">
         <f>E6-F6</f>
@@ -1030,23 +1030,23 @@
         <v/>
       </c>
       <c r="I6" s="7" t="n">
-        <v>212.66</v>
+        <v>157.49</v>
       </c>
       <c r="J6" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="6" t="n">
         <v>11</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>10</v>
       </c>
       <c r="L6" s="5">
         <f>IF(K6=0,"",(J6-K6)/K6)</f>
         <v/>
       </c>
       <c r="M6" s="6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O6" s="7">
         <f>IF(J6=0,"",E6/J6)</f>
@@ -1059,7 +1059,7 @@
         <v>552</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>133.07</v>
+        <v>150.93</v>
       </c>
       <c r="S6" s="2">
         <f>IF(AND('Engine Inputs'!E6=0,R6=0),"",IF('Engine Inputs'!E6=0,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&gt;Config!$B$2,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1069,7 +1069,7 @@
         <v>82</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>7.19</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2">
         <f>IF(AND('Engine Inputs'!D6=0,U6=0),"",IF('Engine Inputs'!D6=0,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&gt;Config!$B$2,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7">
         <f>E7-F7</f>
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" s="5">
         <f>IF(K7=0,"",(J7-K7)/K7)</f>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E9" s="7" t="n">
+        <v>217.52</v>
+      </c>
+      <c r="F9" s="7" t="n">
         <v>397.19</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>256.76</v>
       </c>
       <c r="G9" s="7">
         <f>E9-F9</f>
@@ -1297,23 +1297,23 @@
         <v/>
       </c>
       <c r="I9" s="7" t="n">
-        <v>394.9</v>
+        <v>339.99</v>
       </c>
       <c r="J9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>19</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>11</v>
       </c>
       <c r="L9" s="5">
         <f>IF(K9=0,"",(J9-K9)/K9)</f>
         <v/>
       </c>
       <c r="M9" s="6" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="O9" s="7">
         <f>IF(J9=0,"",E9/J9)</f>
@@ -1326,7 +1326,7 @@
         <v>449</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>379.38</v>
+        <v>155.64</v>
       </c>
       <c r="S9" s="2">
         <f>IF(AND('Engine Inputs'!E9=0,R9=0),"",IF('Engine Inputs'!E9=0,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&gt;Config!$B$2,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1336,7 +1336,7 @@
         <v>92</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>33.38</v>
+        <v>42.4</v>
       </c>
       <c r="V9" s="2">
         <f>IF(AND('Engine Inputs'!D9=0,U9=0),"",IF('Engine Inputs'!D9=0,"📈 Up",IF((U9-'Engine Inputs'!D9)/'Engine Inputs'!D9&gt;Config!$B$2,"📈 Up",IF((U9-'Engine Inputs'!D9)/'Engine Inputs'!D9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E10" s="4" t="n">
+        <v>381.98</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>202.68</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>280.92</v>
       </c>
       <c r="G10" s="4">
         <f>E10-F10</f>
@@ -1386,36 +1386,36 @@
         <v/>
       </c>
       <c r="I10" s="4" t="n">
-        <v>113.61</v>
+        <v>93.39</v>
       </c>
       <c r="J10" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="K10" s="6" t="n">
         <v>8</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>15</v>
       </c>
       <c r="L10" s="5">
         <f>IF(K10=0,"",(J10-K10)/K10)</f>
         <v/>
       </c>
       <c r="M10" s="6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="O10" s="4">
         <f>IF(J10=0,"",E10/J10)</f>
         <v/>
       </c>
       <c r="P10" s="6" t="n">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>202.68</v>
+        <v>378.99</v>
       </c>
       <c r="S10" s="2">
         <f>IF(AND('Engine Inputs'!E10=0,R10=0),"",IF('Engine Inputs'!E10=0,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&gt;Config!$B$2,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E11" s="7" t="n">
+        <v>87.06999999999999</v>
+      </c>
+      <c r="F11" s="7" t="n">
         <v>45.48</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>159.54</v>
       </c>
       <c r="G11" s="7">
         <f>E11-F11</f>
@@ -1475,13 +1475,13 @@
         <v/>
       </c>
       <c r="I11" s="7" t="n">
-        <v>105.46</v>
+        <v>105.86</v>
       </c>
       <c r="J11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>9</v>
       </c>
       <c r="L11" s="5">
         <f>IF(K11=0,"",(J11-K11)/K11)</f>
@@ -1491,7 +1491,7 @@
         <v>6</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O11" s="7">
         <f>IF(J11=0,"",E11/J11)</f>
@@ -1504,7 +1504,7 @@
         <v>450</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>26.57</v>
+        <v>65.81</v>
       </c>
       <c r="S11" s="2">
         <f>IF(AND('Engine Inputs'!E11=0,R11=0),"",IF('Engine Inputs'!E11=0,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&gt;Config!$B$2,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1514,7 +1514,7 @@
         <v>36</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>6.7</v>
+        <v>4.95</v>
       </c>
       <c r="V11" s="2">
         <f>IF(AND('Engine Inputs'!D11=0,U11=0),"",IF('Engine Inputs'!D11=0,"📈 Up",IF((U11-'Engine Inputs'!D11)/'Engine Inputs'!D11&gt;Config!$B$2,"📈 Up",IF((U11-'Engine Inputs'!D11)/'Engine Inputs'!D11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E12" s="4" t="n">
+        <v>140.52</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>157.59</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>75.78</v>
       </c>
       <c r="G12" s="4">
         <f>E12-F12</f>
@@ -1564,10 +1564,10 @@
         <v/>
       </c>
       <c r="I12" s="4" t="n">
-        <v>82.87</v>
+        <v>176.91</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>8</v>
@@ -1580,7 +1580,7 @@
         <v>10</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O12" s="4">
         <f>IF(J12=0,"",E12/J12)</f>
@@ -1593,7 +1593,7 @@
         <v>474</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>166.07</v>
+        <v>150.5</v>
       </c>
       <c r="S12" s="2">
         <f>IF(AND('Engine Inputs'!E12=0,R12=0),"",IF('Engine Inputs'!E12=0,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&gt;Config!$B$2,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E13" s="4" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>41.99</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>57.7</v>
       </c>
       <c r="G13" s="4">
         <f>E13-F13</f>
@@ -1653,36 +1653,36 @@
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>27.34</v>
+        <v>99.7</v>
       </c>
       <c r="J13" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>2</v>
       </c>
       <c r="L13" s="5">
         <f>IF(K13=0,"",(J13-K13)/K13)</f>
         <v/>
       </c>
       <c r="M13" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="O13" s="4">
         <f>IF(J13=0,"",E13/J13)</f>
         <v/>
       </c>
       <c r="P13" s="6" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>45.43</v>
+        <v>57.76</v>
       </c>
       <c r="S13" s="2">
         <f>IF(AND('Engine Inputs'!E13=0,R13=0),"",IF('Engine Inputs'!E13=0,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&gt;Config!$B$2,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>65.78</v>
+        <v>0</v>
       </c>
       <c r="G14" s="4">
         <f>E14-F14</f>
@@ -1742,23 +1742,23 @@
         <v/>
       </c>
       <c r="I14" s="4" t="n">
-        <v>314.72</v>
+        <v>52.25</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="5">
         <f>IF(K14=0,"",(J14-K14)/K14)</f>
         <v/>
       </c>
       <c r="M14" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" s="4">
         <f>IF(J14=0,"",E14/J14)</f>
@@ -1771,7 +1771,7 @@
         <v>403</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="S14" s="2">
         <f>IF(AND('Engine Inputs'!E14=0,R14=0),"",IF('Engine Inputs'!E14=0,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&gt;Config!$B$2,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>26.33</v>
+        <v>0</v>
       </c>
       <c r="G17" s="7">
         <f>E17-F17</f>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
         <f>IF(K17=0,"",(J17-K17)/K17)</f>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>29.62</v>
+        <v>0</v>
       </c>
       <c r="G18" s="9">
         <f>E18-F18</f>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="5">
         <f>IF(K18=0,"",(J18-K18)/K18)</f>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="7" t="n">
         <v>32.29</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>78.15000000000001</v>
       </c>
       <c r="G19" s="7">
         <f>E19-F19</f>
@@ -2187,23 +2187,23 @@
         <v/>
       </c>
       <c r="I19" s="7" t="n">
-        <v>152.48</v>
+        <v>93.22</v>
       </c>
       <c r="J19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="L19" s="5">
         <f>IF(K19=0,"",(J19-K19)/K19)</f>
         <v/>
       </c>
       <c r="M19" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O19" s="7">
         <f>IF(J19=0,"",E19/J19)</f>
@@ -2216,7 +2216,7 @@
         <v>295</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>28.84</v>
+        <v>0</v>
       </c>
       <c r="S19" s="2">
         <f>IF(AND('Engine Inputs'!E19=0,R19=0),"",IF('Engine Inputs'!E19=0,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&gt;Config!$B$2,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>16.58</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4">
         <f>E20-F20</f>
@@ -2276,20 +2276,20 @@
         <v/>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0</v>
+        <v>69.78</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="5">
         <f>IF(K20=0,"",(J20-K20)/K20)</f>
         <v/>
       </c>
       <c r="M20" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>0</v>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>0</v>
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E23" s="7" t="n">
+        <v>37.98</v>
+      </c>
+      <c r="F23" s="7" t="n">
         <v>152.91</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>28.98</v>
       </c>
       <c r="G23" s="7">
         <f>E23-F23</f>
@@ -2546,10 +2546,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>2</v>
       </c>
       <c r="L23" s="5">
         <f>IF(K23=0,"",(J23-K23)/K23)</f>
@@ -2559,20 +2559,20 @@
         <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O23" s="7">
         <f>IF(J23=0,"",E23/J23)</f>
         <v/>
       </c>
       <c r="P23" s="6" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>157.69</v>
+        <v>37.98</v>
       </c>
       <c r="S23" s="2">
         <f>IF(AND('Engine Inputs'!E23=0,R23=0),"",IF('Engine Inputs'!E23=0,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&gt;Config!$B$2,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="3">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="5">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>PH Sales 2026-07-21</t>
+          <t>PH Sales 2026-07-22</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>AH Sales 2026-07-21</t>
+          <t>AH Sales 2026-07-22</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>534.77</v>
+        <v>394.11</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>336.33</v>
+        <v>436.24</v>
       </c>
     </row>
     <row r="3">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D3" s="16" t="n">
-        <v>292.81</v>
+        <v>223.86</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>166.19</v>
+        <v>197.77</v>
       </c>
     </row>
     <row r="4">
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>7.41</v>
+        <v>0</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>33.65</v>
+        <v>298.23</v>
       </c>
     </row>
     <row r="5">
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>53.83</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>146.1</v>
+        <v>201.28</v>
       </c>
     </row>
     <row r="6">
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>30.07</v>
+        <v>7.19</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>208.41</v>
+        <v>133.07</v>
       </c>
     </row>
     <row r="7">
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>5.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>60.27</v>
+        <v>33.38</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>201.27</v>
+        <v>379.38</v>
       </c>
     </row>
     <row r="10">
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>271.95</v>
+        <v>202.68</v>
       </c>
     </row>
     <row r="11">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>138.84</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="12">
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>77.09999999999999</v>
+        <v>166.07</v>
       </c>
     </row>
     <row r="13">
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>60.76</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="14">
@@ -4075,7 +4075,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>68.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>9.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>26.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>68.09</v>
+        <v>28.84</v>
       </c>
     </row>
     <row r="20">
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>16.58</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>28.98</v>
+        <v>157.69</v>
       </c>
     </row>
     <row r="24">
@@ -4582,7 +4582,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Generated 2026-07-23.  "Today" = 2026-07-22.  "Yesterday" = 2026-07-21.  Same Day LY = 2025-07-22.</t>
+          <t xml:space="preserve">  Generated 2026-07-24.  "Today" = 2026-07-23.  "Yesterday" = 2026-07-22.  Same Day LY = 2025-07-23.</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-07-22</t>
+          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-07-23</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2026-07-22 was a Wednesday; 2025-07-22 was a Tuesday). Day-of-week effects are present in this comparison.</t>
+          <t xml:space="preserve">  (2026-07-23 was a Thursday; 2025-07-23 was a Wednesday). Day-of-week effects are present in this comparison.</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>723.67</v>
+        <v>923.54</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>837.9299999999999</v>
+        <v>772.84</v>
       </c>
       <c r="G2" s="4">
         <f>E2-F2</f>
@@ -674,36 +674,36 @@
         <v/>
       </c>
       <c r="I2" s="4" t="n">
-        <v>928.04</v>
+        <v>1039.14</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="L2" s="5">
         <f>IF(K2=0,"",(J2-K2)/K2)</f>
         <v/>
       </c>
       <c r="M2" s="6" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="O2" s="4">
         <f>IF(J2=0,"",E2/J2)</f>
         <v/>
       </c>
       <c r="P2" s="6" t="n">
-        <v>2851</v>
+        <v>2853</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>261.57</v>
+        <v>649.38</v>
       </c>
       <c r="S2" s="2">
         <f>IF(AND('Engine Inputs'!E2=0,R2=0),"",IF('Engine Inputs'!E2=0,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&gt;Config!$B$2,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -713,7 +713,7 @@
         <v>1248</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>473.2</v>
+        <v>290.47</v>
       </c>
       <c r="V2" s="2">
         <f>IF(AND('Engine Inputs'!D2=0,U2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>375.11</v>
+        <v>376.56</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>397.95</v>
+        <v>398.39</v>
       </c>
       <c r="G3" s="4">
         <f>E3-F3</f>
@@ -763,46 +763,46 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>682.62</v>
+        <v>497.59</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="L3" s="5">
         <f>IF(K3=0,"",(J3-K3)/K3)</f>
         <v/>
       </c>
       <c r="M3" s="6" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O3" s="4">
         <f>IF(J3=0,"",E3/J3)</f>
         <v/>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1514</v>
+        <v>1518</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>81.13</v>
+        <v>203.03</v>
       </c>
       <c r="S3" s="2">
         <f>IF(AND('Engine Inputs'!E3=0,R3=0),"",IF('Engine Inputs'!E3=0,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&gt;Config!$B$2,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T3" s="6" t="n">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>307.45</v>
+        <v>181.09</v>
       </c>
       <c r="V3" s="2">
         <f>IF(AND('Engine Inputs'!D3=0,U3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>62.89</v>
+        <v>436.29</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>306.58</v>
+        <v>184.49</v>
       </c>
       <c r="G4" s="7">
         <f>E4-F4</f>
@@ -852,46 +852,46 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>428.11</v>
+        <v>343.74</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L4" s="5">
         <f>IF(K4=0,"",(J4-K4)/K4)</f>
         <v/>
       </c>
       <c r="M4" s="6" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="O4" s="7">
         <f>IF(J4=0,"",E4/J4)</f>
         <v/>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>1140</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>37.94</v>
+        <v>383.78</v>
       </c>
       <c r="S4" s="2">
         <f>IF(AND('Engine Inputs'!E4=0,R4=0),"",IF('Engine Inputs'!E4=0,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&gt;Config!$B$2,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T4" s="6" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>7.83</v>
+        <v>13.39</v>
       </c>
       <c r="V4" s="2">
         <f>IF(AND('Engine Inputs'!D4=0,U4=0),"",IF('Engine Inputs'!D4=0,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&gt;Config!$B$2,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>104.03</v>
+        <v>234.28</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>261.26</v>
+        <v>218.11</v>
       </c>
       <c r="G5" s="4">
         <f>E5-F5</f>
@@ -941,36 +941,36 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>243.68</v>
+        <v>306.47</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L5" s="5">
         <f>IF(K5=0,"",(J5-K5)/K5)</f>
         <v/>
       </c>
       <c r="M5" s="6" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O5" s="4">
         <f>IF(J5=0,"",E5/J5)</f>
         <v/>
       </c>
       <c r="P5" s="6" t="n">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>39.67</v>
+        <v>221.24</v>
       </c>
       <c r="S5" s="2">
         <f>IF(AND('Engine Inputs'!E5=0,R5=0),"",IF('Engine Inputs'!E5=0,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&gt;Config!$B$2,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -980,7 +980,7 @@
         <v>457</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>56.12</v>
+        <v>17.48</v>
       </c>
       <c r="V5" s="2">
         <f>IF(AND('Engine Inputs'!D5=0,U5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>159.67</v>
+        <v>401.78</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>149.5</v>
+        <v>245.32</v>
       </c>
       <c r="G6" s="7">
         <f>E6-F6</f>
@@ -1030,10 +1030,10 @@
         <v/>
       </c>
       <c r="I6" s="7" t="n">
-        <v>157.49</v>
+        <v>136.83</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>11</v>
@@ -1043,23 +1043,23 @@
         <v/>
       </c>
       <c r="M6" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="O6" s="7">
         <f>IF(J6=0,"",E6/J6)</f>
         <v/>
       </c>
       <c r="P6" s="6" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>150.93</v>
+        <v>371.61</v>
       </c>
       <c r="S6" s="2">
         <f>IF(AND('Engine Inputs'!E6=0,R6=0),"",IF('Engine Inputs'!E6=0,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&gt;Config!$B$2,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1069,7 +1069,7 @@
         <v>82</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>0</v>
+        <v>25.58</v>
       </c>
       <c r="V6" s="2">
         <f>IF(AND('Engine Inputs'!D6=0,U6=0),"",IF('Engine Inputs'!D6=0,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&gt;Config!$B$2,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>217.52</v>
+        <v>362.2</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>397.19</v>
+        <v>177.65</v>
       </c>
       <c r="G9" s="7">
         <f>E9-F9</f>
@@ -1297,23 +1297,23 @@
         <v/>
       </c>
       <c r="I9" s="7" t="n">
-        <v>339.99</v>
+        <v>413.26</v>
       </c>
       <c r="J9" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>10</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>19</v>
       </c>
       <c r="L9" s="5">
         <f>IF(K9=0,"",(J9-K9)/K9)</f>
         <v/>
       </c>
       <c r="M9" s="6" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="O9" s="7">
         <f>IF(J9=0,"",E9/J9)</f>
@@ -1326,7 +1326,7 @@
         <v>449</v>
       </c>
       <c r="R9" s="7" t="n">
-        <v>155.64</v>
+        <v>359.82</v>
       </c>
       <c r="S9" s="2">
         <f>IF(AND('Engine Inputs'!E9=0,R9=0),"",IF('Engine Inputs'!E9=0,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&gt;Config!$B$2,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1336,7 +1336,7 @@
         <v>92</v>
       </c>
       <c r="U9" s="7" t="n">
-        <v>42.4</v>
+        <v>10.34</v>
       </c>
       <c r="V9" s="2">
         <f>IF(AND('Engine Inputs'!D9=0,U9=0),"",IF('Engine Inputs'!D9=0,"📈 Up",IF((U9-'Engine Inputs'!D9)/'Engine Inputs'!D9&gt;Config!$B$2,"📈 Up",IF((U9-'Engine Inputs'!D9)/'Engine Inputs'!D9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>381.98</v>
+        <v>325.97</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>202.68</v>
+        <v>207.18</v>
       </c>
       <c r="G10" s="4">
         <f>E10-F10</f>
@@ -1386,36 +1386,36 @@
         <v/>
       </c>
       <c r="I10" s="4" t="n">
-        <v>93.39</v>
+        <v>179.9</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L10" s="5">
         <f>IF(K10=0,"",(J10-K10)/K10)</f>
         <v/>
       </c>
       <c r="M10" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="O10" s="4">
         <f>IF(J10=0,"",E10/J10)</f>
         <v/>
       </c>
       <c r="P10" s="6" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>378.99</v>
+        <v>319.73</v>
       </c>
       <c r="S10" s="2">
         <f>IF(AND('Engine Inputs'!E10=0,R10=0),"",IF('Engine Inputs'!E10=0,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&gt;Config!$B$2,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>87.06999999999999</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>45.48</v>
+        <v>165.27</v>
       </c>
       <c r="G11" s="7">
         <f>E11-F11</f>
@@ -1475,23 +1475,23 @@
         <v/>
       </c>
       <c r="I11" s="7" t="n">
-        <v>105.86</v>
+        <v>106.78</v>
       </c>
       <c r="J11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="L11" s="5">
         <f>IF(K11=0,"",(J11-K11)/K11)</f>
         <v/>
       </c>
       <c r="M11" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O11" s="7">
         <f>IF(J11=0,"",E11/J11)</f>
@@ -1504,7 +1504,7 @@
         <v>450</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>65.81</v>
+        <v>61.37</v>
       </c>
       <c r="S11" s="2">
         <f>IF(AND('Engine Inputs'!E11=0,R11=0),"",IF('Engine Inputs'!E11=0,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&gt;Config!$B$2,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1514,7 +1514,7 @@
         <v>36</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>4.95</v>
+        <v>19.3</v>
       </c>
       <c r="V11" s="2">
         <f>IF(AND('Engine Inputs'!D11=0,U11=0),"",IF('Engine Inputs'!D11=0,"📈 Up",IF((U11-'Engine Inputs'!D11)/'Engine Inputs'!D11&gt;Config!$B$2,"📈 Up",IF((U11-'Engine Inputs'!D11)/'Engine Inputs'!D11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>140.52</v>
+        <v>170.78</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>157.59</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="G12" s="4">
         <f>E12-F12</f>
@@ -1564,23 +1564,23 @@
         <v/>
       </c>
       <c r="I12" s="4" t="n">
-        <v>176.91</v>
+        <v>93.09</v>
       </c>
       <c r="J12" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="6" t="n">
         <v>7</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>8</v>
       </c>
       <c r="L12" s="5">
         <f>IF(K12=0,"",(J12-K12)/K12)</f>
         <v/>
       </c>
       <c r="M12" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="O12" s="4">
         <f>IF(J12=0,"",E12/J12)</f>
@@ -1593,7 +1593,7 @@
         <v>474</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>150.5</v>
+        <v>177.04</v>
       </c>
       <c r="S12" s="2">
         <f>IF(AND('Engine Inputs'!E12=0,R12=0),"",IF('Engine Inputs'!E12=0,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&gt;Config!$B$2,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>55.94</v>
+        <v>64.86</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>41.99</v>
+        <v>23.64</v>
       </c>
       <c r="G13" s="4">
         <f>E13-F13</f>
@@ -1653,23 +1653,23 @@
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>99.7</v>
+        <v>55.23</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13" s="5">
         <f>IF(K13=0,"",(J13-K13)/K13)</f>
         <v/>
       </c>
       <c r="M13" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O13" s="4">
         <f>IF(J13=0,"",E13/J13)</f>
@@ -1682,7 +1682,7 @@
         <v>470</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>57.76</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="S13" s="2">
         <f>IF(AND('Engine Inputs'!E13=0,R13=0),"",IF('Engine Inputs'!E13=0,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&gt;Config!$B$2,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>0</v>
@@ -1742,10 +1742,10 @@
         <v/>
       </c>
       <c r="I14" s="4" t="n">
-        <v>52.25</v>
+        <v>80.05</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
@@ -1758,20 +1758,20 @@
         <v>4</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="4">
         <f>IF(J14=0,"",E14/J14)</f>
         <v/>
       </c>
       <c r="P14" s="6" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="S14" s="2">
         <f>IF(AND('Engine Inputs'!E14=0,R14=0),"",IF('Engine Inputs'!E14=0,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&gt;Config!$B$2,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v/>
       </c>
       <c r="P15" s="6" t="n">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0</v>
+        <v>15.46</v>
       </c>
       <c r="G16" s="9">
         <f>E16-F16</f>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="5">
         <f>IF(K16=0,"",(J16-K16)/K16)</f>
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>0</v>
@@ -2012,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17" s="7">
         <f>IF(J17=0,"",E17/J17)</f>
@@ -2038,7 +2038,7 @@
         <v>368</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0</v>
+        <v>39.9</v>
       </c>
       <c r="S17" s="2">
         <f>IF(AND('Engine Inputs'!E17=0,R17=0),"",IF('Engine Inputs'!E17=0,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&gt;Config!$B$2,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0</v>
+        <v>19.25</v>
       </c>
       <c r="G18" s="9">
         <f>E18-F18</f>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="5">
         <f>IF(K18=0,"",(J18-K18)/K18)</f>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0</v>
+        <v>59.4</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>32.29</v>
+        <v>39.53</v>
       </c>
       <c r="G19" s="7">
         <f>E19-F19</f>
@@ -2187,23 +2187,23 @@
         <v/>
       </c>
       <c r="I19" s="7" t="n">
-        <v>93.22</v>
+        <v>93.12</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L19" s="5">
         <f>IF(K19=0,"",(J19-K19)/K19)</f>
         <v/>
       </c>
       <c r="M19" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O19" s="7">
         <f>IF(J19=0,"",E19/J19)</f>
@@ -2216,7 +2216,7 @@
         <v>295</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>0</v>
+        <v>52.59</v>
       </c>
       <c r="S19" s="2">
         <f>IF(AND('Engine Inputs'!E19=0,R19=0),"",IF('Engine Inputs'!E19=0,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&gt;Config!$B$2,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0</v>
+        <v>33.82</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0</v>
+        <v>53.47</v>
       </c>
       <c r="G20" s="4">
         <f>E20-F20</f>
@@ -2276,36 +2276,36 @@
         <v/>
       </c>
       <c r="I20" s="4" t="n">
-        <v>69.78</v>
+        <v>11.13</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" s="5">
         <f>IF(K20=0,"",(J20-K20)/K20)</f>
         <v/>
       </c>
       <c r="M20" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O20" s="4">
         <f>IF(J20=0,"",E20/J20)</f>
         <v/>
       </c>
       <c r="P20" s="6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0</v>
+        <v>33.82</v>
       </c>
       <c r="S20" s="2">
         <f>IF(AND('Engine Inputs'!E20=0,R20=0),"",IF('Engine Inputs'!E20=0,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&gt;Config!$B$2,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>0</v>
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>37.98</v>
+        <v>33.58</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>152.91</v>
+        <v>10.39</v>
       </c>
       <c r="G23" s="7">
         <f>E23-F23</f>
@@ -2546,10 +2546,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L23" s="5">
         <f>IF(K23=0,"",(J23-K23)/K23)</f>
@@ -2566,13 +2566,13 @@
         <v/>
       </c>
       <c r="P23" s="6" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>37.98</v>
+        <v>35.36</v>
       </c>
       <c r="S23" s="2">
         <f>IF(AND('Engine Inputs'!E23=0,R23=0),"",IF('Engine Inputs'!E23=0,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&gt;Config!$B$2,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="F27" s="4" t="n">
         <v>0</v>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
@@ -2915,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" s="4">
         <f>IF(J27=0,"",E27/J27)</f>
@@ -2928,7 +2928,7 @@
         <v>65</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0</v>
+        <v>6.64</v>
       </c>
       <c r="S27" s="2">
         <f>IF(AND('Engine Inputs'!E27=0,R27=0),"",IF('Engine Inputs'!E27=0,"📈 Up",IF((R27-'Engine Inputs'!E27)/'Engine Inputs'!E27&gt;Config!$B$2,"📈 Up",IF((R27-'Engine Inputs'!E27)/'Engine Inputs'!E27&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46226</v>
+        <v>46229</v>
       </c>
     </row>
     <row r="3">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="5">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>PH Sales 2026-07-22</t>
+          <t>PH Sales 2026-07-25</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>AH Sales 2026-07-22</t>
+          <t>AH Sales 2026-07-25</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>394.11</v>
+        <v>322.88</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>436.24</v>
+        <v>431.91</v>
       </c>
     </row>
     <row r="3">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D3" s="16" t="n">
-        <v>223.86</v>
+        <v>272.7</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>197.77</v>
+        <v>144.18</v>
       </c>
     </row>
     <row r="4">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>298.23</v>
+        <v>142.21</v>
       </c>
     </row>
     <row r="5">
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>70.20999999999999</v>
+        <v>74.69</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>201.28</v>
+        <v>130.14</v>
       </c>
     </row>
     <row r="6">
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>7.19</v>
+        <v>41.28</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>133.07</v>
+        <v>205.44</v>
       </c>
     </row>
     <row r="7">
@@ -3957,10 +3957,10 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>33.38</v>
+        <v>21.31</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>379.38</v>
+        <v>156.8</v>
       </c>
     </row>
     <row r="10">
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>202.68</v>
+        <v>204.19</v>
       </c>
     </row>
     <row r="11">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>6.7</v>
+        <v>103.56</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>26.57</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="12">
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>166.07</v>
+        <v>84.26000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>45.43</v>
+        <v>24.54</v>
       </c>
     </row>
     <row r="14">
@@ -4121,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="17">
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>0</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="19">
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>28.84</v>
+        <v>35.57</v>
       </c>
     </row>
     <row r="20">
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>0</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="21">
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>157.69</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="24">
@@ -4582,7 +4582,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Generated 2026-07-24.  "Today" = 2026-07-23.  "Yesterday" = 2026-07-22.  Same Day LY = 2025-07-23.</t>
+          <t xml:space="preserve">  Generated 2026-07-27.  "Today" = 2026-07-26.  "Yesterday" = 2026-07-25.  Same Day LY = 2025-07-26.</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-07-23</t>
+          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-07-26</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2026-07-23 was a Thursday; 2025-07-23 was a Wednesday). Day-of-week effects are present in this comparison.</t>
+          <t xml:space="preserve">  (2026-07-26 was a Sunday; 2025-07-26 was a Saturday). Day-of-week effects are present in this comparison.</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E2" s="4" t="n">
+        <v>1149.82</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>923.54</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>772.84</v>
       </c>
       <c r="G2" s="4">
         <f>E2-F2</f>
@@ -674,46 +674,46 @@
         <v/>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1039.14</v>
+        <v>1447.52</v>
       </c>
       <c r="J2" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="K2" s="6" t="n">
         <v>37</v>
-      </c>
-      <c r="K2" s="6" t="n">
-        <v>49</v>
       </c>
       <c r="L2" s="5">
         <f>IF(K2=0,"",(J2-K2)/K2)</f>
         <v/>
       </c>
       <c r="M2" s="6" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="O2" s="4">
         <f>IF(J2=0,"",E2/J2)</f>
         <v/>
       </c>
       <c r="P2" s="6" t="n">
-        <v>2853</v>
+        <v>2861</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>1605</v>
+        <v>1609</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>649.38</v>
+        <v>534.37</v>
       </c>
       <c r="S2" s="2">
         <f>IF(AND('Engine Inputs'!E2=0,R2=0),"",IF('Engine Inputs'!E2=0,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&gt;Config!$B$2,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T2" s="6" t="n">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>290.47</v>
+        <v>583.11</v>
       </c>
       <c r="V2" s="2">
         <f>IF(AND('Engine Inputs'!D2=0,U2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E3" s="4" t="n">
+        <v>501.7</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>376.56</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>398.39</v>
       </c>
       <c r="G3" s="4">
         <f>E3-F3</f>
@@ -763,46 +763,46 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>497.59</v>
+        <v>438.94</v>
       </c>
       <c r="J3" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="K3" s="6" t="n">
         <v>30</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>27</v>
       </c>
       <c r="L3" s="5">
         <f>IF(K3=0,"",(J3-K3)/K3)</f>
         <v/>
       </c>
       <c r="M3" s="6" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="O3" s="4">
         <f>IF(J3=0,"",E3/J3)</f>
         <v/>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1518</v>
+        <v>1522</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>203.03</v>
+        <v>190.42</v>
       </c>
       <c r="S3" s="2">
         <f>IF(AND('Engine Inputs'!E3=0,R3=0),"",IF('Engine Inputs'!E3=0,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&gt;Config!$B$2,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T3" s="6" t="n">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>181.09</v>
+        <v>329.62</v>
       </c>
       <c r="V3" s="2">
         <f>IF(AND('Engine Inputs'!D3=0,U3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E4" s="7" t="n">
+        <v>274.41</v>
+      </c>
+      <c r="F4" s="7" t="n">
         <v>436.29</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>184.49</v>
       </c>
       <c r="G4" s="7">
         <f>E4-F4</f>
@@ -852,36 +852,36 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>343.74</v>
+        <v>381.39</v>
       </c>
       <c r="J4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>11</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>7</v>
       </c>
       <c r="L4" s="5">
         <f>IF(K4=0,"",(J4-K4)/K4)</f>
         <v/>
       </c>
       <c r="M4" s="6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="O4" s="7">
         <f>IF(J4=0,"",E4/J4)</f>
         <v/>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>383.78</v>
+        <v>208.91</v>
       </c>
       <c r="S4" s="2">
         <f>IF(AND('Engine Inputs'!E4=0,R4=0),"",IF('Engine Inputs'!E4=0,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&gt;Config!$B$2,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -891,7 +891,7 @@
         <v>216</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>13.39</v>
+        <v>26.78</v>
       </c>
       <c r="V4" s="2">
         <f>IF(AND('Engine Inputs'!D4=0,U4=0),"",IF('Engine Inputs'!D4=0,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&gt;Config!$B$2,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E5" s="4" t="n">
+        <v>287.49</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>234.28</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>218.11</v>
       </c>
       <c r="G5" s="4">
         <f>E5-F5</f>
@@ -941,46 +941,46 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>306.47</v>
+        <v>259.85</v>
       </c>
       <c r="J5" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>12</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>13</v>
       </c>
       <c r="L5" s="5">
         <f>IF(K5=0,"",(J5-K5)/K5)</f>
         <v/>
       </c>
       <c r="M5" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="O5" s="4">
         <f>IF(J5=0,"",E5/J5)</f>
         <v/>
       </c>
       <c r="P5" s="6" t="n">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>221.24</v>
+        <v>200.75</v>
       </c>
       <c r="S5" s="2">
         <f>IF(AND('Engine Inputs'!E5=0,R5=0),"",IF('Engine Inputs'!E5=0,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&gt;Config!$B$2,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T5" s="6" t="n">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>17.48</v>
+        <v>92.58</v>
       </c>
       <c r="V5" s="2">
         <f>IF(AND('Engine Inputs'!D5=0,U5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E6" s="7" t="n">
+        <v>349.81</v>
+      </c>
+      <c r="F6" s="7" t="n">
         <v>401.78</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>245.32</v>
       </c>
       <c r="G6" s="7">
         <f>E6-F6</f>
@@ -1030,36 +1030,36 @@
         <v/>
       </c>
       <c r="I6" s="7" t="n">
-        <v>136.83</v>
+        <v>373.43</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>14</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L6" s="5">
         <f>IF(K6=0,"",(J6-K6)/K6)</f>
         <v/>
       </c>
       <c r="M6" s="6" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O6" s="7">
         <f>IF(J6=0,"",E6/J6)</f>
         <v/>
       </c>
       <c r="P6" s="6" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>371.61</v>
+        <v>292.05</v>
       </c>
       <c r="S6" s="2">
         <f>IF(AND('Engine Inputs'!E6=0,R6=0),"",IF('Engine Inputs'!E6=0,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&gt;Config!$B$2,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1069,7 +1069,7 @@
         <v>82</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>25.58</v>
+        <v>63.33</v>
       </c>
       <c r="V6" s="2">
         <f>IF(AND('Engine Inputs'!D6=0,U6=0),"",IF('Engine Inputs'!D6=0,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&gt;Config!$B$2,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1231,10 +1231,10 @@
         <v/>
       </c>
       <c r="P8" s="6" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>0</v>
@@ -1266,29 +1266,29 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Huetten Lampen DE</t>
+          <t>Coventry Lights</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>362.2</v>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>177.65</v>
-      </c>
-      <c r="G9" s="7">
+        <v>46230</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>190.91</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>325.97</v>
+      </c>
+      <c r="G9" s="4">
         <f>E9-F9</f>
         <v/>
       </c>
@@ -1296,11 +1296,11 @@
         <f>IF(F9=0,"",(E9-F9)/F9)</f>
         <v/>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>413.26</v>
+      <c r="I9" s="4" t="n">
+        <v>169.03</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>10</v>
@@ -1310,12 +1310,12 @@
         <v/>
       </c>
       <c r="M9" s="6" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="O9" s="7">
+        <v>12</v>
+      </c>
+      <c r="O9" s="4">
         <f>IF(J9=0,"",E9/J9)</f>
         <v/>
       </c>
@@ -1323,20 +1323,20 @@
         <v>541</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>449</v>
-      </c>
-      <c r="R9" s="7" t="n">
-        <v>359.82</v>
+        <v>541</v>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>187.42</v>
       </c>
       <c r="S9" s="2">
         <f>IF(AND('Engine Inputs'!E9=0,R9=0),"",IF('Engine Inputs'!E9=0,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&gt;Config!$B$2,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T9" s="6" t="n">
-        <v>92</v>
-      </c>
-      <c r="U9" s="7" t="n">
-        <v>10.34</v>
+        <v>0</v>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="V9" s="2">
         <f>IF(AND('Engine Inputs'!D9=0,U9=0),"",IF('Engine Inputs'!D9=0,"📈 Up",IF((U9-'Engine Inputs'!D9)/'Engine Inputs'!D9&gt;Config!$B$2,"📈 Up",IF((U9-'Engine Inputs'!D9)/'Engine Inputs'!D9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1348,36 +1348,36 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>Jarsini</t>
+          <t>Genga</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Coventry Lights</t>
+          <t>Huetten Lampen DE</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46229</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>325.97</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>207.18</v>
-      </c>
-      <c r="G10" s="4">
+        <v>46230</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>565.01</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>362.2</v>
+      </c>
+      <c r="G10" s="7">
         <f>E10-F10</f>
         <v/>
       </c>
@@ -1385,47 +1385,47 @@
         <f>IF(F10=0,"",(E10-F10)/F10)</f>
         <v/>
       </c>
-      <c r="I10" s="4" t="n">
-        <v>179.9</v>
+      <c r="I10" s="7" t="n">
+        <v>393.59</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L10" s="5">
         <f>IF(K10=0,"",(J10-K10)/K10)</f>
         <v/>
       </c>
       <c r="M10" s="6" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="O10" s="4">
+        <v>33</v>
+      </c>
+      <c r="O10" s="7">
         <f>IF(J10=0,"",E10/J10)</f>
         <v/>
       </c>
       <c r="P10" s="6" t="n">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>540</v>
-      </c>
-      <c r="R10" s="4" t="n">
-        <v>319.73</v>
+        <v>449</v>
+      </c>
+      <c r="R10" s="7" t="n">
+        <v>574.1900000000001</v>
       </c>
       <c r="S10" s="2">
         <f>IF(AND('Engine Inputs'!E10=0,R10=0),"",IF('Engine Inputs'!E10=0,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&gt;Config!$B$2,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="U10" s="7" t="n">
+        <v>19.44</v>
       </c>
       <c r="V10" s="2">
         <f>IF(AND('Engine Inputs'!D10=0,U10=0),"",IF('Engine Inputs'!D10=0,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&gt;Config!$B$2,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>Genga</t>
+          <t>Jarsini</t>
         </is>
       </c>
     </row>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E11" s="7" t="n">
+        <v>248.04</v>
+      </c>
+      <c r="F11" s="7" t="n">
         <v>95.29000000000001</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>165.27</v>
       </c>
       <c r="G11" s="7">
         <f>E11-F11</f>
@@ -1475,23 +1475,23 @@
         <v/>
       </c>
       <c r="I11" s="7" t="n">
-        <v>106.78</v>
+        <v>244.84</v>
       </c>
       <c r="J11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="6" t="n">
         <v>7</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>6</v>
       </c>
       <c r="L11" s="5">
         <f>IF(K11=0,"",(J11-K11)/K11)</f>
         <v/>
       </c>
       <c r="M11" s="6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O11" s="7">
         <f>IF(J11=0,"",E11/J11)</f>
@@ -1504,7 +1504,7 @@
         <v>450</v>
       </c>
       <c r="R11" s="7" t="n">
-        <v>61.37</v>
+        <v>174.97</v>
       </c>
       <c r="S11" s="2">
         <f>IF(AND('Engine Inputs'!E11=0,R11=0),"",IF('Engine Inputs'!E11=0,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&gt;Config!$B$2,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1514,7 +1514,7 @@
         <v>36</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="V11" s="2">
         <f>IF(AND('Engine Inputs'!D11=0,U11=0),"",IF('Engine Inputs'!D11=0,"📈 Up",IF((U11-'Engine Inputs'!D11)/'Engine Inputs'!D11&gt;Config!$B$2,"📈 Up",IF((U11-'Engine Inputs'!D11)/'Engine Inputs'!D11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E12" s="4" t="n">
+        <v>38.37</v>
+      </c>
+      <c r="F12" s="4" t="n">
         <v>170.78</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>86.06999999999999</v>
       </c>
       <c r="G12" s="4">
         <f>E12-F12</f>
@@ -1564,23 +1564,23 @@
         <v/>
       </c>
       <c r="I12" s="4" t="n">
-        <v>93.09</v>
+        <v>216.71</v>
       </c>
       <c r="J12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" s="6" t="n">
         <v>10</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>7</v>
       </c>
       <c r="L12" s="5">
         <f>IF(K12=0,"",(J12-K12)/K12)</f>
         <v/>
       </c>
       <c r="M12" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O12" s="4">
         <f>IF(J12=0,"",E12/J12)</f>
@@ -1593,7 +1593,7 @@
         <v>474</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>177.04</v>
+        <v>38.37</v>
       </c>
       <c r="S12" s="2">
         <f>IF(AND('Engine Inputs'!E12=0,R12=0),"",IF('Engine Inputs'!E12=0,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&gt;Config!$B$2,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E13" s="4" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>64.86</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>23.64</v>
       </c>
       <c r="G13" s="4">
         <f>E13-F13</f>
@@ -1653,36 +1653,36 @@
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>55.23</v>
+        <v>67.09</v>
       </c>
       <c r="J13" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" s="6" t="n">
         <v>8</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>3</v>
       </c>
       <c r="L13" s="5">
         <f>IF(K13=0,"",(J13-K13)/K13)</f>
         <v/>
       </c>
       <c r="M13" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O13" s="4">
         <f>IF(J13=0,"",E13/J13)</f>
         <v/>
       </c>
       <c r="P13" s="6" t="n">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>66.81999999999999</v>
+        <v>18.22</v>
       </c>
       <c r="S13" s="2">
         <f>IF(AND('Engine Inputs'!E13=0,R13=0),"",IF('Engine Inputs'!E13=0,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&gt;Config!$B$2,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>15.6</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>0</v>
@@ -1742,10 +1742,10 @@
         <v/>
       </c>
       <c r="I14" s="4" t="n">
-        <v>80.05</v>
+        <v>135.1</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
@@ -1755,10 +1755,10 @@
         <v/>
       </c>
       <c r="M14" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O14" s="4">
         <f>IF(J14=0,"",E14/J14)</f>
@@ -1771,7 +1771,7 @@
         <v>405</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0</v>
+        <v>17.34</v>
       </c>
       <c r="S14" s="2">
         <f>IF(AND('Engine Inputs'!E14=0,R14=0),"",IF('Engine Inputs'!E14=0,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&gt;Config!$B$2,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>15.46</v>
+        <v>0</v>
       </c>
       <c r="G16" s="9">
         <f>E16-F16</f>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
         <f>IF(K16=0,"",(J16-K16)/K16)</f>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="7" t="n">
         <v>64.43000000000001</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="G17" s="7">
         <f>E17-F17</f>
@@ -2012,10 +2012,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="L17" s="5">
         <f>IF(K17=0,"",(J17-K17)/K17)</f>
@@ -2025,20 +2025,20 @@
         <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" s="7">
         <f>IF(J17=0,"",E17/J17)</f>
         <v/>
       </c>
       <c r="P17" s="6" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>39.9</v>
+        <v>0</v>
       </c>
       <c r="S17" s="2">
         <f>IF(AND('Engine Inputs'!E17=0,R17=0),"",IF('Engine Inputs'!E17=0,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&gt;Config!$B$2,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>19.25</v>
+        <v>0</v>
       </c>
       <c r="G18" s="9">
         <f>E18-F18</f>
@@ -2104,7 +2104,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" s="5">
         <f>IF(K18=0,"",(J18-K18)/K18)</f>
@@ -2121,10 +2121,10 @@
         <v/>
       </c>
       <c r="P18" s="6" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E19" s="7" t="n">
+        <v>186.6</v>
+      </c>
+      <c r="F19" s="7" t="n">
         <v>59.4</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>39.53</v>
       </c>
       <c r="G19" s="7">
         <f>E19-F19</f>
@@ -2187,10 +2187,10 @@
         <v/>
       </c>
       <c r="I19" s="7" t="n">
-        <v>93.12</v>
+        <v>42.33</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>3</v>
@@ -2200,10 +2200,10 @@
         <v/>
       </c>
       <c r="M19" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O19" s="7">
         <f>IF(J19=0,"",E19/J19)</f>
@@ -2216,7 +2216,7 @@
         <v>295</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>52.59</v>
+        <v>147.99</v>
       </c>
       <c r="S19" s="2">
         <f>IF(AND('Engine Inputs'!E19=0,R19=0),"",IF('Engine Inputs'!E19=0,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&gt;Config!$B$2,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E20" s="4" t="n">
+        <v>27.26</v>
+      </c>
+      <c r="F20" s="4" t="n">
         <v>33.82</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>53.47</v>
       </c>
       <c r="G20" s="4">
         <f>E20-F20</f>
@@ -2276,20 +2276,20 @@
         <v/>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11.13</v>
+        <v>136.51</v>
       </c>
       <c r="J20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>5</v>
       </c>
       <c r="L20" s="5">
         <f>IF(K20=0,"",(J20-K20)/K20)</f>
         <v/>
       </c>
       <c r="M20" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>4</v>
@@ -2299,13 +2299,13 @@
         <v/>
       </c>
       <c r="P20" s="6" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>33.82</v>
+        <v>27.26</v>
       </c>
       <c r="S20" s="2">
         <f>IF(AND('Engine Inputs'!E20=0,R20=0),"",IF('Engine Inputs'!E20=0,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&gt;Config!$B$2,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>0</v>
@@ -2423,12 +2423,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ElectricalSone UK</t>
+          <t>Homin GmbH</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0</v>
+        <v>33.58</v>
       </c>
       <c r="G22" s="7">
         <f>E22-F22</f>
@@ -2454,20 +2454,20 @@
         <v/>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0</v>
+        <v>15.34</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="5">
         <f>IF(K22=0,"",(J22-K22)/K22)</f>
         <v/>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>0</v>
@@ -2477,10 +2477,10 @@
         <v/>
       </c>
       <c r="P22" s="6" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="R22" s="7" t="n">
         <v>0</v>
@@ -2490,7 +2490,7 @@
         <v/>
       </c>
       <c r="T22" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="U22" s="7" t="n">
         <v>0</v>
@@ -2503,21 +2503,21 @@
         <f>IF(AND(F22=0,E22=0),"",IF(F22=0,"📈 Up",IF((E22-F22)/F22&gt;Config!$B$2,"📈 Up",IF((E22-F22)/F22&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X22" s="2" t="inlineStr">
-        <is>
-          <t>Kobiga</t>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t>— not assigned</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Homin GmbH</t>
+          <t>ElectricalSone UK</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>33.58</v>
+        <v>0</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>10.39</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7">
         <f>E23-F23</f>
@@ -2546,10 +2546,10 @@
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="5">
         <f>IF(K23=0,"",(J23-K23)/K23)</f>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" s="7">
         <f>IF(J23=0,"",E23/J23)</f>
@@ -2569,17 +2569,17 @@
         <v>167</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>35.36</v>
+        <v>0</v>
       </c>
       <c r="S23" s="2">
         <f>IF(AND('Engine Inputs'!E23=0,R23=0),"",IF('Engine Inputs'!E23=0,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&gt;Config!$B$2,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T23" s="6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U23" s="7" t="n">
         <v>0</v>
@@ -2592,9 +2592,9 @@
         <f>IF(AND(F23=0,E23=0),"",IF(F23=0,"📈 Up",IF((E23-F23)/F23&gt;Config!$B$2,"📈 Up",IF((E23-F23)/F23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>— not assigned</t>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>Kobiga</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E25" s="7" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
@@ -2833,10 +2833,10 @@
         <v/>
       </c>
       <c r="P26" s="6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R26" s="7" t="n">
         <v>0</v>
@@ -2882,13 +2882,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
         <v>6.64</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="G27" s="4">
         <f>E27-F27</f>
@@ -2902,10 +2902,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="L27" s="5">
         <f>IF(K27=0,"",(J27-K27)/K27)</f>
@@ -2915,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O27" s="4">
         <f>IF(J27=0,"",E27/J27)</f>
@@ -2928,7 +2928,7 @@
         <v>65</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>6.64</v>
+        <v>0</v>
       </c>
       <c r="S27" s="2">
         <f>IF(AND('Engine Inputs'!E27=0,R27=0),"",IF('Engine Inputs'!E27=0,"📈 Up",IF((R27-'Engine Inputs'!E27)/'Engine Inputs'!E27&gt;Config!$B$2,"📈 Up",IF((R27-'Engine Inputs'!E27)/'Engine Inputs'!E27&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
       <c r="E31" s="4" t="n">
         <v>0</v>
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46229</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="3">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
     </row>
     <row r="5">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>PH Sales 2026-07-25</t>
+          <t>PH Sales 2026-07-26</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>AH Sales 2026-07-25</t>
+          <t>AH Sales 2026-07-26</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>322.88</v>
+        <v>290.47</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>431.91</v>
+        <v>649.38</v>
       </c>
     </row>
     <row r="3">
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="D3" s="16" t="n">
-        <v>272.7</v>
+        <v>181.09</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>144.18</v>
+        <v>203.03</v>
       </c>
     </row>
     <row r="4">
@@ -3842,10 +3842,10 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>0</v>
+        <v>13.39</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>142.21</v>
+        <v>383.78</v>
       </c>
     </row>
     <row r="5">
@@ -3865,10 +3865,10 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>74.69</v>
+        <v>17.48</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>130.14</v>
+        <v>221.24</v>
       </c>
     </row>
     <row r="6">
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>41.28</v>
+        <v>25.58</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>205.44</v>
+        <v>371.61</v>
       </c>
     </row>
     <row r="7">
@@ -3943,47 +3943,47 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Huetten Lampen DE</t>
+          <t>Coventry Lights</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>21.31</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>156.8</v>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>319.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Coventry Lights</t>
+          <t>Huetten Lampen DE</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>204.19</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>359.82</v>
       </c>
     </row>
     <row r="11">
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>103.56</v>
+        <v>19.3</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>42.51</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="12">
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>84.26000000000001</v>
+        <v>177.04</v>
       </c>
     </row>
     <row r="13">
@@ -4052,7 +4052,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>24.54</v>
+        <v>66.81999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -4121,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>0</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="18">
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>17.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>35.57</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="20">
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>53.47</v>
+        <v>33.82</v>
       </c>
     </row>
     <row r="21">
@@ -4242,12 +4242,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ElectricalSone UK</t>
+          <t>Homin GmbH</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4259,18 +4259,18 @@
         <v>0</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>0</v>
+        <v>35.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Homin GmbH</t>
+          <t>ElectricalSone UK</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -4282,7 +4282,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>10.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4374,7 +4374,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>0</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="28">
@@ -4582,7 +4582,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Generated 2026-07-27.  "Today" = 2026-07-26.  "Yesterday" = 2026-07-25.  Same Day LY = 2025-07-26.</t>
+          <t xml:space="preserve">  Generated 2026-07-28.  "Today" = 2026-07-27.  "Yesterday" = 2026-07-26.  Same Day LY = 2025-07-27.</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-07-26</t>
+          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-07-27</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2026-07-26 was a Sunday; 2025-07-26 was a Saturday). Day-of-week effects are present in this comparison.</t>
+          <t xml:space="preserve">  (2026-07-27 was a Monday; 2025-07-27 was a Sunday). Day-of-week effects are present in this comparison.</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Notes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Sales Track'!$A$1:$X$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Daily Sales Track'!$A$1:$X$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1149.82</v>
+        <v>1128.69</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>923.54</v>
+        <v>932.88</v>
       </c>
       <c r="G2" s="4">
         <f>E2-F2</f>
@@ -674,46 +674,46 @@
         <v/>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1447.52</v>
+        <v>1070.98</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="L2" s="5">
         <f>IF(K2=0,"",(J2-K2)/K2)</f>
         <v/>
       </c>
       <c r="M2" s="6" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="O2" s="4">
         <f>IF(J2=0,"",E2/J2)</f>
         <v/>
       </c>
       <c r="P2" s="6" t="n">
-        <v>2861</v>
+        <v>3036</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>1609</v>
+        <v>1731</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>534.37</v>
+        <v>568.36</v>
       </c>
       <c r="S2" s="2">
         <f>IF(AND('Engine Inputs'!E2=0,R2=0),"",IF('Engine Inputs'!E2=0,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&gt;Config!$B$2,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T2" s="6" t="n">
-        <v>1252</v>
+        <v>1305</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>583.11</v>
+        <v>548.76</v>
       </c>
       <c r="V2" s="2">
         <f>IF(AND('Engine Inputs'!D2=0,U2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>501.7</v>
+        <v>353.49</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>376.56</v>
+        <v>549.5</v>
       </c>
       <c r="G3" s="4">
         <f>E3-F3</f>
@@ -763,46 +763,46 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>438.94</v>
+        <v>607.8200000000001</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="5">
         <f>IF(K3=0,"",(J3-K3)/K3)</f>
         <v/>
       </c>
       <c r="M3" s="6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="O3" s="4">
         <f>IF(J3=0,"",E3/J3)</f>
         <v/>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1522</v>
+        <v>1678</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>971</v>
+        <v>1081</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>190.42</v>
+        <v>222.27</v>
       </c>
       <c r="S3" s="2">
         <f>IF(AND('Engine Inputs'!E3=0,R3=0),"",IF('Engine Inputs'!E3=0,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&gt;Config!$B$2,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T3" s="6" t="n">
-        <v>551</v>
+        <v>597</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>329.62</v>
+        <v>147.44</v>
       </c>
       <c r="V3" s="2">
         <f>IF(AND('Engine Inputs'!D3=0,U3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>274.41</v>
+        <v>340.06</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>436.29</v>
+        <v>259.33</v>
       </c>
       <c r="G4" s="7">
         <f>E4-F4</f>
@@ -852,46 +852,46 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>381.39</v>
+        <v>396.06</v>
       </c>
       <c r="J4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>10</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>11</v>
       </c>
       <c r="L4" s="5">
         <f>IF(K4=0,"",(J4-K4)/K4)</f>
         <v/>
       </c>
       <c r="M4" s="6" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="O4" s="7">
         <f>IF(J4=0,"",E4/J4)</f>
         <v/>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1357</v>
+        <v>1441</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>1141</v>
+        <v>1209</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>208.91</v>
+        <v>273.58</v>
       </c>
       <c r="S4" s="2">
         <f>IF(AND('Engine Inputs'!E4=0,R4=0),"",IF('Engine Inputs'!E4=0,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&gt;Config!$B$2,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T4" s="6" t="n">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>26.78</v>
+        <v>16.7</v>
       </c>
       <c r="V4" s="2">
         <f>IF(AND('Engine Inputs'!D4=0,U4=0),"",IF('Engine Inputs'!D4=0,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&gt;Config!$B$2,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>287.49</v>
+        <v>289.57</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>234.28</v>
+        <v>300.45</v>
       </c>
       <c r="G5" s="4">
         <f>E5-F5</f>
@@ -941,46 +941,46 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>259.85</v>
+        <v>322.23</v>
       </c>
       <c r="J5" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>15</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>12</v>
       </c>
       <c r="L5" s="5">
         <f>IF(K5=0,"",(J5-K5)/K5)</f>
         <v/>
       </c>
       <c r="M5" s="6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="O5" s="4">
         <f>IF(J5=0,"",E5/J5)</f>
         <v/>
       </c>
       <c r="P5" s="6" t="n">
-        <v>1158</v>
+        <v>1187</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>700</v>
+        <v>718</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>200.75</v>
+        <v>206.2</v>
       </c>
       <c r="S5" s="2">
         <f>IF(AND('Engine Inputs'!E5=0,R5=0),"",IF('Engine Inputs'!E5=0,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&gt;Config!$B$2,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T5" s="6" t="n">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>92.58</v>
+        <v>78.81</v>
       </c>
       <c r="V5" s="2">
         <f>IF(AND('Engine Inputs'!D5=0,U5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>349.81</v>
+        <v>275.07</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>401.78</v>
+        <v>422.04</v>
       </c>
       <c r="G6" s="7">
         <f>E6-F6</f>
@@ -1030,46 +1030,46 @@
         <v/>
       </c>
       <c r="I6" s="7" t="n">
-        <v>373.43</v>
+        <v>273</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L6" s="5">
         <f>IF(K6=0,"",(J6-K6)/K6)</f>
         <v/>
       </c>
       <c r="M6" s="6" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O6" s="7">
         <f>IF(J6=0,"",E6/J6)</f>
         <v/>
       </c>
       <c r="P6" s="6" t="n">
-        <v>637</v>
+        <v>653</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>292.05</v>
+        <v>223.46</v>
       </c>
       <c r="S6" s="2">
         <f>IF(AND('Engine Inputs'!E6=0,R6=0),"",IF('Engine Inputs'!E6=0,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&gt;Config!$B$2,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T6" s="6" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>63.33</v>
+        <v>48.65</v>
       </c>
       <c r="V6" s="2">
         <f>IF(AND('Engine Inputs'!D6=0,U6=0),"",IF('Engine Inputs'!D6=0,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&gt;Config!$B$2,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -1142,10 +1142,10 @@
         <v/>
       </c>
       <c r="P7" s="6" t="n">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="Q7" s="6" t="n">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="R7" s="7" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1231,10 +1231,10 @@
         <v/>
       </c>
       <c r="P8" s="6" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="R8" s="7" t="n">
         <v>0</v>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>190.91</v>
+        <v>189.64</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>325.97</v>
+        <v>256.34</v>
       </c>
       <c r="G9" s="4">
         <f>E9-F9</f>
@@ -1297,13 +1297,13 @@
         <v/>
       </c>
       <c r="I9" s="4" t="n">
-        <v>169.03</v>
+        <v>229.19</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>9</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="L9" s="5">
         <f>IF(K9=0,"",(J9-K9)/K9)</f>
@@ -1313,20 +1313,20 @@
         <v>16</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O9" s="4">
         <f>IF(J9=0,"",E9/J9)</f>
         <v/>
       </c>
       <c r="P9" s="6" t="n">
-        <v>541</v>
+        <v>579</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>541</v>
+        <v>579</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>187.42</v>
+        <v>186.65</v>
       </c>
       <c r="S9" s="2">
         <f>IF(AND('Engine Inputs'!E9=0,R9=0),"",IF('Engine Inputs'!E9=0,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&gt;Config!$B$2,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>565.01</v>
+        <v>651.92</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>362.2</v>
+        <v>179</v>
       </c>
       <c r="G10" s="7">
         <f>E10-F10</f>
@@ -1386,46 +1386,46 @@
         <v/>
       </c>
       <c r="I10" s="7" t="n">
-        <v>393.59</v>
+        <v>520.39</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L10" s="5">
         <f>IF(K10=0,"",(J10-K10)/K10)</f>
         <v/>
       </c>
       <c r="M10" s="6" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="O10" s="7">
         <f>IF(J10=0,"",E10/J10)</f>
         <v/>
       </c>
       <c r="P10" s="6" t="n">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>574.1900000000001</v>
+        <v>608.15</v>
       </c>
       <c r="S10" s="2">
         <f>IF(AND('Engine Inputs'!E10=0,R10=0),"",IF('Engine Inputs'!E10=0,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&gt;Config!$B$2,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T10" s="6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>19.44</v>
+        <v>47.37</v>
       </c>
       <c r="V10" s="2">
         <f>IF(AND('Engine Inputs'!D10=0,U10=0),"",IF('Engine Inputs'!D10=0,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&gt;Config!$B$2,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1444,29 +1444,29 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ElectricalSone UK</t>
+          <t>DC Transformer</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>248.04</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>95.29000000000001</v>
-      </c>
-      <c r="G11" s="7">
+        <v>46236</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="G11" s="4">
         <f>E11-F11</f>
         <v/>
       </c>
@@ -1474,46 +1474,46 @@
         <f>IF(F11=0,"",(E11-F11)/F11)</f>
         <v/>
       </c>
-      <c r="I11" s="7" t="n">
-        <v>244.84</v>
+      <c r="I11" s="4" t="n">
+        <v>98.73</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L11" s="5">
         <f>IF(K11=0,"",(J11-K11)/K11)</f>
         <v/>
       </c>
       <c r="M11" s="6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="O11" s="7">
+        <v>11</v>
+      </c>
+      <c r="O11" s="4">
         <f>IF(J11=0,"",E11/J11)</f>
         <v/>
       </c>
       <c r="P11" s="6" t="n">
-        <v>486</v>
+        <v>508</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>450</v>
-      </c>
-      <c r="R11" s="7" t="n">
-        <v>174.97</v>
+        <v>508</v>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>50.29</v>
       </c>
       <c r="S11" s="2">
         <f>IF(AND('Engine Inputs'!E11=0,R11=0),"",IF('Engine Inputs'!E11=0,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&gt;Config!$B$2,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T11" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="U11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="2">
@@ -1524,38 +1524,38 @@
         <f>IF(AND(F11=0,E11=0),"",IF(F11=0,"📈 Up",IF((E11-F11)/F11&gt;Config!$B$2,"📈 Up",IF((E11-F11)/F11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X11" s="2" t="inlineStr">
-        <is>
-          <t>Kobiga</t>
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t>— not assigned</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Vintage Interior</t>
+          <t>ElectricalSone UK</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>38.37</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>170.78</v>
-      </c>
-      <c r="G12" s="4">
+        <v>46236</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>17.94</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>29.61</v>
+      </c>
+      <c r="G12" s="7">
         <f>E12-F12</f>
         <v/>
       </c>
@@ -1563,46 +1563,46 @@
         <f>IF(F12=0,"",(E12-F12)/F12)</f>
         <v/>
       </c>
-      <c r="I12" s="4" t="n">
-        <v>216.71</v>
+      <c r="I12" s="7" t="n">
+        <v>40.25</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="L12" s="5">
         <f>IF(K12=0,"",(J12-K12)/K12)</f>
         <v/>
       </c>
       <c r="M12" s="6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="O12" s="4">
+        <v>1</v>
+      </c>
+      <c r="O12" s="7">
         <f>IF(J12=0,"",E12/J12)</f>
         <v/>
       </c>
       <c r="P12" s="6" t="n">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="Q12" s="6" t="n">
-        <v>474</v>
-      </c>
-      <c r="R12" s="4" t="n">
-        <v>38.37</v>
+        <v>454</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>10.66</v>
       </c>
       <c r="S12" s="2">
         <f>IF(AND('Engine Inputs'!E12=0,R12=0),"",IF('Engine Inputs'!E12=0,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&gt;Config!$B$2,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="U12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="2">
@@ -1613,16 +1613,16 @@
         <f>IF(AND(F12=0,E12=0),"",IF(F12=0,"📈 Up",IF((E12-F12)/F12&gt;Config!$B$2,"📈 Up",IF((E12-F12)/F12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X12" s="8" t="inlineStr">
-        <is>
-          <t>— not assigned</t>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Kobiga</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DC Transformer</t>
+          <t>Vintage Interior</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>17.86</v>
+        <v>50.82</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>64.86</v>
+        <v>89.38</v>
       </c>
       <c r="G13" s="4">
         <f>E13-F13</f>
@@ -1653,10 +1653,10 @@
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>67.09</v>
+        <v>50.4</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>8</v>
@@ -1666,23 +1666,23 @@
         <v/>
       </c>
       <c r="M13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="N13" s="6" t="n">
         <v>6</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="O13" s="4">
         <f>IF(J13=0,"",E13/J13)</f>
         <v/>
       </c>
       <c r="P13" s="6" t="n">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>18.22</v>
+        <v>52.48</v>
       </c>
       <c r="S13" s="2">
         <f>IF(AND('Engine Inputs'!E13=0,R13=0),"",IF('Engine Inputs'!E13=0,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&gt;Config!$B$2,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>15.6</v>
+        <v>25.63</v>
       </c>
       <c r="F14" s="4" t="n">
         <v>0</v>
@@ -1742,10 +1742,10 @@
         <v/>
       </c>
       <c r="I14" s="4" t="n">
-        <v>135.1</v>
+        <v>45.37</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
@@ -1755,23 +1755,23 @@
         <v/>
       </c>
       <c r="M14" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O14" s="4">
         <f>IF(J14=0,"",E14/J14)</f>
         <v/>
       </c>
       <c r="P14" s="6" t="n">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>405</v>
+        <v>433</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>17.34</v>
+        <v>25.63</v>
       </c>
       <c r="S14" s="2">
         <f>IF(AND('Engine Inputs'!E14=0,R14=0),"",IF('Engine Inputs'!E14=0,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&gt;Config!$B$2,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1805,24 +1805,24 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="E15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9">
+        <v>46236</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7">
         <f>E15-F15</f>
         <v/>
       </c>
@@ -1830,7 +1830,7 @@
         <f>IF(F15=0,"",(E15-F15)/F15)</f>
         <v/>
       </c>
-      <c r="I15" s="9" t="n">
+      <c r="I15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
@@ -1849,17 +1849,17 @@
       <c r="N15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="7">
         <f>IF(J15=0,"",E15/J15)</f>
         <v/>
       </c>
       <c r="P15" s="6" t="n">
-        <v>393</v>
+        <v>431</v>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>355</v>
-      </c>
-      <c r="R15" s="9" t="n">
+        <v>431</v>
+      </c>
+      <c r="R15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S15" s="2">
@@ -1867,9 +1867,9 @@
         <v/>
       </c>
       <c r="T15" s="6" t="n">
-        <v>38</v>
-      </c>
-      <c r="U15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="2">
@@ -1889,7 +1889,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ElectricalSone UK</t>
+          <t>LEDSone UK</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
         <v/>
       </c>
       <c r="P16" s="6" t="n">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>0</v>
@@ -1956,7 +1956,7 @@
         <v/>
       </c>
       <c r="T16" s="6" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="U16" s="9" t="n">
         <v>0</v>
@@ -1971,36 +1971,36 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>Kobiga</t>
+          <t>Sharmilan</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LEDSone UK</t>
+          <t>ElectricalSone UK</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>64.43000000000001</v>
-      </c>
-      <c r="G17" s="7">
+        <v>46236</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>42.37</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
         <f>E17-F17</f>
         <v/>
       </c>
@@ -2008,14 +2008,14 @@
         <f>IF(F17=0,"",(E17-F17)/F17)</f>
         <v/>
       </c>
-      <c r="I17" s="7" t="n">
+      <c r="I17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
         <f>IF(K17=0,"",(J17-K17)/K17)</f>
@@ -2025,29 +2025,29 @@
         <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="7">
+        <v>2</v>
+      </c>
+      <c r="O17" s="9">
         <f>IF(J17=0,"",E17/J17)</f>
         <v/>
       </c>
       <c r="P17" s="6" t="n">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>369</v>
-      </c>
-      <c r="R17" s="7" t="n">
-        <v>0</v>
+        <v>377</v>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>39.49</v>
       </c>
       <c r="S17" s="2">
         <f>IF(AND('Engine Inputs'!E17=0,R17=0),"",IF('Engine Inputs'!E17=0,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&gt;Config!$B$2,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V17" s="2">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>Sharmilan</t>
+          <t>Kobiga</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>186.6</v>
+        <v>80.16</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>59.4</v>
+        <v>126.54</v>
       </c>
       <c r="G19" s="7">
         <f>E19-F19</f>
@@ -2187,23 +2187,23 @@
         <v/>
       </c>
       <c r="I19" s="7" t="n">
-        <v>42.33</v>
+        <v>86.63</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L19" s="5">
         <f>IF(K19=0,"",(J19-K19)/K19)</f>
         <v/>
       </c>
       <c r="M19" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O19" s="7">
         <f>IF(J19=0,"",E19/J19)</f>
@@ -2216,7 +2216,7 @@
         <v>295</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>147.99</v>
+        <v>67.37</v>
       </c>
       <c r="S19" s="2">
         <f>IF(AND('Engine Inputs'!E19=0,R19=0),"",IF('Engine Inputs'!E19=0,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&gt;Config!$B$2,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>27.26</v>
+        <v>6.49</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>33.82</v>
+        <v>20.37</v>
       </c>
       <c r="G20" s="4">
         <f>E20-F20</f>
@@ -2276,36 +2276,36 @@
         <v/>
       </c>
       <c r="I20" s="4" t="n">
-        <v>136.51</v>
+        <v>56.94</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L20" s="5">
         <f>IF(K20=0,"",(J20-K20)/K20)</f>
         <v/>
       </c>
       <c r="M20" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O20" s="4">
         <f>IF(J20=0,"",E20/J20)</f>
         <v/>
       </c>
       <c r="P20" s="6" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>27.26</v>
+        <v>6.49</v>
       </c>
       <c r="S20" s="2">
         <f>IF(AND('Engine Inputs'!E20=0,R20=0),"",IF('Engine Inputs'!E20=0,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&gt;Config!$B$2,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E21" s="10" t="n">
         <v>0</v>
@@ -2423,12 +2423,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Homin GmbH</t>
+          <t>LEDSone UK</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0</v>
+        <v>102.98</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>33.58</v>
+        <v>0</v>
       </c>
       <c r="G22" s="7">
         <f>E22-F22</f>
@@ -2454,36 +2454,36 @@
         <v/>
       </c>
       <c r="I22" s="7" t="n">
-        <v>15.34</v>
+        <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" s="5">
         <f>IF(K22=0,"",(J22-K22)/K22)</f>
         <v/>
       </c>
       <c r="M22" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O22" s="7">
         <f>IF(J22=0,"",E22/J22)</f>
         <v/>
       </c>
       <c r="P22" s="6" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="R22" s="7" t="n">
-        <v>0</v>
+        <v>71.28</v>
       </c>
       <c r="S22" s="2">
         <f>IF(AND('Engine Inputs'!E22=0,R22=0),"",IF('Engine Inputs'!E22=0,"📈 Up",IF((R22-'Engine Inputs'!E22)/'Engine Inputs'!E22&gt;Config!$B$2,"📈 Up",IF((R22-'Engine Inputs'!E22)/'Engine Inputs'!E22&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2503,21 +2503,21 @@
         <f>IF(AND(F22=0,E22=0),"",IF(F22=0,"📈 Up",IF((E22-F22)/F22&gt;Config!$B$2,"📈 Up",IF((E22-F22)/F22&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t>— not assigned</t>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>Sharmilan</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ElectricalSone UK</t>
+          <t>Homin GmbH</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>0</v>
+        <v>47.98</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0</v>
+        <v>10.99</v>
       </c>
       <c r="G23" s="7">
         <f>E23-F23</f>
@@ -2543,43 +2543,43 @@
         <v/>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0</v>
+        <v>22.95</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="5">
         <f>IF(K23=0,"",(J23-K23)/K23)</f>
         <v/>
       </c>
       <c r="M23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" s="7">
         <f>IF(J23=0,"",E23/J23)</f>
         <v/>
       </c>
       <c r="P23" s="6" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>0</v>
+        <v>47.98</v>
       </c>
       <c r="S23" s="2">
         <f>IF(AND('Engine Inputs'!E23=0,R23=0),"",IF('Engine Inputs'!E23=0,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&gt;Config!$B$2,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T23" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="U23" s="7" t="n">
         <v>0</v>
@@ -2592,9 +2592,9 @@
         <f>IF(AND(F23=0,E23=0),"",IF(F23=0,"📈 Up",IF((E23-F23)/F23&gt;Config!$B$2,"📈 Up",IF((E23-F23)/F23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X23" s="2" t="inlineStr">
-        <is>
-          <t>Kobiga</t>
+      <c r="X23" s="8" t="inlineStr">
+        <is>
+          <t>— not assigned</t>
         </is>
       </c>
     </row>
@@ -2606,24 +2606,24 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="10">
+        <v>46236</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7">
         <f>E24-F24</f>
         <v/>
       </c>
@@ -2631,7 +2631,7 @@
         <f>IF(F24=0,"",(E24-F24)/F24)</f>
         <v/>
       </c>
-      <c r="I24" s="10" t="n">
+      <c r="I24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
@@ -2650,17 +2650,17 @@
       <c r="N24" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="10">
+      <c r="O24" s="7">
         <f>IF(J24=0,"",E24/J24)</f>
         <v/>
       </c>
       <c r="P24" s="6" t="n">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="Q24" s="6" t="n">
-        <v>154</v>
-      </c>
-      <c r="R24" s="10" t="n">
+        <v>151</v>
+      </c>
+      <c r="R24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S24" s="2">
@@ -2668,9 +2668,9 @@
         <v/>
       </c>
       <c r="T24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="U24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V24" s="2">
@@ -2690,29 +2690,29 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>LEDSone UK</t>
+          <t>ElectricalSone UK</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="7">
+        <v>46236</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="10">
         <f>E25-F25</f>
         <v/>
       </c>
@@ -2720,7 +2720,7 @@
         <f>IF(F25=0,"",(E25-F25)/F25)</f>
         <v/>
       </c>
-      <c r="I25" s="7" t="n">
+      <c r="I25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
@@ -2739,17 +2739,17 @@
       <c r="N25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="7">
+      <c r="O25" s="10">
         <f>IF(J25=0,"",E25/J25)</f>
         <v/>
       </c>
       <c r="P25" s="6" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="Q25" s="6" t="n">
-        <v>137</v>
-      </c>
-      <c r="R25" s="7" t="n">
+        <v>154</v>
+      </c>
+      <c r="R25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="S25" s="2">
@@ -2759,7 +2759,7 @@
       <c r="T25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U25" s="7" t="n">
+      <c r="U25" s="10" t="n">
         <v>0</v>
       </c>
       <c r="V25" s="2">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>Sharmilan</t>
+          <t>Kobiga</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
@@ -2833,10 +2833,10 @@
         <v/>
       </c>
       <c r="P26" s="6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="R26" s="7" t="n">
         <v>0</v>
@@ -2882,13 +2882,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.64</v>
+        <v>0</v>
       </c>
       <c r="G27" s="4">
         <f>E27-F27</f>
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="5">
         <f>IF(K27=0,"",(J27-K27)/K27)</f>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
@@ -3011,10 +3011,10 @@
         <v/>
       </c>
       <c r="P28" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R28" s="7" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -3135,29 +3135,29 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Huetten Lampen DE</t>
+          <t>Sunsone</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="7">
+        <v>46236</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
         <f>E30-F30</f>
         <v/>
       </c>
@@ -3165,7 +3165,7 @@
         <f>IF(F30=0,"",(E30-F30)/F30)</f>
         <v/>
       </c>
-      <c r="I30" s="7" t="n">
+      <c r="I30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
@@ -3184,17 +3184,17 @@
       <c r="N30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="7">
+      <c r="O30" s="9">
         <f>IF(J30=0,"",E30/J30)</f>
         <v/>
       </c>
       <c r="P30" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="R30" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S30" s="2">
@@ -3204,7 +3204,7 @@
       <c r="T30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="7" t="n">
+      <c r="U30" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2">
@@ -3215,38 +3215,38 @@
         <f>IF(AND(F30=0,E30=0),"",IF(F30=0,"📈 Up",IF((E30-F30)/F30&gt;Config!$B$2,"📈 Up",IF((E30-F30)/F30&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X30" s="2" t="inlineStr">
-        <is>
-          <t>Jarsini</t>
+      <c r="X30" s="8" t="inlineStr">
+        <is>
+          <t>— not assigned</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LEDSone DE</t>
+          <t>Huetten Lampen DE</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46230</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="4">
+        <v>46236</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="7">
         <f>E31-F31</f>
         <v/>
       </c>
@@ -3254,7 +3254,7 @@
         <f>IF(F31=0,"",(E31-F31)/F31)</f>
         <v/>
       </c>
-      <c r="I31" s="4" t="n">
+      <c r="I31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
@@ -3273,7 +3273,7 @@
       <c r="N31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O31" s="4">
+      <c r="O31" s="7">
         <f>IF(J31=0,"",E31/J31)</f>
         <v/>
       </c>
@@ -3283,7 +3283,7 @@
       <c r="Q31" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="4" t="n">
+      <c r="R31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S31" s="2">
@@ -3293,7 +3293,7 @@
       <c r="T31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U31" s="4" t="n">
+      <c r="U31" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V31" s="2">
@@ -3310,8 +3310,186 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>LEDSone DE</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4">
+        <f>E32-F32</f>
+        <v/>
+      </c>
+      <c r="H32" s="5">
+        <f>IF(F32=0,"",(E32-F32)/F32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>6.46</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="5">
+        <f>IF(K32=0,"",(J32-K32)/K32)</f>
+        <v/>
+      </c>
+      <c r="M32" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="4">
+        <f>IF(J32=0,"",E32/J32)</f>
+        <v/>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
+        <f>IF(AND('Engine Inputs'!E32=0,R32=0),"",IF('Engine Inputs'!E32=0,"📈 Up",IF((R32-'Engine Inputs'!E32)/'Engine Inputs'!E32&gt;Config!$B$2,"📈 Up",IF((R32-'Engine Inputs'!E32)/'Engine Inputs'!E32&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T32" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2">
+        <f>IF(AND('Engine Inputs'!D32=0,U32=0),"",IF('Engine Inputs'!D32=0,"📈 Up",IF((U32-'Engine Inputs'!D32)/'Engine Inputs'!D32&gt;Config!$B$2,"📈 Up",IF((U32-'Engine Inputs'!D32)/'Engine Inputs'!D32&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W32" s="2">
+        <f>IF(AND(F32=0,E32=0),"",IF(F32=0,"📈 Up",IF((E32-F32)/F32&gt;Config!$B$2,"📈 Up",IF((E32-F32)/F32&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>Jarsini</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ElectricalSone UK</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>46236</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="7">
+        <f>E33-F33</f>
+        <v/>
+      </c>
+      <c r="H33" s="5">
+        <f>IF(F33=0,"",(E33-F33)/F33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="5">
+        <f>IF(K33=0,"",(J33-K33)/K33)</f>
+        <v/>
+      </c>
+      <c r="M33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="7">
+        <f>IF(J33=0,"",E33/J33)</f>
+        <v/>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
+        <f>IF(AND('Engine Inputs'!E33=0,R33=0),"",IF('Engine Inputs'!E33=0,"📈 Up",IF((R33-'Engine Inputs'!E33)/'Engine Inputs'!E33&gt;Config!$B$2,"📈 Up",IF((R33-'Engine Inputs'!E33)/'Engine Inputs'!E33&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="T33" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2">
+        <f>IF(AND('Engine Inputs'!D33=0,U33=0),"",IF('Engine Inputs'!D33=0,"📈 Up",IF((U33-'Engine Inputs'!D33)/'Engine Inputs'!D33&gt;Config!$B$2,"📈 Up",IF((U33-'Engine Inputs'!D33)/'Engine Inputs'!D33&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="W33" s="2">
+        <f>IF(AND(F33=0,E33=0),"",IF(F33=0,"📈 Up",IF((E33-F33)/F33&gt;Config!$B$2,"📈 Up",IF((E33-F33)/F33&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
+        <v/>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>Kobiga</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X31"/>
+  <autoFilter ref="A1:X33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3343,7 +3521,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46230</v>
+        <v>46236</v>
       </c>
     </row>
     <row r="3">
@@ -3353,7 +3531,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46231</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="5">
@@ -3375,7 +3553,7 @@
         </is>
       </c>
       <c r="B6" s="6">
-        <f>COUNTA('Daily Sales Track'!A2:A31)</f>
+        <f>COUNTA('Daily Sales Track'!A2:A33)</f>
         <v/>
       </c>
     </row>
@@ -3386,7 +3564,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$E$2:$E$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"GBP",'Daily Sales Track'!$E$2:$E$33)</f>
         <v/>
       </c>
     </row>
@@ -3397,7 +3575,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$E$2:$E$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"EUR",'Daily Sales Track'!$E$2:$E$33)</f>
         <v/>
       </c>
     </row>
@@ -3408,7 +3586,7 @@
         </is>
       </c>
       <c r="B9" s="9">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$E$2:$E$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"USD",'Daily Sales Track'!$E$2:$E$33)</f>
         <v/>
       </c>
     </row>
@@ -3419,7 +3597,7 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$E$2:$E$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"CAD",'Daily Sales Track'!$E$2:$E$33)</f>
         <v/>
       </c>
     </row>
@@ -3430,7 +3608,7 @@
         </is>
       </c>
       <c r="B11" s="4">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$F$2:$F$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"GBP",'Daily Sales Track'!$F$2:$F$33)</f>
         <v/>
       </c>
     </row>
@@ -3441,7 +3619,7 @@
         </is>
       </c>
       <c r="B12" s="7">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$F$2:$F$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"EUR",'Daily Sales Track'!$F$2:$F$33)</f>
         <v/>
       </c>
     </row>
@@ -3452,7 +3630,7 @@
         </is>
       </c>
       <c r="B13" s="9">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$F$2:$F$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"USD",'Daily Sales Track'!$F$2:$F$33)</f>
         <v/>
       </c>
     </row>
@@ -3463,7 +3641,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$F$2:$F$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"CAD",'Daily Sales Track'!$F$2:$F$33)</f>
         <v/>
       </c>
     </row>
@@ -3474,7 +3652,7 @@
         </is>
       </c>
       <c r="B15" s="4">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$I$2:$I$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"GBP",'Daily Sales Track'!$I$2:$I$33)</f>
         <v/>
       </c>
     </row>
@@ -3485,7 +3663,7 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$I$2:$I$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"EUR",'Daily Sales Track'!$I$2:$I$33)</f>
         <v/>
       </c>
     </row>
@@ -3496,7 +3674,7 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$I$2:$I$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"USD",'Daily Sales Track'!$I$2:$I$33)</f>
         <v/>
       </c>
     </row>
@@ -3507,7 +3685,7 @@
         </is>
       </c>
       <c r="B18" s="10">
-        <f>SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$I$2:$I$31)</f>
+        <f>SUMIF('Daily Sales Track'!$C$2:$C$33,"CAD",'Daily Sales Track'!$I$2:$I$33)</f>
         <v/>
       </c>
     </row>
@@ -3562,7 +3740,7 @@
         </is>
       </c>
       <c r="B23" s="6">
-        <f>SUM('Daily Sales Track'!J2:J31)</f>
+        <f>SUM('Daily Sales Track'!J2:J33)</f>
         <v/>
       </c>
     </row>
@@ -3573,7 +3751,7 @@
         </is>
       </c>
       <c r="B24" s="6">
-        <f>SUM('Daily Sales Track'!K2:K31)</f>
+        <f>SUM('Daily Sales Track'!K2:K33)</f>
         <v/>
       </c>
     </row>
@@ -3584,7 +3762,7 @@
         </is>
       </c>
       <c r="B25" s="6">
-        <f>SUM('Daily Sales Track'!N2:N31)</f>
+        <f>SUM('Daily Sales Track'!N2:N33)</f>
         <v/>
       </c>
     </row>
@@ -3595,7 +3773,7 @@
         </is>
       </c>
       <c r="B26" s="4">
-        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$J$2:$J$31)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$E$2:$E$31)/SUMIF('Daily Sales Track'!$C$2:$C$31,"GBP",'Daily Sales Track'!$J$2:$J$31))</f>
+        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$33,"GBP",'Daily Sales Track'!$J$2:$J$33)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$33,"GBP",'Daily Sales Track'!$E$2:$E$33)/SUMIF('Daily Sales Track'!$C$2:$C$33,"GBP",'Daily Sales Track'!$J$2:$J$33))</f>
         <v/>
       </c>
     </row>
@@ -3606,7 +3784,7 @@
         </is>
       </c>
       <c r="B27" s="7">
-        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$J$2:$J$31)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$E$2:$E$31)/SUMIF('Daily Sales Track'!$C$2:$C$31,"EUR",'Daily Sales Track'!$J$2:$J$31))</f>
+        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$33,"EUR",'Daily Sales Track'!$J$2:$J$33)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$33,"EUR",'Daily Sales Track'!$E$2:$E$33)/SUMIF('Daily Sales Track'!$C$2:$C$33,"EUR",'Daily Sales Track'!$J$2:$J$33))</f>
         <v/>
       </c>
     </row>
@@ -3617,7 +3795,7 @@
         </is>
       </c>
       <c r="B28" s="9">
-        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$J$2:$J$31)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$E$2:$E$31)/SUMIF('Daily Sales Track'!$C$2:$C$31,"USD",'Daily Sales Track'!$J$2:$J$31))</f>
+        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$33,"USD",'Daily Sales Track'!$J$2:$J$33)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$33,"USD",'Daily Sales Track'!$E$2:$E$33)/SUMIF('Daily Sales Track'!$C$2:$C$33,"USD",'Daily Sales Track'!$J$2:$J$33))</f>
         <v/>
       </c>
     </row>
@@ -3628,7 +3806,7 @@
         </is>
       </c>
       <c r="B29" s="10">
-        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$J$2:$J$31)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$E$2:$E$31)/SUMIF('Daily Sales Track'!$C$2:$C$31,"CAD",'Daily Sales Track'!$J$2:$J$31))</f>
+        <f>IF(SUMIF('Daily Sales Track'!$C$2:$C$33,"CAD",'Daily Sales Track'!$J$2:$J$33)=0,"",SUMIF('Daily Sales Track'!$C$2:$C$33,"CAD",'Daily Sales Track'!$E$2:$E$33)/SUMIF('Daily Sales Track'!$C$2:$C$33,"CAD",'Daily Sales Track'!$J$2:$J$33))</f>
         <v/>
       </c>
     </row>
@@ -3737,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3765,17 +3943,17 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>PH Sales 2026-07-26</t>
+          <t>PH Sales 2026-08-01</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>AH Sales 2026-07-26</t>
+          <t>AH Sales 2026-08-01</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
         <is>
-          <t>Prior-day (R-2) AH / PH sales - these drive the AH Sales Trend and PH Sales Trend columns. Rows 2..31 align 1:1 with 'Daily Sales Track' rows 2..31; do not sort or insert rows on either sheet independently.</t>
+          <t>Prior-day (R-2) AH / PH sales - these drive the AH Sales Trend and PH Sales Trend columns. Rows 2..33 align 1:1 with 'Daily Sales Track' rows 2..33; do not sort or insert rows on either sheet independently.</t>
         </is>
       </c>
     </row>
@@ -3796,10 +3974,10 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>290.47</v>
+        <v>684.66</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>649.38</v>
+        <v>259.71</v>
       </c>
     </row>
     <row r="3">
@@ -3819,10 +3997,10 @@
         </is>
       </c>
       <c r="D3" s="16" t="n">
-        <v>181.09</v>
+        <v>296.46</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>203.03</v>
+        <v>275.49</v>
       </c>
     </row>
     <row r="4">
@@ -3842,10 +4020,10 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>13.39</v>
+        <v>37.57</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>383.78</v>
+        <v>152.71</v>
       </c>
     </row>
     <row r="5">
@@ -3865,10 +4043,10 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>17.48</v>
+        <v>134.89</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>221.24</v>
+        <v>142.53</v>
       </c>
     </row>
     <row r="6">
@@ -3888,10 +4066,10 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>25.58</v>
+        <v>0</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>371.61</v>
+        <v>429.05</v>
       </c>
     </row>
     <row r="7">
@@ -3960,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>319.73</v>
+        <v>228.49</v>
       </c>
     </row>
     <row r="10">
@@ -3980,62 +4158,62 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>10.34</v>
+        <v>27.53</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>359.82</v>
+        <v>149.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ElectricalSone UK</t>
+          <t>DC Transformer</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>61.37</v>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>47.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Vintage Interior</t>
+          <t>ElectricalSone UK</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>GBP</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>177.04</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>14.97</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DC Transformer</t>
+          <t>Vintage Interior</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -4052,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>66.81999999999999</v>
+        <v>87.95</v>
       </c>
     </row>
     <row r="14">
@@ -4086,25 +4264,25 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="18" t="n">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ElectricalSone UK</t>
+          <t>LEDSone UK</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -4127,24 +4305,24 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LEDSone UK</t>
+          <t>ElectricalSone UK</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>39.9</v>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4190,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>52.59</v>
+        <v>100.22</v>
       </c>
     </row>
     <row r="20">
@@ -4213,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>33.82</v>
+        <v>20.37</v>
       </c>
     </row>
     <row r="21">
@@ -4242,12 +4420,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Homin GmbH</t>
+          <t>LEDSone UK</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -4259,18 +4437,18 @@
         <v>0</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>35.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ElectricalSone UK</t>
+          <t>Homin GmbH</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -4282,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="24">
@@ -4293,41 +4471,41 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="19" t="n">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>LEDSone UK</t>
+          <t>ElectricalSone UK</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="17" t="n">
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4374,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>6.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -4426,46 +4604,92 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Huetten Lampen DE</t>
+          <t>Sunsone</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="17" t="n">
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D30" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>Huetten Lampen DE</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>LEDSone DE</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>UK</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="D31" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="16" t="n">
+      <c r="D32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ElectricalSone UK</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4582,7 +4806,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Generated 2026-07-28.  "Today" = 2026-07-27.  "Yesterday" = 2026-07-26.  Same Day LY = 2025-07-27.</t>
+          <t xml:space="preserve">  Generated 2026-08-03.  "Today" = 2026-08-02.  "Yesterday" = 2026-08-01.  Same Day LY = 2025-08-02.</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-07-27</t>
+          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-02</t>
         </is>
       </c>
     </row>
@@ -4938,7 +5162,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2026-07-27 was a Monday; 2025-07-27 was a Sunday). Day-of-week effects are present in this comparison.</t>
+          <t xml:space="preserve">  (2026-08-02 was a Sunday; 2025-08-02 was a Saturday). Day-of-week effects are present in this comparison.</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E2" s="4" t="n">
+        <v>1522.4</v>
+      </c>
+      <c r="F2" s="4" t="n">
         <v>1128.69</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>932.88</v>
       </c>
       <c r="G2" s="4">
         <f>E2-F2</f>
@@ -674,36 +674,36 @@
         <v/>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1070.98</v>
+        <v>1445.52</v>
       </c>
       <c r="J2" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="K2" s="6" t="n">
         <v>64</v>
-      </c>
-      <c r="K2" s="6" t="n">
-        <v>53</v>
       </c>
       <c r="L2" s="5">
         <f>IF(K2=0,"",(J2-K2)/K2)</f>
         <v/>
       </c>
       <c r="M2" s="6" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="O2" s="4">
         <f>IF(J2=0,"",E2/J2)</f>
         <v/>
       </c>
       <c r="P2" s="6" t="n">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>568.36</v>
+        <v>745.54</v>
       </c>
       <c r="S2" s="2">
         <f>IF(AND('Engine Inputs'!E2=0,R2=0),"",IF('Engine Inputs'!E2=0,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&gt;Config!$B$2,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -713,7 +713,7 @@
         <v>1305</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>548.76</v>
+        <v>806.4299999999999</v>
       </c>
       <c r="V2" s="2">
         <f>IF(AND('Engine Inputs'!D2=0,U2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E3" s="4" t="n">
+        <v>341.93</v>
+      </c>
+      <c r="F3" s="4" t="n">
         <v>353.49</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>549.5</v>
       </c>
       <c r="G3" s="4">
         <f>E3-F3</f>
@@ -763,36 +763,36 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>607.8200000000001</v>
+        <v>629.22</v>
       </c>
       <c r="J3" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="K3" s="6" t="n">
         <v>21</v>
-      </c>
-      <c r="K3" s="6" t="n">
-        <v>31</v>
       </c>
       <c r="L3" s="5">
         <f>IF(K3=0,"",(J3-K3)/K3)</f>
         <v/>
       </c>
       <c r="M3" s="6" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="O3" s="4">
         <f>IF(J3=0,"",E3/J3)</f>
         <v/>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>222.27</v>
+        <v>216.66</v>
       </c>
       <c r="S3" s="2">
         <f>IF(AND('Engine Inputs'!E3=0,R3=0),"",IF('Engine Inputs'!E3=0,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&gt;Config!$B$2,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -802,7 +802,7 @@
         <v>597</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>147.44</v>
+        <v>128.8</v>
       </c>
       <c r="V3" s="2">
         <f>IF(AND('Engine Inputs'!D3=0,U3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E4" s="7" t="n">
+        <v>393.41</v>
+      </c>
+      <c r="F4" s="7" t="n">
         <v>340.06</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>259.33</v>
       </c>
       <c r="G4" s="7">
         <f>E4-F4</f>
@@ -852,36 +852,36 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>396.06</v>
+        <v>611.78</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>12</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L4" s="5">
         <f>IF(K4=0,"",(J4-K4)/K4)</f>
         <v/>
       </c>
       <c r="M4" s="6" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="O4" s="7">
         <f>IF(J4=0,"",E4/J4)</f>
         <v/>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>273.58</v>
+        <v>315.96</v>
       </c>
       <c r="S4" s="2">
         <f>IF(AND('Engine Inputs'!E4=0,R4=0),"",IF('Engine Inputs'!E4=0,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&gt;Config!$B$2,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -891,7 +891,7 @@
         <v>232</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>16.7</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2">
         <f>IF(AND('Engine Inputs'!D4=0,U4=0),"",IF('Engine Inputs'!D4=0,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&gt;Config!$B$2,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E5" s="4" t="n">
+        <v>126.17</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>289.57</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>300.45</v>
       </c>
       <c r="G5" s="4">
         <f>E5-F5</f>
@@ -941,23 +941,23 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>322.23</v>
+        <v>191.14</v>
       </c>
       <c r="J5" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>16</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>15</v>
       </c>
       <c r="L5" s="5">
         <f>IF(K5=0,"",(J5-K5)/K5)</f>
         <v/>
       </c>
       <c r="M5" s="6" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="O5" s="4">
         <f>IF(J5=0,"",E5/J5)</f>
@@ -970,7 +970,7 @@
         <v>718</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>206.2</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="S5" s="2">
         <f>IF(AND('Engine Inputs'!E5=0,R5=0),"",IF('Engine Inputs'!E5=0,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&gt;Config!$B$2,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -980,7 +980,7 @@
         <v>469</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>78.81</v>
+        <v>24.55</v>
       </c>
       <c r="V5" s="2">
         <f>IF(AND('Engine Inputs'!D5=0,U5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E6" s="7" t="n">
+        <v>146.48</v>
+      </c>
+      <c r="F6" s="7" t="n">
         <v>275.07</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>422.04</v>
       </c>
       <c r="G6" s="7">
         <f>E6-F6</f>
@@ -1030,46 +1030,46 @@
         <v/>
       </c>
       <c r="I6" s="7" t="n">
-        <v>273</v>
+        <v>470.64</v>
       </c>
       <c r="J6" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="6" t="n">
         <v>15</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>10</v>
       </c>
       <c r="L6" s="5">
         <f>IF(K6=0,"",(J6-K6)/K6)</f>
         <v/>
       </c>
       <c r="M6" s="6" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="O6" s="7">
         <f>IF(J6=0,"",E6/J6)</f>
         <v/>
       </c>
       <c r="P6" s="6" t="n">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>223.46</v>
+        <v>122.92</v>
       </c>
       <c r="S6" s="2">
         <f>IF(AND('Engine Inputs'!E6=0,R6=0),"",IF('Engine Inputs'!E6=0,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&gt;Config!$B$2,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T6" s="6" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>48.65</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2">
         <f>IF(AND('Engine Inputs'!D6=0,U6=0),"",IF('Engine Inputs'!D6=0,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&gt;Config!$B$2,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E9" s="4" t="n">
+        <v>114.14</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>189.64</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>256.34</v>
       </c>
       <c r="G9" s="4">
         <f>E9-F9</f>
@@ -1297,23 +1297,23 @@
         <v/>
       </c>
       <c r="I9" s="4" t="n">
-        <v>229.19</v>
+        <v>399.68</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>9</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L9" s="5">
         <f>IF(K9=0,"",(J9-K9)/K9)</f>
         <v/>
       </c>
       <c r="M9" s="6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O9" s="4">
         <f>IF(J9=0,"",E9/J9)</f>
@@ -1326,7 +1326,7 @@
         <v>579</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>186.65</v>
+        <v>108.16</v>
       </c>
       <c r="S9" s="2">
         <f>IF(AND('Engine Inputs'!E9=0,R9=0),"",IF('Engine Inputs'!E9=0,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&gt;Config!$B$2,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E10" s="7" t="n">
+        <v>390.64</v>
+      </c>
+      <c r="F10" s="7" t="n">
         <v>651.92</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>179</v>
       </c>
       <c r="G10" s="7">
         <f>E10-F10</f>
@@ -1386,36 +1386,36 @@
         <v/>
       </c>
       <c r="I10" s="7" t="n">
-        <v>520.39</v>
+        <v>591.05</v>
       </c>
       <c r="J10" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="K10" s="6" t="n">
         <v>30</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>10</v>
       </c>
       <c r="L10" s="5">
         <f>IF(K10=0,"",(J10-K10)/K10)</f>
         <v/>
       </c>
       <c r="M10" s="6" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="O10" s="7">
         <f>IF(J10=0,"",E10/J10)</f>
         <v/>
       </c>
       <c r="P10" s="6" t="n">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>608.15</v>
+        <v>258.52</v>
       </c>
       <c r="S10" s="2">
         <f>IF(AND('Engine Inputs'!E10=0,R10=0),"",IF('Engine Inputs'!E10=0,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&gt;Config!$B$2,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1425,7 +1425,7 @@
         <v>93</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>47.37</v>
+        <v>63.9</v>
       </c>
       <c r="V10" s="2">
         <f>IF(AND('Engine Inputs'!D10=0,U10=0),"",IF('Engine Inputs'!D10=0,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&gt;Config!$B$2,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E11" s="4" t="n">
+        <v>65.13</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>47.85</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>43.83</v>
       </c>
       <c r="G11" s="4">
         <f>E11-F11</f>
@@ -1475,23 +1475,23 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>98.73</v>
+        <v>67.23</v>
       </c>
       <c r="J11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K11" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="L11" s="5">
         <f>IF(K11=0,"",(J11-K11)/K11)</f>
         <v/>
       </c>
       <c r="M11" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O11" s="4">
         <f>IF(J11=0,"",E11/J11)</f>
@@ -1504,7 +1504,7 @@
         <v>508</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>50.29</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="S11" s="2">
         <f>IF(AND('Engine Inputs'!E11=0,R11=0),"",IF('Engine Inputs'!E11=0,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&gt;Config!$B$2,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E12" s="7" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="F12" s="7" t="n">
         <v>17.94</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>29.61</v>
       </c>
       <c r="G12" s="7">
         <f>E12-F12</f>
@@ -1564,23 +1564,23 @@
         <v/>
       </c>
       <c r="I12" s="7" t="n">
-        <v>40.25</v>
+        <v>221.53</v>
       </c>
       <c r="J12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>2</v>
       </c>
       <c r="L12" s="5">
         <f>IF(K12=0,"",(J12-K12)/K12)</f>
         <v/>
       </c>
       <c r="M12" s="6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O12" s="7">
         <f>IF(J12=0,"",E12/J12)</f>
@@ -1593,7 +1593,7 @@
         <v>454</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>10.66</v>
+        <v>31.82</v>
       </c>
       <c r="S12" s="2">
         <f>IF(AND('Engine Inputs'!E12=0,R12=0),"",IF('Engine Inputs'!E12=0,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&gt;Config!$B$2,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E13" s="4" t="n">
+        <v>60.16</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>50.82</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>89.38</v>
       </c>
       <c r="G13" s="4">
         <f>E13-F13</f>
@@ -1653,36 +1653,36 @@
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>50.4</v>
+        <v>175.02</v>
       </c>
       <c r="J13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>8</v>
       </c>
       <c r="L13" s="5">
         <f>IF(K13=0,"",(J13-K13)/K13)</f>
         <v/>
       </c>
       <c r="M13" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O13" s="4">
         <f>IF(J13=0,"",E13/J13)</f>
         <v/>
       </c>
       <c r="P13" s="6" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>52.48</v>
+        <v>60.16</v>
       </c>
       <c r="S13" s="2">
         <f>IF(AND('Engine Inputs'!E13=0,R13=0),"",IF('Engine Inputs'!E13=0,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&gt;Config!$B$2,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E14" s="4" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>25.63</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="G14" s="4">
         <f>E14-F14</f>
@@ -1742,23 +1742,23 @@
         <v/>
       </c>
       <c r="I14" s="4" t="n">
-        <v>45.37</v>
+        <v>74.05</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L14" s="5">
         <f>IF(K14=0,"",(J14-K14)/K14)</f>
         <v/>
       </c>
       <c r="M14" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O14" s="4">
         <f>IF(J14=0,"",E14/J14)</f>
@@ -1771,7 +1771,7 @@
         <v>433</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>25.63</v>
+        <v>18.47</v>
       </c>
       <c r="S14" s="2">
         <f>IF(AND('Engine Inputs'!E14=0,R14=0),"",IF('Engine Inputs'!E14=0,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&gt;Config!$B$2,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="9" t="n">
         <v>42.37</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="G17" s="9">
         <f>E17-F17</f>
@@ -2012,10 +2012,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="L17" s="5">
         <f>IF(K17=0,"",(J17-K17)/K17)</f>
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O17" s="9">
         <f>IF(J17=0,"",E17/J17)</f>
@@ -2038,7 +2038,7 @@
         <v>377</v>
       </c>
       <c r="R17" s="9" t="n">
-        <v>39.49</v>
+        <v>0</v>
       </c>
       <c r="S17" s="2">
         <f>IF(AND('Engine Inputs'!E17=0,R17=0),"",IF('Engine Inputs'!E17=0,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&gt;Config!$B$2,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E19" s="7" t="n">
+        <v>56.28</v>
+      </c>
+      <c r="F19" s="7" t="n">
         <v>80.16</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>126.54</v>
       </c>
       <c r="G19" s="7">
         <f>E19-F19</f>
@@ -2187,13 +2187,13 @@
         <v/>
       </c>
       <c r="I19" s="7" t="n">
-        <v>86.63</v>
+        <v>196.39</v>
       </c>
       <c r="J19" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="L19" s="5">
         <f>IF(K19=0,"",(J19-K19)/K19)</f>
@@ -2216,7 +2216,7 @@
         <v>295</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>67.37</v>
+        <v>41.9</v>
       </c>
       <c r="S19" s="2">
         <f>IF(AND('Engine Inputs'!E19=0,R19=0),"",IF('Engine Inputs'!E19=0,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&gt;Config!$B$2,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E20" s="4" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="F20" s="4" t="n">
         <v>6.49</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>20.37</v>
       </c>
       <c r="G20" s="4">
         <f>E20-F20</f>
@@ -2276,10 +2276,10 @@
         <v/>
       </c>
       <c r="I20" s="4" t="n">
-        <v>56.94</v>
+        <v>26.26</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>1</v>
@@ -2292,20 +2292,20 @@
         <v>3</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="4">
         <f>IF(J20=0,"",E20/J20)</f>
         <v/>
       </c>
       <c r="P20" s="6" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>6.49</v>
+        <v>21.28</v>
       </c>
       <c r="S20" s="2">
         <f>IF(AND('Engine Inputs'!E20=0,R20=0),"",IF('Engine Inputs'!E20=0,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&gt;Config!$B$2,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2334,29 +2334,29 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>LEDSone UK</t>
+          <t>Homin GmbH</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="10">
+        <v>46237</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="G21" s="7">
         <f>E21-F21</f>
         <v/>
       </c>
@@ -2364,14 +2364,14 @@
         <f>IF(F21=0,"",(E21-F21)/F21)</f>
         <v/>
       </c>
-      <c r="I21" s="10" t="n">
+      <c r="I21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="5">
         <f>IF(K21=0,"",(J21-K21)/K21)</f>
@@ -2383,17 +2383,17 @@
       <c r="N21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="7">
         <f>IF(J21=0,"",E21/J21)</f>
         <v/>
       </c>
       <c r="P21" s="6" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>184</v>
-      </c>
-      <c r="R21" s="10" t="n">
+        <v>192</v>
+      </c>
+      <c r="R21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S21" s="2">
@@ -2403,7 +2403,7 @@
       <c r="T21" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U21" s="10" t="n">
+      <c r="U21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V21" s="2">
@@ -2414,9 +2414,9 @@
         <f>IF(AND(F21=0,E21=0),"",IF(F21=0,"📈 Up",IF((E21-F21)/F21&gt;Config!$B$2,"📈 Up",IF((E21-F21)/F21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X21" s="2" t="inlineStr">
-        <is>
-          <t>Sharmilan</t>
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t>— not assigned</t>
         </is>
       </c>
     </row>
@@ -2428,24 +2428,24 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46236</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>102.98</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="7">
+        <v>46237</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="10">
         <f>E22-F22</f>
         <v/>
       </c>
@@ -2453,11 +2453,11 @@
         <f>IF(F22=0,"",(E22-F22)/F22)</f>
         <v/>
       </c>
-      <c r="I22" s="7" t="n">
+      <c r="I22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
@@ -2470,20 +2470,20 @@
         <v>0</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="O22" s="7">
+        <v>0</v>
+      </c>
+      <c r="O22" s="10">
         <f>IF(J22=0,"",E22/J22)</f>
         <v/>
       </c>
       <c r="P22" s="6" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="Q22" s="6" t="n">
-        <v>177</v>
-      </c>
-      <c r="R22" s="7" t="n">
-        <v>71.28</v>
+        <v>184</v>
+      </c>
+      <c r="R22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="S22" s="2">
         <f>IF(AND('Engine Inputs'!E22=0,R22=0),"",IF('Engine Inputs'!E22=0,"📈 Up",IF((R22-'Engine Inputs'!E22)/'Engine Inputs'!E22&gt;Config!$B$2,"📈 Up",IF((R22-'Engine Inputs'!E22)/'Engine Inputs'!E22&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2492,7 +2492,7 @@
       <c r="T22" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U22" s="7" t="n">
+      <c r="U22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="V22" s="2">
@@ -2512,12 +2512,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Homin GmbH</t>
+          <t>LEDSone UK</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>47.98</v>
+        <v>0</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>10.99</v>
+        <v>102.98</v>
       </c>
       <c r="G23" s="7">
         <f>E23-F23</f>
@@ -2543,10 +2543,10 @@
         <v/>
       </c>
       <c r="I23" s="7" t="n">
-        <v>22.95</v>
+        <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>1</v>
@@ -2556,23 +2556,23 @@
         <v/>
       </c>
       <c r="M23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O23" s="7">
         <f>IF(J23=0,"",E23/J23)</f>
         <v/>
       </c>
       <c r="P23" s="6" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="Q23" s="6" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="R23" s="7" t="n">
-        <v>47.98</v>
+        <v>0</v>
       </c>
       <c r="S23" s="2">
         <f>IF(AND('Engine Inputs'!E23=0,R23=0),"",IF('Engine Inputs'!E23=0,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&gt;Config!$B$2,"📈 Up",IF((R23-'Engine Inputs'!E23)/'Engine Inputs'!E23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2592,9 +2592,9 @@
         <f>IF(AND(F23=0,E23=0),"",IF(F23=0,"📈 Up",IF((E23-F23)/F23&gt;Config!$B$2,"📈 Up",IF((E23-F23)/F23&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X23" s="8" t="inlineStr">
-        <is>
-          <t>— not assigned</t>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>Sharmilan</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E30" s="9" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>0</v>
@@ -3344,7 +3344,7 @@
         <v/>
       </c>
       <c r="I32" s="4" t="n">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
         <v>0</v>
@@ -3357,7 +3357,7 @@
         <v/>
       </c>
       <c r="M32" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="6" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46236</v>
+        <v>46237</v>
       </c>
     </row>
     <row r="3">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
     </row>
     <row r="5">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>PH Sales 2026-08-01</t>
+          <t>PH Sales 2026-08-02</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>AH Sales 2026-08-01</t>
+          <t>AH Sales 2026-08-02</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>684.66</v>
+        <v>548.76</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>259.71</v>
+        <v>568.36</v>
       </c>
     </row>
     <row r="3">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D3" s="16" t="n">
-        <v>296.46</v>
+        <v>147.44</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>275.49</v>
+        <v>222.27</v>
       </c>
     </row>
     <row r="4">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>37.57</v>
+        <v>16.7</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>152.71</v>
+        <v>273.58</v>
       </c>
     </row>
     <row r="5">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>134.89</v>
+        <v>78.81</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>142.53</v>
+        <v>206.2</v>
       </c>
     </row>
     <row r="6">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0</v>
+        <v>48.65</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>429.05</v>
+        <v>223.46</v>
       </c>
     </row>
     <row r="7">
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>228.49</v>
+        <v>186.65</v>
       </c>
     </row>
     <row r="10">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>27.53</v>
+        <v>47.37</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>149.38</v>
+        <v>608.15</v>
       </c>
     </row>
     <row r="11">
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>47.48</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="12">
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>14.97</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="13">
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>87.95</v>
+        <v>52.48</v>
       </c>
     </row>
     <row r="14">
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>0</v>
+        <v>25.63</v>
       </c>
     </row>
     <row r="15">
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0</v>
+        <v>39.49</v>
       </c>
     </row>
     <row r="18">
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>100.22</v>
+        <v>67.37</v>
       </c>
     </row>
     <row r="20">
@@ -4391,30 +4391,30 @@
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>20.37</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>LEDSone UK</t>
+          <t>Homin GmbH</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>CAD</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="19" t="n">
-        <v>0</v>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>47.98</v>
       </c>
     </row>
     <row r="22">
@@ -4425,30 +4425,30 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="17" t="n">
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Homin GmbH</t>
+          <t>LEDSone UK</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>10.99</v>
+        <v>71.28</v>
       </c>
     </row>
     <row r="24">
@@ -4806,7 +4806,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Generated 2026-08-03.  "Today" = 2026-08-02.  "Yesterday" = 2026-08-01.  Same Day LY = 2025-08-02.</t>
+          <t xml:space="preserve">  Generated 2026-08-04.  "Today" = 2026-08-03.  "Yesterday" = 2026-08-02.  Same Day LY = 2025-08-03.</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-02</t>
+          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2026-08-02 was a Sunday; 2025-08-02 was a Saturday). Day-of-week effects are present in this comparison.</t>
+          <t xml:space="preserve">  (2026-08-03 was a Monday; 2025-08-03 was a Sunday). Day-of-week effects are present in this comparison.</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1522.4</v>
+        <v>977.35</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1128.69</v>
+        <v>1040.89</v>
       </c>
       <c r="G2" s="4">
         <f>E2-F2</f>
@@ -674,46 +674,46 @@
         <v/>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1445.52</v>
+        <v>1380.96</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="L2" s="5">
         <f>IF(K2=0,"",(J2-K2)/K2)</f>
         <v/>
       </c>
       <c r="M2" s="6" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="O2" s="4">
         <f>IF(J2=0,"",E2/J2)</f>
         <v/>
       </c>
       <c r="P2" s="6" t="n">
-        <v>3037</v>
+        <v>3043</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>1732</v>
+        <v>1737</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>745.54</v>
+        <v>559.78</v>
       </c>
       <c r="S2" s="2">
         <f>IF(AND('Engine Inputs'!E2=0,R2=0),"",IF('Engine Inputs'!E2=0,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&gt;Config!$B$2,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T2" s="6" t="n">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>806.4299999999999</v>
+        <v>445.02</v>
       </c>
       <c r="V2" s="2">
         <f>IF(AND('Engine Inputs'!D2=0,U2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>341.93</v>
+        <v>238.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>353.49</v>
+        <v>544.0599999999999</v>
       </c>
       <c r="G3" s="4">
         <f>E3-F3</f>
@@ -763,36 +763,36 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>629.22</v>
+        <v>867.9</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="L3" s="5">
         <f>IF(K3=0,"",(J3-K3)/K3)</f>
         <v/>
       </c>
       <c r="M3" s="6" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="O3" s="4">
         <f>IF(J3=0,"",E3/J3)</f>
         <v/>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1679</v>
+        <v>1684</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>1082</v>
+        <v>1087</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>216.66</v>
+        <v>58.27</v>
       </c>
       <c r="S3" s="2">
         <f>IF(AND('Engine Inputs'!E3=0,R3=0),"",IF('Engine Inputs'!E3=0,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&gt;Config!$B$2,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -802,7 +802,7 @@
         <v>597</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>128.8</v>
+        <v>189.76</v>
       </c>
       <c r="V3" s="2">
         <f>IF(AND('Engine Inputs'!D3=0,U3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>393.41</v>
+        <v>301.21</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>340.06</v>
+        <v>188.66</v>
       </c>
       <c r="G4" s="7">
         <f>E4-F4</f>
@@ -852,36 +852,36 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>611.78</v>
+        <v>322.54</v>
       </c>
       <c r="J4" s="6" t="n">
         <v>12</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L4" s="5">
         <f>IF(K4=0,"",(J4-K4)/K4)</f>
         <v/>
       </c>
       <c r="M4" s="6" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O4" s="7">
         <f>IF(J4=0,"",E4/J4)</f>
         <v/>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1443</v>
+        <v>1451</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>1211</v>
+        <v>1219</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>315.96</v>
+        <v>212.08</v>
       </c>
       <c r="S4" s="2">
         <f>IF(AND('Engine Inputs'!E4=0,R4=0),"",IF('Engine Inputs'!E4=0,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&gt;Config!$B$2,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>126.17</v>
+        <v>297.45</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>289.57</v>
+        <v>108.19</v>
       </c>
       <c r="G5" s="4">
         <f>E5-F5</f>
@@ -941,46 +941,46 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>191.14</v>
+        <v>345.32</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="L5" s="5">
         <f>IF(K5=0,"",(J5-K5)/K5)</f>
         <v/>
       </c>
       <c r="M5" s="6" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="O5" s="4">
         <f>IF(J5=0,"",E5/J5)</f>
         <v/>
       </c>
       <c r="P5" s="6" t="n">
-        <v>1187</v>
+        <v>1198</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>718</v>
+        <v>728</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>98.65000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="S5" s="2">
         <f>IF(AND('Engine Inputs'!E5=0,R5=0),"",IF('Engine Inputs'!E5=0,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&gt;Config!$B$2,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
       <c r="T5" s="6" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>24.55</v>
+        <v>213.54</v>
       </c>
       <c r="V5" s="2">
         <f>IF(AND('Engine Inputs'!D5=0,U5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>146.48</v>
+        <v>156.9</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>275.07</v>
+        <v>226.77</v>
       </c>
       <c r="G6" s="7">
         <f>E6-F6</f>
@@ -1030,20 +1030,20 @@
         <v/>
       </c>
       <c r="I6" s="7" t="n">
-        <v>470.64</v>
+        <v>223.79</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>6</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L6" s="5">
         <f>IF(K6=0,"",(J6-K6)/K6)</f>
         <v/>
       </c>
       <c r="M6" s="6" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>9</v>
@@ -1059,7 +1059,7 @@
         <v>577</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>122.92</v>
+        <v>126.02</v>
       </c>
       <c r="S6" s="2">
         <f>IF(AND('Engine Inputs'!E6=0,R6=0),"",IF('Engine Inputs'!E6=0,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&gt;Config!$B$2,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v/>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v/>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>114.14</v>
+        <v>306.47</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>189.64</v>
+        <v>305.38</v>
       </c>
       <c r="G9" s="4">
         <f>E9-F9</f>
@@ -1297,23 +1297,23 @@
         <v/>
       </c>
       <c r="I9" s="4" t="n">
-        <v>399.68</v>
+        <v>188.67</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L9" s="5">
         <f>IF(K9=0,"",(J9-K9)/K9)</f>
         <v/>
       </c>
       <c r="M9" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O9" s="4">
         <f>IF(J9=0,"",E9/J9)</f>
@@ -1326,7 +1326,7 @@
         <v>579</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>108.16</v>
+        <v>275.08</v>
       </c>
       <c r="S9" s="2">
         <f>IF(AND('Engine Inputs'!E9=0,R9=0),"",IF('Engine Inputs'!E9=0,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&gt;Config!$B$2,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>390.64</v>
+        <v>202.07</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>651.92</v>
+        <v>286.2</v>
       </c>
       <c r="G10" s="7">
         <f>E10-F10</f>
@@ -1386,36 +1386,36 @@
         <v/>
       </c>
       <c r="I10" s="7" t="n">
-        <v>591.05</v>
+        <v>232.59</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="L10" s="5">
         <f>IF(K10=0,"",(J10-K10)/K10)</f>
         <v/>
       </c>
       <c r="M10" s="6" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="O10" s="7">
         <f>IF(J10=0,"",E10/J10)</f>
         <v/>
       </c>
       <c r="P10" s="6" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>258.52</v>
+        <v>169.08</v>
       </c>
       <c r="S10" s="2">
         <f>IF(AND('Engine Inputs'!E10=0,R10=0),"",IF('Engine Inputs'!E10=0,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&gt;Config!$B$2,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1425,7 +1425,7 @@
         <v>93</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>63.9</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2">
         <f>IF(AND('Engine Inputs'!D10=0,U10=0),"",IF('Engine Inputs'!D10=0,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&gt;Config!$B$2,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>65.13</v>
+        <v>21.28</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>47.85</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="G11" s="4">
         <f>E11-F11</f>
@@ -1475,23 +1475,23 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>67.23</v>
+        <v>112.67</v>
       </c>
       <c r="J11" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="6" t="n">
         <v>8</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>5</v>
       </c>
       <c r="L11" s="5">
         <f>IF(K11=0,"",(J11-K11)/K11)</f>
         <v/>
       </c>
       <c r="M11" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O11" s="4">
         <f>IF(J11=0,"",E11/J11)</f>
@@ -1504,7 +1504,7 @@
         <v>508</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>21.74</v>
       </c>
       <c r="S11" s="2">
         <f>IF(AND('Engine Inputs'!E11=0,R11=0),"",IF('Engine Inputs'!E11=0,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&gt;Config!$B$2,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>42.87</v>
+        <v>50.02</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>17.94</v>
+        <v>61.21</v>
       </c>
       <c r="G12" s="7">
         <f>E12-F12</f>
@@ -1564,23 +1564,23 @@
         <v/>
       </c>
       <c r="I12" s="7" t="n">
-        <v>221.53</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" s="5">
         <f>IF(K12=0,"",(J12-K12)/K12)</f>
         <v/>
       </c>
       <c r="M12" s="6" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O12" s="7">
         <f>IF(J12=0,"",E12/J12)</f>
@@ -1593,7 +1593,7 @@
         <v>454</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>31.82</v>
+        <v>0</v>
       </c>
       <c r="S12" s="2">
         <f>IF(AND('Engine Inputs'!E12=0,R12=0),"",IF('Engine Inputs'!E12=0,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&gt;Config!$B$2,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1603,7 +1603,7 @@
         <v>37</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>0</v>
+        <v>33.21</v>
       </c>
       <c r="V12" s="2">
         <f>IF(AND('Engine Inputs'!D12=0,U12=0),"",IF('Engine Inputs'!D12=0,"📈 Up",IF((U12-'Engine Inputs'!D12)/'Engine Inputs'!D12&gt;Config!$B$2,"📈 Up",IF((U12-'Engine Inputs'!D12)/'Engine Inputs'!D12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>60.16</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>50.82</v>
+        <v>135.16</v>
       </c>
       <c r="G13" s="4">
         <f>E13-F13</f>
@@ -1653,36 +1653,36 @@
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>175.02</v>
+        <v>156.31</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L13" s="5">
         <f>IF(K13=0,"",(J13-K13)/K13)</f>
         <v/>
       </c>
       <c r="M13" s="6" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O13" s="4">
         <f>IF(J13=0,"",E13/J13)</f>
         <v/>
       </c>
       <c r="P13" s="6" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>60.16</v>
+        <v>66.84</v>
       </c>
       <c r="S13" s="2">
         <f>IF(AND('Engine Inputs'!E13=0,R13=0),"",IF('Engine Inputs'!E13=0,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&gt;Config!$B$2,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>18.47</v>
+        <v>12.78</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>25.63</v>
+        <v>11.78</v>
       </c>
       <c r="G14" s="4">
         <f>E14-F14</f>
@@ -1742,36 +1742,36 @@
         <v/>
       </c>
       <c r="I14" s="4" t="n">
-        <v>74.05</v>
+        <v>32.51</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="5">
         <f>IF(K14=0,"",(J14-K14)/K14)</f>
         <v/>
       </c>
       <c r="M14" s="6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="4">
         <f>IF(J14=0,"",E14/J14)</f>
         <v/>
       </c>
       <c r="P14" s="6" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>18.47</v>
+        <v>12.78</v>
       </c>
       <c r="S14" s="2">
         <f>IF(AND('Engine Inputs'!E14=0,R14=0),"",IF('Engine Inputs'!E14=0,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&gt;Config!$B$2,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v/>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0</v>
+        <v>94.64</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v/>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0</v>
+        <v>44.09</v>
       </c>
       <c r="G16" s="9">
         <f>E16-F16</f>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="5">
         <f>IF(K16=0,"",(J16-K16)/K16)</f>
@@ -1943,10 +1943,10 @@
         <v/>
       </c>
       <c r="P16" s="6" t="n">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="R16" s="9" t="n">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>42.37</v>
+        <v>0</v>
       </c>
       <c r="G17" s="9">
         <f>E17-F17</f>
@@ -2015,7 +2015,7 @@
         <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" s="5">
         <f>IF(K17=0,"",(J17-K17)/K17)</f>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>56.28</v>
+        <v>18.06</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>80.16</v>
+        <v>158.59</v>
       </c>
       <c r="G19" s="7">
         <f>E19-F19</f>
@@ -2187,36 +2187,36 @@
         <v/>
       </c>
       <c r="I19" s="7" t="n">
-        <v>196.39</v>
+        <v>219.75</v>
       </c>
       <c r="J19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="6" t="n">
         <v>5</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>3</v>
       </c>
       <c r="L19" s="5">
         <f>IF(K19=0,"",(J19-K19)/K19)</f>
         <v/>
       </c>
       <c r="M19" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O19" s="7">
         <f>IF(J19=0,"",E19/J19)</f>
         <v/>
       </c>
       <c r="P19" s="6" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>41.9</v>
+        <v>10.8</v>
       </c>
       <c r="S19" s="2">
         <f>IF(AND('Engine Inputs'!E19=0,R19=0),"",IF('Engine Inputs'!E19=0,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&gt;Config!$B$2,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>21.28</v>
+        <v>81.84</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4">
         <f>E20-F20</f>
@@ -2276,23 +2276,23 @@
         <v/>
       </c>
       <c r="I20" s="4" t="n">
-        <v>26.26</v>
+        <v>34.82</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="5">
         <f>IF(K20=0,"",(J20-K20)/K20)</f>
         <v/>
       </c>
       <c r="M20" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O20" s="4">
         <f>IF(J20=0,"",E20/J20)</f>
@@ -2305,7 +2305,7 @@
         <v>264</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>21.28</v>
+        <v>81.84</v>
       </c>
       <c r="S20" s="2">
         <f>IF(AND('Engine Inputs'!E20=0,R20=0),"",IF('Engine Inputs'!E20=0,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&gt;Config!$B$2,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0</v>
+        <v>50.02</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>47.98</v>
+        <v>48.48</v>
       </c>
       <c r="G21" s="7">
         <f>E21-F21</f>
@@ -2368,10 +2368,10 @@
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" s="5">
         <f>IF(K21=0,"",(J21-K21)/K21)</f>
@@ -2381,7 +2381,7 @@
         <v>0</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" s="7">
         <f>IF(J21=0,"",E21/J21)</f>
@@ -2394,7 +2394,7 @@
         <v>192</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>0</v>
+        <v>39.52</v>
       </c>
       <c r="S21" s="2">
         <f>IF(AND('Engine Inputs'!E21=0,R21=0),"",IF('Engine Inputs'!E21=0,"📈 Up",IF((R21-'Engine Inputs'!E21)/'Engine Inputs'!E21&gt;Config!$B$2,"📈 Up",IF((R21-'Engine Inputs'!E21)/'Engine Inputs'!E21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0</v>
@@ -2526,13 +2526,13 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>102.98</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7">
         <f>E23-F23</f>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="5">
         <f>IF(K23=0,"",(J23-K23)/K23)</f>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>0</v>
@@ -2957,29 +2957,29 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LEDSone UK</t>
+          <t>Sunsone</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="E28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="7">
+        <v>46245</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="9">
         <f>E28-F28</f>
         <v/>
       </c>
@@ -2987,7 +2987,7 @@
         <f>IF(F28=0,"",(E28-F28)/F28)</f>
         <v/>
       </c>
-      <c r="I28" s="7" t="n">
+      <c r="I28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
@@ -3006,17 +3006,17 @@
       <c r="N28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="7">
+      <c r="O28" s="9">
         <f>IF(J28=0,"",E28/J28)</f>
         <v/>
       </c>
       <c r="P28" s="6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="R28" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="R28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S28" s="2">
@@ -3026,7 +3026,7 @@
       <c r="T28" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U28" s="7" t="n">
+      <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V28" s="2">
@@ -3037,9 +3037,9 @@
         <f>IF(AND(F28=0,E28=0),"",IF(F28=0,"📈 Up",IF((E28-F28)/F28&gt;Config!$B$2,"📈 Up",IF((E28-F28)/F28&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X28" s="2" t="inlineStr">
-        <is>
-          <t>Sharmilan</t>
+      <c r="X28" s="8" t="inlineStr">
+        <is>
+          <t>— not assigned</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -3100,10 +3100,10 @@
         <v/>
       </c>
       <c r="P29" s="6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="R29" s="7" t="n">
         <v>0</v>
@@ -3135,29 +3135,29 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Sunsone</t>
+          <t>LEDSone UK</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="9">
+        <v>46245</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="7">
         <f>E30-F30</f>
         <v/>
       </c>
@@ -3165,7 +3165,7 @@
         <f>IF(F30=0,"",(E30-F30)/F30)</f>
         <v/>
       </c>
-      <c r="I30" s="9" t="n">
+      <c r="I30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
@@ -3184,17 +3184,17 @@
       <c r="N30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O30" s="9">
+      <c r="O30" s="7">
         <f>IF(J30=0,"",E30/J30)</f>
         <v/>
       </c>
       <c r="P30" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="R30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="S30" s="2">
@@ -3204,7 +3204,7 @@
       <c r="T30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="U30" s="9" t="n">
+      <c r="U30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V30" s="2">
@@ -3215,9 +3215,9 @@
         <f>IF(AND(F30=0,E30=0),"",IF(F30=0,"📈 Up",IF((E30-F30)/F30&gt;Config!$B$2,"📈 Up",IF((E30-F30)/F30&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
         <v/>
       </c>
-      <c r="X30" s="8" t="inlineStr">
-        <is>
-          <t>— not assigned</t>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>Sharmilan</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
     </row>
     <row r="3">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
     </row>
     <row r="5">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>PH Sales 2026-08-02</t>
+          <t>PH Sales 2026-08-10</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>AH Sales 2026-08-02</t>
+          <t>AH Sales 2026-08-10</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>548.76</v>
+        <v>426.6</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>568.36</v>
+        <v>608.98</v>
       </c>
     </row>
     <row r="3">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D3" s="16" t="n">
-        <v>147.44</v>
+        <v>260.89</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>222.27</v>
+        <v>308.78</v>
       </c>
     </row>
     <row r="4">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>16.7</v>
+        <v>14.52</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>273.58</v>
+        <v>116.76</v>
       </c>
     </row>
     <row r="5">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>78.81</v>
+        <v>38.07</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>206.2</v>
+        <v>69.56</v>
       </c>
     </row>
     <row r="6">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>48.65</v>
+        <v>6.58</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>223.46</v>
+        <v>192.37</v>
       </c>
     </row>
     <row r="7">
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>186.65</v>
+        <v>291.02</v>
       </c>
     </row>
     <row r="10">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>47.37</v>
+        <v>18.24</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>608.15</v>
+        <v>199.2</v>
       </c>
     </row>
     <row r="11">
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>50.29</v>
+        <v>69.61</v>
       </c>
     </row>
     <row r="12">
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>10.66</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="13">
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>52.48</v>
+        <v>142.16</v>
       </c>
     </row>
     <row r="14">
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>25.63</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>0</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="17">
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>39.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>67.37</v>
+        <v>114.02</v>
       </c>
     </row>
     <row r="20">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4414,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>47.98</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="22">
@@ -4460,7 +4460,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>71.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4558,23 +4558,23 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LEDSone UK</t>
+          <t>Sunsone</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>US</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="17" t="n">
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D28" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4586,7 +4586,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -4604,23 +4604,23 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Sunsone</t>
+          <t>LEDSone UK</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D30" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="18" t="n">
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Generated 2026-08-04.  "Today" = 2026-08-03.  "Yesterday" = 2026-08-02.  Same Day LY = 2025-08-03.</t>
+          <t xml:space="preserve">  Generated 2026-08-12.  "Today" = 2026-08-11.  "Yesterday" = 2026-08-10.  Same Day LY = 2025-08-11.</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-03</t>
+          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-11</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2026-08-03 was a Monday; 2025-08-03 was a Sunday). Day-of-week effects are present in this comparison.</t>
+          <t xml:space="preserve">  (2026-08-11 was a Tuesday; 2025-08-11 was a Monday). Day-of-week effects are present in this comparison.</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>977.35</v>
+        <v>965.86</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1040.89</v>
+        <v>816.55</v>
       </c>
       <c r="G2" s="4">
         <f>E2-F2</f>
@@ -674,36 +674,36 @@
         <v/>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1380.96</v>
+        <v>1219.5</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="L2" s="5">
         <f>IF(K2=0,"",(J2-K2)/K2)</f>
         <v/>
       </c>
       <c r="M2" s="6" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="O2" s="4">
         <f>IF(J2=0,"",E2/J2)</f>
         <v/>
       </c>
       <c r="P2" s="6" t="n">
-        <v>3043</v>
+        <v>3058</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>1737</v>
+        <v>1752</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>559.78</v>
+        <v>578.83</v>
       </c>
       <c r="S2" s="2">
         <f>IF(AND('Engine Inputs'!E2=0,R2=0),"",IF('Engine Inputs'!E2=0,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&gt;Config!$B$2,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -713,7 +713,7 @@
         <v>1306</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>445.02</v>
+        <v>379.8</v>
       </c>
       <c r="V2" s="2">
         <f>IF(AND('Engine Inputs'!D2=0,U2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>238.8</v>
+        <v>299.98</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>544.0599999999999</v>
+        <v>227.41</v>
       </c>
       <c r="G3" s="4">
         <f>E3-F3</f>
@@ -763,36 +763,36 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>867.9</v>
+        <v>476.63</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="L3" s="5">
         <f>IF(K3=0,"",(J3-K3)/K3)</f>
         <v/>
       </c>
       <c r="M3" s="6" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="O3" s="4">
         <f>IF(J3=0,"",E3/J3)</f>
         <v/>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1684</v>
+        <v>1695</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>1087</v>
+        <v>1098</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>58.27</v>
+        <v>42.56</v>
       </c>
       <c r="S3" s="2">
         <f>IF(AND('Engine Inputs'!E3=0,R3=0),"",IF('Engine Inputs'!E3=0,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&gt;Config!$B$2,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -802,7 +802,7 @@
         <v>597</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>189.76</v>
+        <v>261.78</v>
       </c>
       <c r="V3" s="2">
         <f>IF(AND('Engine Inputs'!D3=0,U3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>301.21</v>
+        <v>252.71</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>188.66</v>
+        <v>321.17</v>
       </c>
       <c r="G4" s="7">
         <f>E4-F4</f>
@@ -852,13 +852,13 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>322.54</v>
+        <v>493.49</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L4" s="5">
         <f>IF(K4=0,"",(J4-K4)/K4)</f>
@@ -868,20 +868,20 @@
         <v>17</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O4" s="7">
         <f>IF(J4=0,"",E4/J4)</f>
         <v/>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>212.08</v>
+        <v>161.6</v>
       </c>
       <c r="S4" s="2">
         <f>IF(AND('Engine Inputs'!E4=0,R4=0),"",IF('Engine Inputs'!E4=0,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&gt;Config!$B$2,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -891,7 +891,7 @@
         <v>232</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>0</v>
+        <v>13.17</v>
       </c>
       <c r="V4" s="2">
         <f>IF(AND('Engine Inputs'!D4=0,U4=0),"",IF('Engine Inputs'!D4=0,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&gt;Config!$B$2,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>297.45</v>
+        <v>213.89</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>108.19</v>
+        <v>162.69</v>
       </c>
       <c r="G5" s="4">
         <f>E5-F5</f>
@@ -941,20 +941,20 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>345.32</v>
+        <v>219.38</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L5" s="5">
         <f>IF(K5=0,"",(J5-K5)/K5)</f>
         <v/>
       </c>
       <c r="M5" s="6" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="N5" s="6" t="n">
         <v>26</v>
@@ -964,13 +964,13 @@
         <v/>
       </c>
       <c r="P5" s="6" t="n">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>84.5</v>
+        <v>158.62</v>
       </c>
       <c r="S5" s="2">
         <f>IF(AND('Engine Inputs'!E5=0,R5=0),"",IF('Engine Inputs'!E5=0,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&gt;Config!$B$2,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -980,7 +980,7 @@
         <v>470</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>213.54</v>
+        <v>47.53</v>
       </c>
       <c r="V5" s="2">
         <f>IF(AND('Engine Inputs'!D5=0,U5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>156.9</v>
+        <v>203.58</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>226.77</v>
+        <v>178.12</v>
       </c>
       <c r="G6" s="7">
         <f>E6-F6</f>
@@ -1030,10 +1030,10 @@
         <v/>
       </c>
       <c r="I6" s="7" t="n">
-        <v>223.79</v>
+        <v>317.26</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>7</v>
@@ -1043,7 +1043,7 @@
         <v/>
       </c>
       <c r="M6" s="6" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N6" s="6" t="n">
         <v>9</v>
@@ -1053,13 +1053,13 @@
         <v/>
       </c>
       <c r="P6" s="6" t="n">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>126.02</v>
+        <v>187.69</v>
       </c>
       <c r="S6" s="2">
         <f>IF(AND('Engine Inputs'!E6=0,R6=0),"",IF('Engine Inputs'!E6=0,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&gt;Config!$B$2,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v/>
       </c>
       <c r="I7" s="7" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>0</v>
@@ -1132,7 +1132,7 @@
         <v/>
       </c>
       <c r="M7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="6" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>306.47</v>
+        <v>208.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>305.38</v>
+        <v>315.7</v>
       </c>
       <c r="G9" s="4">
         <f>E9-F9</f>
@@ -1297,23 +1297,23 @@
         <v/>
       </c>
       <c r="I9" s="4" t="n">
-        <v>188.67</v>
+        <v>28.02</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="L9" s="5">
         <f>IF(K9=0,"",(J9-K9)/K9)</f>
         <v/>
       </c>
       <c r="M9" s="6" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="O9" s="4">
         <f>IF(J9=0,"",E9/J9)</f>
@@ -1326,7 +1326,7 @@
         <v>579</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>275.08</v>
+        <v>208.8</v>
       </c>
       <c r="S9" s="2">
         <f>IF(AND('Engine Inputs'!E9=0,R9=0),"",IF('Engine Inputs'!E9=0,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&gt;Config!$B$2,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>202.07</v>
+        <v>326.92</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>286.2</v>
+        <v>468.51</v>
       </c>
       <c r="G10" s="7">
         <f>E10-F10</f>
@@ -1386,23 +1386,23 @@
         <v/>
       </c>
       <c r="I10" s="7" t="n">
-        <v>232.59</v>
+        <v>205.97</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L10" s="5">
         <f>IF(K10=0,"",(J10-K10)/K10)</f>
         <v/>
       </c>
       <c r="M10" s="6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="O10" s="7">
         <f>IF(J10=0,"",E10/J10)</f>
@@ -1415,7 +1415,7 @@
         <v>465</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>169.08</v>
+        <v>180.33</v>
       </c>
       <c r="S10" s="2">
         <f>IF(AND('Engine Inputs'!E10=0,R10=0),"",IF('Engine Inputs'!E10=0,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&gt;Config!$B$2,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1425,7 +1425,7 @@
         <v>93</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>0</v>
+        <v>62.09</v>
       </c>
       <c r="V10" s="2">
         <f>IF(AND('Engine Inputs'!D10=0,U10=0),"",IF('Engine Inputs'!D10=0,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&gt;Config!$B$2,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>21.28</v>
+        <v>80.05</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>67.40000000000001</v>
+        <v>36.06</v>
       </c>
       <c r="G11" s="4">
         <f>E11-F11</f>
@@ -1475,36 +1475,36 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>112.67</v>
+        <v>69.38</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L11" s="5">
         <f>IF(K11=0,"",(J11-K11)/K11)</f>
         <v/>
       </c>
       <c r="M11" s="6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="O11" s="4">
         <f>IF(J11=0,"",E11/J11)</f>
         <v/>
       </c>
       <c r="P11" s="6" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Q11" s="6" t="n">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>21.74</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="S11" s="2">
         <f>IF(AND('Engine Inputs'!E11=0,R11=0),"",IF('Engine Inputs'!E11=0,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&gt;Config!$B$2,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>50.02</v>
+        <v>96.73</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>61.21</v>
+        <v>93.66</v>
       </c>
       <c r="G12" s="7">
         <f>E12-F12</f>
@@ -1564,23 +1564,23 @@
         <v/>
       </c>
       <c r="I12" s="7" t="n">
-        <v>90.31999999999999</v>
+        <v>122.78</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L12" s="5">
         <f>IF(K12=0,"",(J12-K12)/K12)</f>
         <v/>
       </c>
       <c r="M12" s="6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O12" s="7">
         <f>IF(J12=0,"",E12/J12)</f>
@@ -1593,7 +1593,7 @@
         <v>454</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>0</v>
+        <v>64.23</v>
       </c>
       <c r="S12" s="2">
         <f>IF(AND('Engine Inputs'!E12=0,R12=0),"",IF('Engine Inputs'!E12=0,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&gt;Config!$B$2,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1603,7 +1603,7 @@
         <v>37</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>33.21</v>
+        <v>2.85</v>
       </c>
       <c r="V12" s="2">
         <f>IF(AND('Engine Inputs'!D12=0,U12=0),"",IF('Engine Inputs'!D12=0,"📈 Up",IF((U12-'Engine Inputs'!D12)/'Engine Inputs'!D12&gt;Config!$B$2,"📈 Up",IF((U12-'Engine Inputs'!D12)/'Engine Inputs'!D12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>65.26000000000001</v>
+        <v>23.91</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>135.16</v>
+        <v>109.12</v>
       </c>
       <c r="G13" s="4">
         <f>E13-F13</f>
@@ -1653,36 +1653,36 @@
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>156.31</v>
+        <v>142.56</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L13" s="5">
         <f>IF(K13=0,"",(J13-K13)/K13)</f>
         <v/>
       </c>
       <c r="M13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" s="6" t="n">
         <v>4</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>6</v>
       </c>
       <c r="O13" s="4">
         <f>IF(J13=0,"",E13/J13)</f>
         <v/>
       </c>
       <c r="P13" s="6" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Q13" s="6" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>66.84</v>
+        <v>23.91</v>
       </c>
       <c r="S13" s="2">
         <f>IF(AND('Engine Inputs'!E13=0,R13=0),"",IF('Engine Inputs'!E13=0,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&gt;Config!$B$2,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>12.78</v>
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>11.78</v>
+        <v>65.38</v>
       </c>
       <c r="G14" s="4">
         <f>E14-F14</f>
@@ -1742,23 +1742,23 @@
         <v/>
       </c>
       <c r="I14" s="4" t="n">
-        <v>32.51</v>
+        <v>31.95</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L14" s="5">
         <f>IF(K14=0,"",(J14-K14)/K14)</f>
         <v/>
       </c>
       <c r="M14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="4">
         <f>IF(J14=0,"",E14/J14)</f>
@@ -1771,7 +1771,7 @@
         <v>434</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>12.78</v>
+        <v>0</v>
       </c>
       <c r="S14" s="2">
         <f>IF(AND('Engine Inputs'!E14=0,R14=0),"",IF('Engine Inputs'!E14=0,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&gt;Config!$B$2,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1814,7 +1814,7 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
@@ -1831,7 +1831,7 @@
         <v/>
       </c>
       <c r="I15" s="7" t="n">
-        <v>94.64</v>
+        <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>0</v>
@@ -1844,7 +1844,7 @@
         <v/>
       </c>
       <c r="M15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>0</v>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>44.09</v>
+        <v>19.18</v>
       </c>
       <c r="G16" s="9">
         <f>E16-F16</f>
@@ -1920,7 +1920,7 @@
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>36.25</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E18" s="9" t="n">
         <v>0</v>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>18.06</v>
+        <v>33.25</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>158.59</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7">
         <f>E19-F19</f>
@@ -2187,36 +2187,36 @@
         <v/>
       </c>
       <c r="I19" s="7" t="n">
-        <v>219.75</v>
+        <v>37.19</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L19" s="5">
         <f>IF(K19=0,"",(J19-K19)/K19)</f>
         <v/>
       </c>
       <c r="M19" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="7">
         <f>IF(J19=0,"",E19/J19)</f>
         <v/>
       </c>
       <c r="P19" s="6" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>10.8</v>
+        <v>19.12</v>
       </c>
       <c r="S19" s="2">
         <f>IF(AND('Engine Inputs'!E19=0,R19=0),"",IF('Engine Inputs'!E19=0,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&gt;Config!$B$2,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>81.84</v>
+        <v>5.89</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0</v>
+        <v>10.78</v>
       </c>
       <c r="G20" s="4">
         <f>E20-F20</f>
@@ -2276,36 +2276,36 @@
         <v/>
       </c>
       <c r="I20" s="4" t="n">
-        <v>34.82</v>
+        <v>14.89</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" s="5">
         <f>IF(K20=0,"",(J20-K20)/K20)</f>
         <v/>
       </c>
       <c r="M20" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O20" s="4">
         <f>IF(J20=0,"",E20/J20)</f>
         <v/>
       </c>
       <c r="P20" s="6" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>81.84</v>
+        <v>5.89</v>
       </c>
       <c r="S20" s="2">
         <f>IF(AND('Engine Inputs'!E20=0,R20=0),"",IF('Engine Inputs'!E20=0,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&gt;Config!$B$2,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>50.02</v>
+        <v>0</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>48.48</v>
+        <v>22.07</v>
       </c>
       <c r="G21" s="7">
         <f>E21-F21</f>
@@ -2365,10 +2365,10 @@
         <v/>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>1</v>
@@ -2378,23 +2378,23 @@
         <v/>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O21" s="7">
         <f>IF(J21=0,"",E21/J21)</f>
         <v/>
       </c>
       <c r="P21" s="6" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>39.52</v>
+        <v>0</v>
       </c>
       <c r="S21" s="2">
         <f>IF(AND('Engine Inputs'!E21=0,R21=0),"",IF('Engine Inputs'!E21=0,"📈 Up",IF((R21-'Engine Inputs'!E21)/'Engine Inputs'!E21&gt;Config!$B$2,"📈 Up",IF((R21-'Engine Inputs'!E21)/'Engine Inputs'!E21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v/>
       </c>
       <c r="I22" s="10" t="n">
-        <v>0</v>
+        <v>44.67</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v/>
       </c>
       <c r="M22" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>0</v>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E27" s="4" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>0</v>
@@ -3011,10 +3011,10 @@
         <v/>
       </c>
       <c r="P28" s="6" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="Q28" s="6" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="R28" s="9" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
     </row>
     <row r="3">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
     </row>
     <row r="5">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>PH Sales 2026-08-10</t>
+          <t>PH Sales 2026-08-12</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>AH Sales 2026-08-10</t>
+          <t>AH Sales 2026-08-12</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>426.6</v>
+        <v>374.56</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>608.98</v>
+        <v>439.25</v>
       </c>
     </row>
     <row r="3">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D3" s="16" t="n">
-        <v>260.89</v>
+        <v>81.38</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>308.78</v>
+        <v>147.06</v>
       </c>
     </row>
     <row r="4">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>14.52</v>
+        <v>37.57</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>116.76</v>
+        <v>211.08</v>
       </c>
     </row>
     <row r="5">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>38.07</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>69.56</v>
+        <v>88.81999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>6.58</v>
+        <v>32.14</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>192.37</v>
+        <v>153.26</v>
       </c>
     </row>
     <row r="7">
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>291.02</v>
+        <v>304.11</v>
       </c>
     </row>
     <row r="10">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>18.24</v>
+        <v>6.58</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>199.2</v>
+        <v>411.21</v>
       </c>
     </row>
     <row r="11">
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>69.61</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="12">
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>40.6</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="13">
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>142.16</v>
+        <v>113.02</v>
       </c>
     </row>
     <row r="14">
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>8.890000000000001</v>
+        <v>65.38</v>
       </c>
     </row>
     <row r="15">
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>40.49</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="17">
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>114.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>0</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="21">
@@ -4414,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>37.98</v>
+        <v>17.98</v>
       </c>
     </row>
     <row r="22">
@@ -4806,7 +4806,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Generated 2026-08-12.  "Today" = 2026-08-11.  "Yesterday" = 2026-08-10.  Same Day LY = 2025-08-11.</t>
+          <t xml:space="preserve">  Generated 2026-08-14.  "Today" = 2026-08-13.  "Yesterday" = 2026-08-12.  Same Day LY = 2025-08-13.</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-11</t>
+          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-13</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2026-08-11 was a Tuesday; 2025-08-11 was a Monday). Day-of-week effects are present in this comparison.</t>
+          <t xml:space="preserve">  (2026-08-13 was a Thursday; 2025-08-13 was a Wednesday). Day-of-week effects are present in this comparison.</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>965.86</v>
+        <v>1122.21</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>816.55</v>
+        <v>1160.45</v>
       </c>
       <c r="G2" s="4">
         <f>E2-F2</f>
@@ -674,36 +674,36 @@
         <v/>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1219.5</v>
+        <v>928.1</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="L2" s="5">
         <f>IF(K2=0,"",(J2-K2)/K2)</f>
         <v/>
       </c>
       <c r="M2" s="6" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="O2" s="4">
         <f>IF(J2=0,"",E2/J2)</f>
         <v/>
       </c>
       <c r="P2" s="6" t="n">
-        <v>3058</v>
+        <v>3062</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>1752</v>
+        <v>1756</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>578.83</v>
+        <v>603.2</v>
       </c>
       <c r="S2" s="2">
         <f>IF(AND('Engine Inputs'!E2=0,R2=0),"",IF('Engine Inputs'!E2=0,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&gt;Config!$B$2,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -713,7 +713,7 @@
         <v>1306</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>379.8</v>
+        <v>517.77</v>
       </c>
       <c r="V2" s="2">
         <f>IF(AND('Engine Inputs'!D2=0,U2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>299.98</v>
+        <v>537.51</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>227.41</v>
+        <v>293.97</v>
       </c>
       <c r="G3" s="4">
         <f>E3-F3</f>
@@ -763,36 +763,36 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>476.63</v>
+        <v>764.91</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L3" s="5">
         <f>IF(K3=0,"",(J3-K3)/K3)</f>
         <v/>
       </c>
       <c r="M3" s="6" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="O3" s="4">
         <f>IF(J3=0,"",E3/J3)</f>
         <v/>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1695</v>
+        <v>1699</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>42.56</v>
+        <v>306.32</v>
       </c>
       <c r="S3" s="2">
         <f>IF(AND('Engine Inputs'!E3=0,R3=0),"",IF('Engine Inputs'!E3=0,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&gt;Config!$B$2,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -802,7 +802,7 @@
         <v>597</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>261.78</v>
+        <v>237.96</v>
       </c>
       <c r="V3" s="2">
         <f>IF(AND('Engine Inputs'!D3=0,U3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E4" s="7" t="n">
-        <v>252.71</v>
+        <v>302.99</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>321.17</v>
+        <v>320.86</v>
       </c>
       <c r="G4" s="7">
         <f>E4-F4</f>
@@ -852,36 +852,36 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>493.49</v>
+        <v>767.77</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K4" s="6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L4" s="5">
         <f>IF(K4=0,"",(J4-K4)/K4)</f>
         <v/>
       </c>
       <c r="M4" s="6" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O4" s="7">
         <f>IF(J4=0,"",E4/J4)</f>
         <v/>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="Q4" s="6" t="n">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>161.6</v>
+        <v>199.69</v>
       </c>
       <c r="S4" s="2">
         <f>IF(AND('Engine Inputs'!E4=0,R4=0),"",IF('Engine Inputs'!E4=0,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&gt;Config!$B$2,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -891,7 +891,7 @@
         <v>232</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>13.17</v>
+        <v>3.78</v>
       </c>
       <c r="V4" s="2">
         <f>IF(AND('Engine Inputs'!D4=0,U4=0),"",IF('Engine Inputs'!D4=0,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&gt;Config!$B$2,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>213.89</v>
+        <v>320.64</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>162.69</v>
+        <v>234.77</v>
       </c>
       <c r="G5" s="4">
         <f>E5-F5</f>
@@ -941,36 +941,36 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>219.38</v>
+        <v>203.52</v>
       </c>
       <c r="J5" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>15</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>13</v>
       </c>
       <c r="L5" s="5">
         <f>IF(K5=0,"",(J5-K5)/K5)</f>
         <v/>
       </c>
       <c r="M5" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="O5" s="4">
         <f>IF(J5=0,"",E5/J5)</f>
         <v/>
       </c>
       <c r="P5" s="6" t="n">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>158.62</v>
+        <v>234.1</v>
       </c>
       <c r="S5" s="2">
         <f>IF(AND('Engine Inputs'!E5=0,R5=0),"",IF('Engine Inputs'!E5=0,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&gt;Config!$B$2,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -980,7 +980,7 @@
         <v>470</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>47.53</v>
+        <v>87.39</v>
       </c>
       <c r="V5" s="2">
         <f>IF(AND('Engine Inputs'!D5=0,U5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>203.58</v>
+        <v>170.81</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>178.12</v>
+        <v>211.06</v>
       </c>
       <c r="G6" s="7">
         <f>E6-F6</f>
@@ -1030,36 +1030,36 @@
         <v/>
       </c>
       <c r="I6" s="7" t="n">
-        <v>317.26</v>
+        <v>337.65</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L6" s="5">
         <f>IF(K6=0,"",(J6-K6)/K6)</f>
         <v/>
       </c>
       <c r="M6" s="6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O6" s="7">
         <f>IF(J6=0,"",E6/J6)</f>
         <v/>
       </c>
       <c r="P6" s="6" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>187.69</v>
+        <v>128.94</v>
       </c>
       <c r="S6" s="2">
         <f>IF(AND('Engine Inputs'!E6=0,R6=0),"",IF('Engine Inputs'!E6=0,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&gt;Config!$B$2,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1069,7 +1069,7 @@
         <v>89</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>0</v>
+        <v>14.99</v>
       </c>
       <c r="V6" s="2">
         <f>IF(AND('Engine Inputs'!D6=0,U6=0),"",IF('Engine Inputs'!D6=0,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&gt;Config!$B$2,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>208.8</v>
+        <v>223.61</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>315.7</v>
+        <v>164.5</v>
       </c>
       <c r="G9" s="4">
         <f>E9-F9</f>
@@ -1297,23 +1297,23 @@
         <v/>
       </c>
       <c r="I9" s="4" t="n">
-        <v>28.02</v>
+        <v>162.52</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L9" s="5">
         <f>IF(K9=0,"",(J9-K9)/K9)</f>
         <v/>
       </c>
       <c r="M9" s="6" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O9" s="4">
         <f>IF(J9=0,"",E9/J9)</f>
@@ -1326,7 +1326,7 @@
         <v>579</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>208.8</v>
+        <v>223.61</v>
       </c>
       <c r="S9" s="2">
         <f>IF(AND('Engine Inputs'!E9=0,R9=0),"",IF('Engine Inputs'!E9=0,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&gt;Config!$B$2,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>326.92</v>
+        <v>288.24</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>468.51</v>
+        <v>323.05</v>
       </c>
       <c r="G10" s="7">
         <f>E10-F10</f>
@@ -1386,10 +1386,10 @@
         <v/>
       </c>
       <c r="I10" s="7" t="n">
-        <v>205.97</v>
+        <v>240.18</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>13</v>
@@ -1399,23 +1399,23 @@
         <v/>
       </c>
       <c r="M10" s="6" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O10" s="7">
         <f>IF(J10=0,"",E10/J10)</f>
         <v/>
       </c>
       <c r="P10" s="6" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>180.33</v>
+        <v>207.36</v>
       </c>
       <c r="S10" s="2">
         <f>IF(AND('Engine Inputs'!E10=0,R10=0),"",IF('Engine Inputs'!E10=0,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&gt;Config!$B$2,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1425,7 +1425,7 @@
         <v>93</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>62.09</v>
+        <v>37.27</v>
       </c>
       <c r="V10" s="2">
         <f>IF(AND('Engine Inputs'!D10=0,U10=0),"",IF('Engine Inputs'!D10=0,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&gt;Config!$B$2,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>80.05</v>
+        <v>111.89</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>36.06</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="G11" s="4">
         <f>E11-F11</f>
@@ -1475,23 +1475,23 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>69.38</v>
+        <v>106.52</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>8</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L11" s="5">
         <f>IF(K11=0,"",(J11-K11)/K11)</f>
         <v/>
       </c>
       <c r="M11" s="6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="O11" s="4">
         <f>IF(J11=0,"",E11/J11)</f>
@@ -1504,7 +1504,7 @@
         <v>509</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>81.56999999999999</v>
+        <v>115.44</v>
       </c>
       <c r="S11" s="2">
         <f>IF(AND('Engine Inputs'!E11=0,R11=0),"",IF('Engine Inputs'!E11=0,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&gt;Config!$B$2,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>96.73</v>
+        <v>14.14</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>93.66</v>
+        <v>60.28</v>
       </c>
       <c r="G12" s="7">
         <f>E12-F12</f>
@@ -1564,10 +1564,10 @@
         <v/>
       </c>
       <c r="I12" s="7" t="n">
-        <v>122.78</v>
+        <v>208.28</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>4</v>
@@ -1577,10 +1577,10 @@
         <v/>
       </c>
       <c r="M12" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O12" s="7">
         <f>IF(J12=0,"",E12/J12)</f>
@@ -1593,7 +1593,7 @@
         <v>454</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>64.23</v>
+        <v>7.47</v>
       </c>
       <c r="S12" s="2">
         <f>IF(AND('Engine Inputs'!E12=0,R12=0),"",IF('Engine Inputs'!E12=0,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&gt;Config!$B$2,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1603,7 +1603,7 @@
         <v>37</v>
       </c>
       <c r="U12" s="7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="V12" s="2">
         <f>IF(AND('Engine Inputs'!D12=0,U12=0),"",IF('Engine Inputs'!D12=0,"📈 Up",IF((U12-'Engine Inputs'!D12)/'Engine Inputs'!D12&gt;Config!$B$2,"📈 Up",IF((U12-'Engine Inputs'!D12)/'Engine Inputs'!D12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>23.91</v>
+        <v>6.99</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>109.12</v>
+        <v>102.12</v>
       </c>
       <c r="G13" s="4">
         <f>E13-F13</f>
@@ -1653,23 +1653,23 @@
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>142.56</v>
+        <v>78.14</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L13" s="5">
         <f>IF(K13=0,"",(J13-K13)/K13)</f>
         <v/>
       </c>
       <c r="M13" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O13" s="4">
         <f>IF(J13=0,"",E13/J13)</f>
@@ -1682,7 +1682,7 @@
         <v>487</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>23.91</v>
+        <v>6.99</v>
       </c>
       <c r="S13" s="2">
         <f>IF(AND('Engine Inputs'!E13=0,R13=0),"",IF('Engine Inputs'!E13=0,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&gt;Config!$B$2,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>65.38</v>
+        <v>14.7</v>
       </c>
       <c r="G14" s="4">
         <f>E14-F14</f>
@@ -1742,36 +1742,36 @@
         <v/>
       </c>
       <c r="I14" s="4" t="n">
-        <v>31.95</v>
+        <v>32.4</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L14" s="5">
         <f>IF(K14=0,"",(J14-K14)/K14)</f>
         <v/>
       </c>
       <c r="M14" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O14" s="4">
         <f>IF(J14=0,"",E14/J14)</f>
         <v/>
       </c>
       <c r="P14" s="6" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0</v>
+        <v>90.76000000000001</v>
       </c>
       <c r="S14" s="2">
         <f>IF(AND('Engine Inputs'!E14=0,R14=0),"",IF('Engine Inputs'!E14=0,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&gt;Config!$B$2,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0</v>
+        <v>26.73</v>
       </c>
       <c r="G15" s="7">
         <f>E15-F15</f>
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="5">
         <f>IF(K15=0,"",(J15-K15)/K15)</f>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>19.18</v>
+        <v>0</v>
       </c>
       <c r="G16" s="9">
         <f>E16-F16</f>
@@ -1920,20 +1920,20 @@
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>36.25</v>
+        <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="5">
         <f>IF(K16=0,"",(J16-K16)/K16)</f>
         <v/>
       </c>
       <c r="M16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="6" t="n">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>0</v>
+        <v>28.47</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>0</v>
+        <v>15.19</v>
       </c>
       <c r="G17" s="9">
         <f>E17-F17</f>
@@ -2012,10 +2012,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="5">
         <f>IF(K17=0,"",(J17-K17)/K17)</f>
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" s="9">
         <f>IF(J17=0,"",E17/J17)</f>
@@ -2038,7 +2038,7 @@
         <v>377</v>
       </c>
       <c r="R17" s="9" t="n">
-        <v>0</v>
+        <v>26.99</v>
       </c>
       <c r="S17" s="2">
         <f>IF(AND('Engine Inputs'!E17=0,R17=0),"",IF('Engine Inputs'!E17=0,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&gt;Config!$B$2,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>0</v>
+        <v>23.44</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>0</v>
+        <v>145.04</v>
       </c>
       <c r="G18" s="9">
         <f>E18-F18</f>
@@ -2101,10 +2101,10 @@
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="5">
         <f>IF(K18=0,"",(J18-K18)/K18)</f>
@@ -2114,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" s="9">
         <f>IF(J18=0,"",E18/J18)</f>
@@ -2127,7 +2127,7 @@
         <v>329</v>
       </c>
       <c r="R18" s="9" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="S18" s="2">
         <f>IF(AND('Engine Inputs'!E18=0,R18=0),"",IF('Engine Inputs'!E18=0,"📈 Up",IF((R18-'Engine Inputs'!E18)/'Engine Inputs'!E18&gt;Config!$B$2,"📈 Up",IF((R18-'Engine Inputs'!E18)/'Engine Inputs'!E18&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>33.25</v>
+        <v>0</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>0</v>
@@ -2187,10 +2187,10 @@
         <v/>
       </c>
       <c r="I19" s="7" t="n">
-        <v>37.19</v>
+        <v>117.93</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
@@ -2203,20 +2203,20 @@
         <v>6</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O19" s="7">
         <f>IF(J19=0,"",E19/J19)</f>
         <v/>
       </c>
       <c r="P19" s="6" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>19.12</v>
+        <v>0</v>
       </c>
       <c r="S19" s="2">
         <f>IF(AND('Engine Inputs'!E19=0,R19=0),"",IF('Engine Inputs'!E19=0,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&gt;Config!$B$2,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>5.89</v>
+        <v>34.88</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>10.78</v>
+        <v>0</v>
       </c>
       <c r="G20" s="4">
         <f>E20-F20</f>
@@ -2276,36 +2276,36 @@
         <v/>
       </c>
       <c r="I20" s="4" t="n">
-        <v>14.89</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="5">
         <f>IF(K20=0,"",(J20-K20)/K20)</f>
         <v/>
       </c>
       <c r="M20" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" s="4">
         <f>IF(J20=0,"",E20/J20)</f>
         <v/>
       </c>
       <c r="P20" s="6" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>5.89</v>
+        <v>34.88</v>
       </c>
       <c r="S20" s="2">
         <f>IF(AND('Engine Inputs'!E20=0,R20=0),"",IF('Engine Inputs'!E20=0,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&gt;Config!$B$2,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>0</v>
+        <v>17.74</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>22.07</v>
+        <v>0</v>
       </c>
       <c r="G21" s="7">
         <f>E21-F21</f>
@@ -2365,36 +2365,36 @@
         <v/>
       </c>
       <c r="I21" s="7" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" s="5">
         <f>IF(K21=0,"",(J21-K21)/K21)</f>
         <v/>
       </c>
       <c r="M21" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" s="7">
         <f>IF(J21=0,"",E21/J21)</f>
         <v/>
       </c>
       <c r="P21" s="6" t="n">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="Q21" s="6" t="n">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>0</v>
+        <v>12.49</v>
       </c>
       <c r="S21" s="2">
         <f>IF(AND('Engine Inputs'!E21=0,R21=0),"",IF('Engine Inputs'!E21=0,"📈 Up",IF((R21-'Engine Inputs'!E21)/'Engine Inputs'!E21&gt;Config!$B$2,"📈 Up",IF((R21-'Engine Inputs'!E21)/'Engine Inputs'!E21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0</v>
@@ -2454,7 +2454,7 @@
         <v/>
       </c>
       <c r="I22" s="10" t="n">
-        <v>44.67</v>
+        <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
         <v>0</v>
@@ -2467,7 +2467,7 @@
         <v/>
       </c>
       <c r="M22" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" s="6" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>0</v>
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0</v>
+        <v>20.89</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>0</v>
@@ -2632,10 +2632,10 @@
         <v/>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0</v>
+        <v>28.67</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
@@ -2645,10 +2645,10 @@
         <v/>
       </c>
       <c r="M24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" s="7">
         <f>IF(J24=0,"",E24/J24)</f>
@@ -2661,7 +2661,7 @@
         <v>151</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>0</v>
+        <v>12.89</v>
       </c>
       <c r="S24" s="2">
         <f>IF(AND('Engine Inputs'!E24=0,R24=0),"",IF('Engine Inputs'!E24=0,"📈 Up",IF((R24-'Engine Inputs'!E24)/'Engine Inputs'!E24&gt;Config!$B$2,"📈 Up",IF((R24-'Engine Inputs'!E24)/'Engine Inputs'!E24&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
@@ -2882,13 +2882,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0</v>
+        <v>17.52</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0</v>
+        <v>12.96</v>
       </c>
       <c r="G27" s="4">
         <f>E27-F27</f>
@@ -2902,10 +2902,10 @@
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="5">
         <f>IF(K27=0,"",(J27-K27)/K27)</f>
@@ -2915,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" s="4">
         <f>IF(J27=0,"",E27/J27)</f>
@@ -2928,7 +2928,7 @@
         <v>65</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0</v>
+        <v>17.52</v>
       </c>
       <c r="S27" s="2">
         <f>IF(AND('Engine Inputs'!E27=0,R27=0),"",IF('Engine Inputs'!E27=0,"📈 Up",IF((R27-'Engine Inputs'!E27)/'Engine Inputs'!E27&gt;Config!$B$2,"📈 Up",IF((R27-'Engine Inputs'!E27)/'Engine Inputs'!E27&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
     </row>
     <row r="3">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="5">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>PH Sales 2026-08-12</t>
+          <t>PH Sales 2026-08-16</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>AH Sales 2026-08-12</t>
+          <t>AH Sales 2026-08-16</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>374.56</v>
+        <v>582.95</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>439.25</v>
+        <v>621.3200000000001</v>
       </c>
     </row>
     <row r="3">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D3" s="16" t="n">
-        <v>81.38</v>
+        <v>157.43</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>147.06</v>
+        <v>146.03</v>
       </c>
     </row>
     <row r="4">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>37.57</v>
+        <v>22.44</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>211.08</v>
+        <v>201.31</v>
       </c>
     </row>
     <row r="5">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>73.70999999999999</v>
+        <v>130.93</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>88.81999999999999</v>
+        <v>106.36</v>
       </c>
     </row>
     <row r="6">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>32.14</v>
+        <v>0</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>153.26</v>
+        <v>186.49</v>
       </c>
     </row>
     <row r="7">
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>304.11</v>
+        <v>197.39</v>
       </c>
     </row>
     <row r="10">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>6.58</v>
+        <v>58.87</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>411.21</v>
+        <v>204.99</v>
       </c>
     </row>
     <row r="11">
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>36.99</v>
+        <v>85.44</v>
       </c>
     </row>
     <row r="12">
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>63.24</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="13">
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>113.02</v>
+        <v>107.38</v>
       </c>
     </row>
     <row r="14">
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>65.38</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="15">
@@ -4276,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>0</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="16">
@@ -4299,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>17.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="18">
@@ -4345,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>0</v>
+        <v>134.96</v>
       </c>
     </row>
     <row r="19">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>7.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -4414,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>17.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -4552,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>0</v>
+        <v>12.96</v>
       </c>
     </row>
     <row r="28">
@@ -4806,7 +4806,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Generated 2026-08-14.  "Today" = 2026-08-13.  "Yesterday" = 2026-08-12.  Same Day LY = 2025-08-13.</t>
+          <t xml:space="preserve">  Generated 2026-08-18.  "Today" = 2026-08-17.  "Yesterday" = 2026-08-16.  Same Day LY = 2025-08-17.</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-13</t>
+          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-17</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2026-08-13 was a Thursday; 2025-08-13 was a Wednesday). Day-of-week effects are present in this comparison.</t>
+          <t xml:space="preserve">  (2026-08-17 was a Monday; 2025-08-17 was a Sunday). Day-of-week effects are present in this comparison.</t>
         </is>
       </c>
     </row>

--- a/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
+++ b/development/abiraj_mini_aios_workbench/projects/PRJ-2026-015_daily-sales-track/evidence/final_outputs/REQ-17_daily-sales-track/REQ-17-D01_daily_sales_track.xlsx
@@ -657,13 +657,13 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>1122.21</v>
+        <v>1099.92</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>1160.45</v>
+        <v>1110.72</v>
       </c>
       <c r="G2" s="4">
         <f>E2-F2</f>
@@ -674,36 +674,36 @@
         <v/>
       </c>
       <c r="I2" s="4" t="n">
-        <v>928.1</v>
+        <v>1599.22</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L2" s="5">
         <f>IF(K2=0,"",(J2-K2)/K2)</f>
         <v/>
       </c>
       <c r="M2" s="6" t="n">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="O2" s="4">
         <f>IF(J2=0,"",E2/J2)</f>
         <v/>
       </c>
       <c r="P2" s="6" t="n">
-        <v>3062</v>
+        <v>3064</v>
       </c>
       <c r="Q2" s="6" t="n">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="R2" s="4" t="n">
-        <v>603.2</v>
+        <v>656.29</v>
       </c>
       <c r="S2" s="2">
         <f>IF(AND('Engine Inputs'!E2=0,R2=0),"",IF('Engine Inputs'!E2=0,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&gt;Config!$B$2,"📈 Up",IF((R2-'Engine Inputs'!E2)/'Engine Inputs'!E2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -713,7 +713,7 @@
         <v>1306</v>
       </c>
       <c r="U2" s="4" t="n">
-        <v>517.77</v>
+        <v>439.76</v>
       </c>
       <c r="V2" s="2">
         <f>IF(AND('Engine Inputs'!D2=0,U2=0),"",IF('Engine Inputs'!D2=0,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&gt;Config!$B$2,"📈 Up",IF((U2-'Engine Inputs'!D2)/'Engine Inputs'!D2&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>537.51</v>
+        <v>374.52</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>293.97</v>
+        <v>488.06</v>
       </c>
       <c r="G3" s="4">
         <f>E3-F3</f>
@@ -763,36 +763,36 @@
         <v/>
       </c>
       <c r="I3" s="4" t="n">
-        <v>764.91</v>
+        <v>481.24</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="L3" s="5">
         <f>IF(K3=0,"",(J3-K3)/K3)</f>
         <v/>
       </c>
       <c r="M3" s="6" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="O3" s="4">
         <f>IF(J3=0,"",E3/J3)</f>
         <v/>
       </c>
       <c r="P3" s="6" t="n">
-        <v>1699</v>
+        <v>1702</v>
       </c>
       <c r="Q3" s="6" t="n">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>306.32</v>
+        <v>151.51</v>
       </c>
       <c r="S3" s="2">
         <f>IF(AND('Engine Inputs'!E3=0,R3=0),"",IF('Engine Inputs'!E3=0,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&gt;Config!$B$2,"📈 Up",IF((R3-'Engine Inputs'!E3)/'Engine Inputs'!E3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -802,7 +802,7 @@
         <v>597</v>
       </c>
       <c r="U3" s="4" t="n">
-        <v>237.96</v>
+        <v>234.39</v>
       </c>
       <c r="V3" s="2">
         <f>IF(AND('Engine Inputs'!D3=0,U3=0),"",IF('Engine Inputs'!D3=0,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&gt;Config!$B$2,"📈 Up",IF((U3-'Engine Inputs'!D3)/'Engine Inputs'!D3&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E4" s="7" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="F4" s="7" t="n">
         <v>302.99</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>320.86</v>
       </c>
       <c r="G4" s="7">
         <f>E4-F4</f>
@@ -852,23 +852,23 @@
         <v/>
       </c>
       <c r="I4" s="7" t="n">
-        <v>767.77</v>
+        <v>315.86</v>
       </c>
       <c r="J4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>13</v>
-      </c>
-      <c r="K4" s="6" t="n">
-        <v>12</v>
       </c>
       <c r="L4" s="5">
         <f>IF(K4=0,"",(J4-K4)/K4)</f>
         <v/>
       </c>
       <c r="M4" s="6" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O4" s="7">
         <f>IF(J4=0,"",E4/J4)</f>
@@ -881,7 +881,7 @@
         <v>1221</v>
       </c>
       <c r="R4" s="7" t="n">
-        <v>199.69</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="S4" s="2">
         <f>IF(AND('Engine Inputs'!E4=0,R4=0),"",IF('Engine Inputs'!E4=0,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&gt;Config!$B$2,"📈 Up",IF((R4-'Engine Inputs'!E4)/'Engine Inputs'!E4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -891,7 +891,7 @@
         <v>232</v>
       </c>
       <c r="U4" s="7" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="V4" s="2">
         <f>IF(AND('Engine Inputs'!D4=0,U4=0),"",IF('Engine Inputs'!D4=0,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&gt;Config!$B$2,"📈 Up",IF((U4-'Engine Inputs'!D4)/'Engine Inputs'!D4&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E5" s="4" t="n">
+        <v>194.94</v>
+      </c>
+      <c r="F5" s="4" t="n">
         <v>320.64</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>234.77</v>
       </c>
       <c r="G5" s="4">
         <f>E5-F5</f>
@@ -941,36 +941,36 @@
         <v/>
       </c>
       <c r="I5" s="4" t="n">
-        <v>203.52</v>
+        <v>355.25</v>
       </c>
       <c r="J5" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>18</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>15</v>
       </c>
       <c r="L5" s="5">
         <f>IF(K5=0,"",(J5-K5)/K5)</f>
         <v/>
       </c>
       <c r="M5" s="6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="O5" s="4">
         <f>IF(J5=0,"",E5/J5)</f>
         <v/>
       </c>
       <c r="P5" s="6" t="n">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="Q5" s="6" t="n">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>234.1</v>
+        <v>92.94</v>
       </c>
       <c r="S5" s="2">
         <f>IF(AND('Engine Inputs'!E5=0,R5=0),"",IF('Engine Inputs'!E5=0,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&gt;Config!$B$2,"📈 Up",IF((R5-'Engine Inputs'!E5)/'Engine Inputs'!E5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -980,7 +980,7 @@
         <v>470</v>
       </c>
       <c r="U5" s="4" t="n">
-        <v>87.39</v>
+        <v>100.81</v>
       </c>
       <c r="V5" s="2">
         <f>IF(AND('Engine Inputs'!D5=0,U5=0),"",IF('Engine Inputs'!D5=0,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&gt;Config!$B$2,"📈 Up",IF((U5-'Engine Inputs'!D5)/'Engine Inputs'!D5&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1013,13 +1013,13 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E6" s="7" t="n">
+        <v>121.13</v>
+      </c>
+      <c r="F6" s="7" t="n">
         <v>170.81</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>211.06</v>
       </c>
       <c r="G6" s="7">
         <f>E6-F6</f>
@@ -1030,7 +1030,7 @@
         <v/>
       </c>
       <c r="I6" s="7" t="n">
-        <v>337.65</v>
+        <v>221.54</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>6</v>
@@ -1043,23 +1043,23 @@
         <v/>
       </c>
       <c r="M6" s="6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O6" s="7">
         <f>IF(J6=0,"",E6/J6)</f>
         <v/>
       </c>
       <c r="P6" s="6" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="R6" s="7" t="n">
-        <v>128.94</v>
+        <v>89.63</v>
       </c>
       <c r="S6" s="2">
         <f>IF(AND('Engine Inputs'!E6=0,R6=0),"",IF('Engine Inputs'!E6=0,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&gt;Config!$B$2,"📈 Up",IF((R6-'Engine Inputs'!E6)/'Engine Inputs'!E6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1069,7 +1069,7 @@
         <v>89</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>14.99</v>
+        <v>0</v>
       </c>
       <c r="V6" s="2">
         <f>IF(AND('Engine Inputs'!D6=0,U6=0),"",IF('Engine Inputs'!D6=0,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&gt;Config!$B$2,"📈 Up",IF((U6-'Engine Inputs'!D6)/'Engine Inputs'!D6&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E9" s="4" t="n">
+        <v>219.92</v>
+      </c>
+      <c r="F9" s="4" t="n">
         <v>223.61</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>164.5</v>
       </c>
       <c r="G9" s="4">
         <f>E9-F9</f>
@@ -1297,23 +1297,23 @@
         <v/>
       </c>
       <c r="I9" s="4" t="n">
-        <v>162.52</v>
+        <v>314.91</v>
       </c>
       <c r="J9" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>16</v>
-      </c>
-      <c r="K9" s="6" t="n">
-        <v>7</v>
       </c>
       <c r="L9" s="5">
         <f>IF(K9=0,"",(J9-K9)/K9)</f>
         <v/>
       </c>
       <c r="M9" s="6" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O9" s="4">
         <f>IF(J9=0,"",E9/J9)</f>
@@ -1326,7 +1326,7 @@
         <v>579</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>223.61</v>
+        <v>219.92</v>
       </c>
       <c r="S9" s="2">
         <f>IF(AND('Engine Inputs'!E9=0,R9=0),"",IF('Engine Inputs'!E9=0,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&gt;Config!$B$2,"📈 Up",IF((R9-'Engine Inputs'!E9)/'Engine Inputs'!E9&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1369,13 +1369,13 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E10" s="7" t="n">
+        <v>346.21</v>
+      </c>
+      <c r="F10" s="7" t="n">
         <v>288.24</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>323.05</v>
       </c>
       <c r="G10" s="7">
         <f>E10-F10</f>
@@ -1386,23 +1386,23 @@
         <v/>
       </c>
       <c r="I10" s="7" t="n">
-        <v>240.18</v>
+        <v>415.37</v>
       </c>
       <c r="J10" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="K10" s="6" t="n">
         <v>11</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>13</v>
       </c>
       <c r="L10" s="5">
         <f>IF(K10=0,"",(J10-K10)/K10)</f>
         <v/>
       </c>
       <c r="M10" s="6" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O10" s="7">
         <f>IF(J10=0,"",E10/J10)</f>
@@ -1415,7 +1415,7 @@
         <v>467</v>
       </c>
       <c r="R10" s="7" t="n">
-        <v>207.36</v>
+        <v>287.71</v>
       </c>
       <c r="S10" s="2">
         <f>IF(AND('Engine Inputs'!E10=0,R10=0),"",IF('Engine Inputs'!E10=0,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&gt;Config!$B$2,"📈 Up",IF((R10-'Engine Inputs'!E10)/'Engine Inputs'!E10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1425,7 +1425,7 @@
         <v>93</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>37.27</v>
+        <v>0</v>
       </c>
       <c r="V10" s="2">
         <f>IF(AND('Engine Inputs'!D10=0,U10=0),"",IF('Engine Inputs'!D10=0,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&gt;Config!$B$2,"📈 Up",IF((U10-'Engine Inputs'!D10)/'Engine Inputs'!D10&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E11" s="4" t="n">
+        <v>110.16</v>
+      </c>
+      <c r="F11" s="4" t="n">
         <v>111.89</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>78.98999999999999</v>
       </c>
       <c r="G11" s="4">
         <f>E11-F11</f>
@@ -1475,23 +1475,23 @@
         <v/>
       </c>
       <c r="I11" s="4" t="n">
-        <v>106.52</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="J11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="6" t="n">
         <v>8</v>
-      </c>
-      <c r="K11" s="6" t="n">
-        <v>7</v>
       </c>
       <c r="L11" s="5">
         <f>IF(K11=0,"",(J11-K11)/K11)</f>
         <v/>
       </c>
       <c r="M11" s="6" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O11" s="4">
         <f>IF(J11=0,"",E11/J11)</f>
@@ -1504,7 +1504,7 @@
         <v>509</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>115.44</v>
+        <v>117.55</v>
       </c>
       <c r="S11" s="2">
         <f>IF(AND('Engine Inputs'!E11=0,R11=0),"",IF('Engine Inputs'!E11=0,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&gt;Config!$B$2,"📈 Up",IF((R11-'Engine Inputs'!E11)/'Engine Inputs'!E11&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E12" s="7" t="n">
+        <v>77.12</v>
+      </c>
+      <c r="F12" s="7" t="n">
         <v>14.14</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>60.28</v>
       </c>
       <c r="G12" s="7">
         <f>E12-F12</f>
@@ -1564,23 +1564,23 @@
         <v/>
       </c>
       <c r="I12" s="7" t="n">
-        <v>208.28</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="J12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>4</v>
       </c>
       <c r="L12" s="5">
         <f>IF(K12=0,"",(J12-K12)/K12)</f>
         <v/>
       </c>
       <c r="M12" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O12" s="7">
         <f>IF(J12=0,"",E12/J12)</f>
@@ -1593,7 +1593,7 @@
         <v>454</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>7.47</v>
+        <v>50.03</v>
       </c>
       <c r="S12" s="2">
         <f>IF(AND('Engine Inputs'!E12=0,R12=0),"",IF('Engine Inputs'!E12=0,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&gt;Config!$B$2,"📈 Up",IF((R12-'Engine Inputs'!E12)/'Engine Inputs'!E12&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1636,13 +1636,13 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E13" s="4" t="n">
+        <v>297.6</v>
+      </c>
+      <c r="F13" s="4" t="n">
         <v>6.99</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>102.12</v>
       </c>
       <c r="G13" s="4">
         <f>E13-F13</f>
@@ -1653,23 +1653,23 @@
         <v/>
       </c>
       <c r="I13" s="4" t="n">
-        <v>78.14</v>
+        <v>159.61</v>
       </c>
       <c r="J13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="K13" s="6" t="n">
-        <v>9</v>
       </c>
       <c r="L13" s="5">
         <f>IF(K13=0,"",(J13-K13)/K13)</f>
         <v/>
       </c>
       <c r="M13" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="O13" s="4">
         <f>IF(J13=0,"",E13/J13)</f>
@@ -1682,7 +1682,7 @@
         <v>487</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>6.99</v>
+        <v>324.09</v>
       </c>
       <c r="S13" s="2">
         <f>IF(AND('Engine Inputs'!E13=0,R13=0),"",IF('Engine Inputs'!E13=0,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&gt;Config!$B$2,"📈 Up",IF((R13-'Engine Inputs'!E13)/'Engine Inputs'!E13&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1725,13 +1725,13 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E14" s="4" t="n">
+        <v>12.89</v>
+      </c>
+      <c r="F14" s="4" t="n">
         <v>90.76000000000001</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>14.7</v>
       </c>
       <c r="G14" s="4">
         <f>E14-F14</f>
@@ -1742,23 +1742,23 @@
         <v/>
       </c>
       <c r="I14" s="4" t="n">
-        <v>32.4</v>
+        <v>97.73999999999999</v>
       </c>
       <c r="J14" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="6" t="n">
         <v>3</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>1</v>
       </c>
       <c r="L14" s="5">
         <f>IF(K14=0,"",(J14-K14)/K14)</f>
         <v/>
       </c>
       <c r="M14" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O14" s="4">
         <f>IF(J14=0,"",E14/J14)</f>
@@ -1771,7 +1771,7 @@
         <v>435</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>90.76000000000001</v>
+        <v>12.89</v>
       </c>
       <c r="S14" s="2">
         <f>IF(AND('Engine Inputs'!E14=0,R14=0),"",IF('Engine Inputs'!E14=0,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&gt;Config!$B$2,"📈 Up",IF((R14-'Engine Inputs'!E14)/'Engine Inputs'!E14&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>26.73</v>
+        <v>0</v>
       </c>
       <c r="G15" s="7">
         <f>E15-F15</f>
@@ -1831,20 +1831,20 @@
         <v/>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0</v>
+        <v>40.33</v>
       </c>
       <c r="J15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="5">
         <f>IF(K15=0,"",(J15-K15)/K15)</f>
         <v/>
       </c>
       <c r="M15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>0</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v/>
       </c>
       <c r="I16" s="9" t="n">
-        <v>0</v>
+        <v>70.98</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>0</v>
@@ -1933,7 +1933,7 @@
         <v/>
       </c>
       <c r="M16" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E17" s="9" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="F17" s="9" t="n">
         <v>28.47</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>15.19</v>
       </c>
       <c r="G17" s="9">
         <f>E17-F17</f>
@@ -2038,7 +2038,7 @@
         <v>377</v>
       </c>
       <c r="R17" s="9" t="n">
-        <v>26.99</v>
+        <v>31.49</v>
       </c>
       <c r="S17" s="2">
         <f>IF(AND('Engine Inputs'!E17=0,R17=0),"",IF('Engine Inputs'!E17=0,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&gt;Config!$B$2,"📈 Up",IF((R17-'Engine Inputs'!E17)/'Engine Inputs'!E17&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2081,13 +2081,13 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E18" s="9" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="F18" s="9" t="n">
         <v>23.44</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>145.04</v>
       </c>
       <c r="G18" s="9">
         <f>E18-F18</f>
@@ -2098,20 +2098,20 @@
         <v/>
       </c>
       <c r="I18" s="9" t="n">
-        <v>0</v>
+        <v>27.86</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L18" s="5">
         <f>IF(K18=0,"",(J18-K18)/K18)</f>
         <v/>
       </c>
       <c r="M18" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
         <v>1</v>
@@ -2127,7 +2127,7 @@
         <v>329</v>
       </c>
       <c r="R18" s="9" t="n">
-        <v>21.5</v>
+        <v>16.19</v>
       </c>
       <c r="S18" s="2">
         <f>IF(AND('Engine Inputs'!E18=0,R18=0),"",IF('Engine Inputs'!E18=0,"📈 Up",IF((R18-'Engine Inputs'!E18)/'Engine Inputs'!E18&gt;Config!$B$2,"📈 Up",IF((R18-'Engine Inputs'!E18)/'Engine Inputs'!E18&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>0</v>
+        <v>43.31</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>0</v>
@@ -2187,10 +2187,10 @@
         <v/>
       </c>
       <c r="I19" s="7" t="n">
-        <v>117.93</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>6</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19" s="7">
         <f>IF(J19=0,"",E19/J19)</f>
@@ -2216,7 +2216,7 @@
         <v>301</v>
       </c>
       <c r="R19" s="7" t="n">
-        <v>0</v>
+        <v>23.15</v>
       </c>
       <c r="S19" s="2">
         <f>IF(AND('Engine Inputs'!E19=0,R19=0),"",IF('Engine Inputs'!E19=0,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&gt;Config!$B$2,"📈 Up",IF((R19-'Engine Inputs'!E19)/'Engine Inputs'!E19&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2259,13 +2259,13 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E20" s="4" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="F20" s="4" t="n">
         <v>34.88</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="G20" s="4">
         <f>E20-F20</f>
@@ -2276,20 +2276,20 @@
         <v/>
       </c>
       <c r="I20" s="4" t="n">
-        <v>71.70999999999999</v>
+        <v>10.18</v>
       </c>
       <c r="J20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="6" t="n">
         <v>2</v>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="L20" s="5">
         <f>IF(K20=0,"",(J20-K20)/K20)</f>
         <v/>
       </c>
       <c r="M20" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
         <v>2</v>
@@ -2305,7 +2305,7 @@
         <v>266</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>34.88</v>
+        <v>15.96</v>
       </c>
       <c r="S20" s="2">
         <f>IF(AND('Engine Inputs'!E20=0,R20=0),"",IF('Engine Inputs'!E20=0,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&gt;Config!$B$2,"📈 Up",IF((R20-'Engine Inputs'!E20)/'Engine Inputs'!E20&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2348,13 +2348,13 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E21" s="7" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="F21" s="7" t="n">
         <v>17.74</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="G21" s="7">
         <f>E21-F21</f>
@@ -2365,20 +2365,20 @@
         <v/>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0</v>
+        <v>28.55</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="5">
         <f>IF(K21=0,"",(J21-K21)/K21)</f>
         <v/>
       </c>
       <c r="M21" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -2394,7 +2394,7 @@
         <v>200</v>
       </c>
       <c r="R21" s="7" t="n">
-        <v>12.49</v>
+        <v>4.38</v>
       </c>
       <c r="S21" s="2">
         <f>IF(AND('Engine Inputs'!E21=0,R21=0),"",IF('Engine Inputs'!E21=0,"📈 Up",IF((R21-'Engine Inputs'!E21)/'Engine Inputs'!E21&gt;Config!$B$2,"📈 Up",IF((R21-'Engine Inputs'!E21)/'Engine Inputs'!E21&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E23" s="7" t="n">
         <v>0</v>
@@ -2615,13 +2615,13 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7" t="n">
         <v>20.89</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="G24" s="7">
         <f>E24-F24</f>
@@ -2632,23 +2632,23 @@
         <v/>
       </c>
       <c r="I24" s="7" t="n">
-        <v>28.67</v>
+        <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="6" t="n">
         <v>1</v>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>0</v>
       </c>
       <c r="L24" s="5">
         <f>IF(K24=0,"",(J24-K24)/K24)</f>
         <v/>
       </c>
       <c r="M24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24" s="7">
         <f>IF(J24=0,"",E24/J24)</f>
@@ -2661,7 +2661,7 @@
         <v>151</v>
       </c>
       <c r="R24" s="7" t="n">
-        <v>12.89</v>
+        <v>0</v>
       </c>
       <c r="S24" s="2">
         <f>IF(AND('Engine Inputs'!E24=0,R24=0),"",IF('Engine Inputs'!E24=0,"📈 Up",IF((R24-'Engine Inputs'!E24)/'Engine Inputs'!E24&gt;Config!$B$2,"📈 Up",IF((R24-'Engine Inputs'!E24)/'Engine Inputs'!E24&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E25" s="10" t="n">
         <v>0</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
@@ -2882,13 +2882,13 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
         <v>17.52</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>12.96</v>
       </c>
       <c r="G27" s="4">
         <f>E27-F27</f>
@@ -2902,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>1</v>
@@ -2915,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27" s="4">
         <f>IF(J27=0,"",E27/J27)</f>
@@ -2928,7 +2928,7 @@
         <v>65</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>17.52</v>
+        <v>0</v>
       </c>
       <c r="S27" s="2">
         <f>IF(AND('Engine Inputs'!E27=0,R27=0),"",IF('Engine Inputs'!E27=0,"📈 Up",IF((R27-'Engine Inputs'!E27)/'Engine Inputs'!E27&gt;Config!$B$2,"📈 Up",IF((R27-'Engine Inputs'!E27)/'Engine Inputs'!E27&lt;-Config!$B$2,"📉 Down","➡ Stable"))))</f>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E28" s="9" t="n">
         <v>0</v>
@@ -3060,7 +3060,7 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E29" s="7" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E30" s="7" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E31" s="7" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E32" s="4" t="n">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="B2" s="12" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
     </row>
     <row r="3">
@@ -3531,7 +3531,7 @@
         </is>
       </c>
       <c r="B3" s="12" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="5">
@@ -3943,12 +3943,12 @@
       </c>
       <c r="D1" s="13" t="inlineStr">
         <is>
-          <t>PH Sales 2026-08-16</t>
+          <t>PH Sales 2026-08-17</t>
         </is>
       </c>
       <c r="E1" s="13" t="inlineStr">
         <is>
-          <t>AH Sales 2026-08-16</t>
+          <t>AH Sales 2026-08-17</t>
         </is>
       </c>
       <c r="F1" s="15" t="inlineStr">
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>582.95</v>
+        <v>517.77</v>
       </c>
       <c r="E2" s="16" t="n">
-        <v>621.3200000000001</v>
+        <v>591.71</v>
       </c>
     </row>
     <row r="3">
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="D3" s="16" t="n">
-        <v>157.43</v>
+        <v>183.01</v>
       </c>
       <c r="E3" s="16" t="n">
-        <v>146.03</v>
+        <v>306.32</v>
       </c>
     </row>
     <row r="4">
@@ -4020,10 +4020,10 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>22.44</v>
+        <v>3.78</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>201.31</v>
+        <v>199.69</v>
       </c>
     </row>
     <row r="5">
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="D5" s="16" t="n">
-        <v>130.93</v>
+        <v>87.39</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>106.36</v>
+        <v>234.1</v>
       </c>
     </row>
     <row r="6">
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0</v>
+        <v>14.99</v>
       </c>
       <c r="E6" s="17" t="n">
-        <v>186.49</v>
+        <v>128.94</v>
       </c>
     </row>
     <row r="7">
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="16" t="n">
-        <v>197.39</v>
+        <v>223.61</v>
       </c>
     </row>
     <row r="10">
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>58.87</v>
+        <v>37.27</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>204.99</v>
+        <v>207.36</v>
       </c>
     </row>
     <row r="11">
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>85.44</v>
+        <v>115.44</v>
       </c>
     </row>
     <row r="12">
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="17" t="n">
-        <v>33.68</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="13">
@@ -4230,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>107.38</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="14">
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>14.7</v>
+        <v>90.76000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -4276,7 +4276,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="17" t="n">
-        <v>9.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4322,7 +4322,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>14.3</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="18">
@@ -4345,7 +4345,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>134.96</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="19">
@@ -4391,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>0</v>
+        <v>34.88</v>
       </c>
     </row>
     <row r="21">
@@ -4414,7 +4414,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>0</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="22">
@@ -4483,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="17" t="n">
-        <v>0</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="25">
@@ -4552,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>12.96</v>
+        <v>17.52</v>
       </c>
     </row>
     <row r="28">
@@ -4806,7 +4806,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Generated 2026-08-18.  "Today" = 2026-08-17.  "Yesterday" = 2026-08-16.  Same Day LY = 2025-08-17.</t>
+          <t xml:space="preserve">  Generated 2026-08-19.  "Today" = 2026-08-18.  "Yesterday" = 2026-08-17.  Same Day LY = 2025-08-18.</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-17</t>
+          <t xml:space="preserve">  Why not 'Completed' only: orders reach Completed about 2 days after purchase. On 2026-08-18</t>
         </is>
       </c>
     </row>
@@ -5162,7 +5162,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (2026-08-17 was a Monday; 2025-08-17 was a Sunday). Day-of-week effects are present in this comparison.</t>
+          <t xml:space="preserve">  (2026-08-18 was a Tuesday; 2025-08-18 was a Monday). Day-of-week effects are present in this comparison.</t>
         </is>
       </c>
     </row>
